--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891182</v>
+        <v>126891648</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685327</v>
+        <v>685260</v>
       </c>
       <c r="R2" t="n">
-        <v>7107186</v>
+        <v>7107165</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,25 +748,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På späd gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890591</v>
+        <v>126890629</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685370</v>
+        <v>685283</v>
       </c>
       <c r="R3" t="n">
-        <v>7107120</v>
+        <v>7107035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890606</v>
+        <v>126893460</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685377</v>
+        <v>685477</v>
       </c>
       <c r="R4" t="n">
-        <v>7107099</v>
+        <v>7107122</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,6 +955,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -971,12 +972,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -987,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893467</v>
+        <v>126893464</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685256</v>
+        <v>685240</v>
       </c>
       <c r="R5" t="n">
-        <v>7107058</v>
+        <v>7107184</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126893460</v>
+        <v>126890591</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,34 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685477</v>
+        <v>685370</v>
       </c>
       <c r="R6" t="n">
-        <v>7107122</v>
+        <v>7107120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,11 +1167,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1199,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893464</v>
+        <v>126890606</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685240</v>
+        <v>685377</v>
       </c>
       <c r="R7" t="n">
-        <v>7107184</v>
+        <v>7107099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,11 +1268,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1289,12 +1280,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1305,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126891648</v>
+        <v>126893467</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,34 +1307,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685260</v>
+        <v>685256</v>
       </c>
       <c r="R8" t="n">
-        <v>7107165</v>
+        <v>7107058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,7 +1371,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På späd gran</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,12 +1386,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1411,45 +1402,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126890629</v>
+        <v>126891182</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685283</v>
+        <v>685327</v>
       </c>
       <c r="R9" t="n">
-        <v>7107035</v>
+        <v>7107186</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,18 +1489,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126889633</v>
+        <v>126890148</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,34 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685223</v>
+        <v>685419</v>
       </c>
       <c r="R10" t="n">
-        <v>7107049</v>
+        <v>7107117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1597,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890191</v>
+        <v>126889633</v>
       </c>
       <c r="B11" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685257</v>
+        <v>685223</v>
       </c>
       <c r="R11" t="n">
-        <v>7107109</v>
+        <v>7107049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,12 +1698,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890148</v>
+        <v>126890092</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>78770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1725,34 +1725,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685419</v>
+        <v>685268</v>
       </c>
       <c r="R12" t="n">
-        <v>7107117</v>
+        <v>7107182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,15 +1796,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1815,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890587</v>
+        <v>126890166</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1826,34 +1841,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685398</v>
+        <v>685415</v>
       </c>
       <c r="R13" t="n">
-        <v>7106998</v>
+        <v>7107111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1915,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1916,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890092</v>
+        <v>126890071</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,21 +1942,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685268</v>
+        <v>685346</v>
       </c>
       <c r="R14" t="n">
-        <v>7107182</v>
+        <v>7106969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,7 +2050,7 @@
         <v>126890180</v>
       </c>
       <c r="B15" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
         <v>126890100</v>
       </c>
       <c r="B16" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890071</v>
+        <v>126890191</v>
       </c>
       <c r="B17" t="n">
-        <v>78647</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,34 +2280,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685346</v>
+        <v>685257</v>
       </c>
       <c r="R17" t="n">
-        <v>7106969</v>
+        <v>7107109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,30 +2351,15 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890166</v>
+        <v>126890587</v>
       </c>
       <c r="B18" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,34 +2381,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685415</v>
+        <v>685398</v>
       </c>
       <c r="R18" t="n">
-        <v>7107111</v>
+        <v>7106998</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,12 +2455,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2471,45 +2471,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890200</v>
+        <v>126890082</v>
       </c>
       <c r="B19" t="n">
-        <v>77929</v>
+        <v>92609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685218</v>
+        <v>685213</v>
       </c>
       <c r="R19" t="n">
-        <v>7107060</v>
+        <v>7107071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2556,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2572,45 +2572,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890630</v>
+        <v>126891185</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>78417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685421</v>
+        <v>685417</v>
       </c>
       <c r="R20" t="n">
-        <v>7107205</v>
+        <v>7106968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,18 +2651,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2673,45 +2674,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890082</v>
+        <v>126890316</v>
       </c>
       <c r="B21" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685213</v>
+        <v>685410</v>
       </c>
       <c r="R21" t="n">
-        <v>7107071</v>
+        <v>7106991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,6 +2747,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2758,12 +2764,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2774,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891185</v>
+        <v>126890200</v>
       </c>
       <c r="B22" t="n">
-        <v>78386</v>
+        <v>77989</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,34 +2791,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685417</v>
+        <v>685218</v>
       </c>
       <c r="R22" t="n">
-        <v>7106968</v>
+        <v>7107060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2853,19 +2859,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2876,45 +2881,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126890316</v>
+        <v>126890630</v>
       </c>
       <c r="B23" t="n">
-        <v>79598</v>
+        <v>98353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685410</v>
+        <v>685421</v>
       </c>
       <c r="R23" t="n">
-        <v>7106991</v>
+        <v>7107205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,11 +2954,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2966,12 +2966,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891637</v>
+        <v>126890098</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>91319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,34 +2993,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685419</v>
+        <v>685407</v>
       </c>
       <c r="R24" t="n">
-        <v>7107106</v>
+        <v>7107134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,15 +3064,30 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3083,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890075</v>
+        <v>126890156</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,14 +3129,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685334</v>
+        <v>685267</v>
       </c>
       <c r="R25" t="n">
-        <v>7107003</v>
+        <v>7107114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3168,12 +3183,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3187,7 +3202,7 @@
         <v>126890328</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,7 +3289,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3285,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890098</v>
+        <v>126890201</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>78417</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,34 +3311,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685407</v>
+        <v>685214</v>
       </c>
       <c r="R27" t="n">
-        <v>7107134</v>
+        <v>7107061</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3367,30 +3382,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890201</v>
+        <v>126890075</v>
       </c>
       <c r="B28" t="n">
-        <v>78386</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,34 +3412,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685214</v>
+        <v>685334</v>
       </c>
       <c r="R28" t="n">
-        <v>7107061</v>
+        <v>7107003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,12 +3486,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3505,7 +3505,7 @@
         <v>126890101</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890156</v>
+        <v>126891637</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,34 +3614,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685267</v>
+        <v>685419</v>
       </c>
       <c r="R30" t="n">
-        <v>7107114</v>
+        <v>7107106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,12 +3688,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3704,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126890081</v>
+        <v>126890627</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,14 +3735,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685215</v>
+        <v>685410</v>
       </c>
       <c r="R31" t="n">
-        <v>7107071</v>
+        <v>7106989</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,12 +3789,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3805,10 +3805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126891394</v>
+        <v>126890103</v>
       </c>
       <c r="B32" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3816,34 +3816,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685267</v>
+        <v>685370</v>
       </c>
       <c r="R32" t="n">
-        <v>7107032</v>
+        <v>7107029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,12 +3890,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3906,53 +3906,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890616</v>
+        <v>126890146</v>
       </c>
       <c r="B33" t="n">
-        <v>58027</v>
+        <v>91792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>5467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685576</v>
+        <v>685217</v>
       </c>
       <c r="R33" t="n">
-        <v>7107009</v>
+        <v>7107070</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3999,12 +3991,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4015,10 +4007,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126890627</v>
+        <v>126890081</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4046,14 +4038,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685410</v>
+        <v>685215</v>
       </c>
       <c r="R34" t="n">
-        <v>7106989</v>
+        <v>7107071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,12 +4092,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4116,10 +4108,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890146</v>
+        <v>126891394</v>
       </c>
       <c r="B35" t="n">
-        <v>91718</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4127,21 +4119,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5467</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4151,10 +4143,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685217</v>
+        <v>685267</v>
       </c>
       <c r="R35" t="n">
-        <v>7107070</v>
+        <v>7107032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4201,12 +4193,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4217,45 +4209,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126890103</v>
+        <v>126890616</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685370</v>
+        <v>685576</v>
       </c>
       <c r="R36" t="n">
-        <v>7107029</v>
+        <v>7107009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4302,12 +4302,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891170</v>
+        <v>126891178</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,21 +4329,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685426</v>
+        <v>685220</v>
       </c>
       <c r="R37" t="n">
-        <v>7106971</v>
+        <v>7107060</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4419,53 +4419,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891640</v>
+        <v>126891170</v>
       </c>
       <c r="B38" t="n">
-        <v>58027</v>
+        <v>79629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685539</v>
+        <v>685426</v>
       </c>
       <c r="R38" t="n">
-        <v>7107065</v>
+        <v>7106971</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4500,11 +4492,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4517,12 +4504,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4533,45 +4520,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891178</v>
+        <v>126890615</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>80150</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685220</v>
+        <v>685399</v>
       </c>
       <c r="R39" t="n">
-        <v>7107060</v>
+        <v>7107027</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4618,12 +4605,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4634,45 +4621,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890615</v>
+        <v>126890196</v>
       </c>
       <c r="B40" t="n">
-        <v>80119</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685399</v>
+        <v>685270</v>
       </c>
       <c r="R40" t="n">
-        <v>7107027</v>
+        <v>7107166</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4719,12 +4706,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4735,45 +4722,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890196</v>
+        <v>126891640</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685270</v>
+        <v>685539</v>
       </c>
       <c r="R41" t="n">
-        <v>7107166</v>
+        <v>7107065</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4808,6 +4803,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4839,7 +4839,7 @@
         <v>126891173</v>
       </c>
       <c r="B42" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890631</v>
+        <v>126889641</v>
       </c>
       <c r="B43" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4968,14 +4968,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685215</v>
+        <v>685348</v>
       </c>
       <c r="R43" t="n">
-        <v>7107084</v>
+        <v>7106970</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,12 +5022,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126889641</v>
+        <v>126890631</v>
       </c>
       <c r="B44" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5069,14 +5069,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685348</v>
+        <v>685215</v>
       </c>
       <c r="R44" t="n">
-        <v>7106970</v>
+        <v>7107084</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5123,12 +5123,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5139,45 +5139,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890087</v>
+        <v>126891169</v>
       </c>
       <c r="B45" t="n">
-        <v>79598</v>
+        <v>91284</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685222</v>
+        <v>685394</v>
       </c>
       <c r="R45" t="n">
-        <v>7107114</v>
+        <v>7107163</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,30 +5221,15 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5255,32 +5240,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126891169</v>
+        <v>126890325</v>
       </c>
       <c r="B46" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5290,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685394</v>
+        <v>685363</v>
       </c>
       <c r="R46" t="n">
-        <v>7107163</v>
+        <v>7107208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5328,6 +5313,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5340,12 +5330,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5356,10 +5346,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890147</v>
+        <v>126890169</v>
       </c>
       <c r="B47" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5391,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685392</v>
+        <v>685422</v>
       </c>
       <c r="R47" t="n">
-        <v>7107087</v>
+        <v>7107111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5457,10 +5447,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890169</v>
+        <v>126890087</v>
       </c>
       <c r="B48" t="n">
-        <v>78738</v>
+        <v>79629</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5468,34 +5458,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685422</v>
+        <v>685222</v>
       </c>
       <c r="R48" t="n">
-        <v>7107111</v>
+        <v>7107114</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5539,15 +5529,30 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5561,7 +5566,7 @@
         <v>126893463</v>
       </c>
       <c r="B49" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5664,10 +5669,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890325</v>
+        <v>126890147</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5675,34 +5680,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685363</v>
+        <v>685392</v>
       </c>
       <c r="R50" t="n">
-        <v>7107208</v>
+        <v>7107087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126890590</v>
+        <v>126893490</v>
       </c>
       <c r="B51" t="n">
-        <v>79598</v>
+        <v>78770</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5781,34 +5781,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685371</v>
+        <v>685403</v>
       </c>
       <c r="R51" t="n">
-        <v>7107135</v>
+        <v>7107099</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,18 +5849,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5871,48 +5872,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893459</v>
+        <v>126877810</v>
       </c>
       <c r="B52" t="n">
-        <v>105381</v>
+        <v>78770</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221725</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Fäbodtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685327</v>
+        <v>685341</v>
       </c>
       <c r="R52" t="n">
-        <v>7107177</v>
+        <v>7107003</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5939,14 +5940,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5955,33 +5961,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126891181</v>
+        <v>126889632</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6009,14 +6010,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685396</v>
+        <v>685270</v>
       </c>
       <c r="R53" t="n">
-        <v>7106961</v>
+        <v>7107186</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6063,12 +6064,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6079,10 +6080,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126889632</v>
+        <v>126891181</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6110,14 +6111,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685270</v>
+        <v>685396</v>
       </c>
       <c r="R54" t="n">
-        <v>7107186</v>
+        <v>7106961</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6164,12 +6165,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6180,10 +6181,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893490</v>
+        <v>126890083</v>
       </c>
       <c r="B55" t="n">
-        <v>78739</v>
+        <v>78417</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6191,34 +6192,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685403</v>
+        <v>685222</v>
       </c>
       <c r="R55" t="n">
-        <v>7107099</v>
+        <v>7107061</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6259,19 +6260,33 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6282,10 +6297,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126877810</v>
+        <v>126890590</v>
       </c>
       <c r="B56" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6293,37 +6308,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fäbodtjärnen, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685341</v>
+        <v>685371</v>
       </c>
       <c r="R56" t="n">
-        <v>7107003</v>
+        <v>7107135</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6350,19 +6365,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6377,22 +6382,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890083</v>
+        <v>126890329</v>
       </c>
       <c r="B57" t="n">
-        <v>78386</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6400,34 +6409,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685222</v>
+        <v>685287</v>
       </c>
       <c r="R57" t="n">
-        <v>7107061</v>
+        <v>7107034</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6462,6 +6471,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6470,31 +6484,16 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6505,45 +6504,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890329</v>
+        <v>126893459</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>105456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685287</v>
+        <v>685327</v>
       </c>
       <c r="R58" t="n">
-        <v>7107034</v>
+        <v>7107177</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6580,7 +6579,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6589,18 +6588,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890097</v>
+        <v>126890185</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,34 +6622,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685305</v>
+        <v>685259</v>
       </c>
       <c r="R59" t="n">
-        <v>7107176</v>
+        <v>7107105</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6693,30 +6693,15 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6730,7 +6715,7 @@
         <v>126891174</v>
       </c>
       <c r="B60" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6828,10 +6813,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890185</v>
+        <v>126891393</v>
       </c>
       <c r="B61" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,21 +6824,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6848,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685259</v>
+        <v>685263</v>
       </c>
       <c r="R61" t="n">
-        <v>7107105</v>
+        <v>7107150</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6913,12 +6898,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6929,10 +6914,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126891393</v>
+        <v>126890586</v>
       </c>
       <c r="B62" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6960,14 +6945,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685263</v>
+        <v>685419</v>
       </c>
       <c r="R62" t="n">
-        <v>7107150</v>
+        <v>7107080</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7014,12 +6999,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7030,10 +7015,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890592</v>
+        <v>126890618</v>
       </c>
       <c r="B63" t="n">
-        <v>79598</v>
+        <v>78769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7041,21 +7026,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7065,10 +7050,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685368</v>
+        <v>685398</v>
       </c>
       <c r="R63" t="n">
-        <v>7107109</v>
+        <v>7106998</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7131,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890597</v>
+        <v>126890592</v>
       </c>
       <c r="B64" t="n">
-        <v>57817</v>
+        <v>79629</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7142,42 +7127,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685576</v>
+        <v>685368</v>
       </c>
       <c r="R64" t="n">
-        <v>7107009</v>
+        <v>7107109</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7240,10 +7217,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890586</v>
+        <v>126890189</v>
       </c>
       <c r="B65" t="n">
-        <v>79598</v>
+        <v>80986</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7251,34 +7228,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685419</v>
+        <v>685256</v>
       </c>
       <c r="R65" t="n">
-        <v>7107080</v>
+        <v>7107175</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7302,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7341,10 +7318,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890618</v>
+        <v>126890097</v>
       </c>
       <c r="B66" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7329,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685398</v>
+        <v>685305</v>
       </c>
       <c r="R66" t="n">
-        <v>7106998</v>
+        <v>7107176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7423,15 +7400,30 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7434,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126890189</v>
+        <v>126890597</v>
       </c>
       <c r="B67" t="n">
-        <v>80955</v>
+        <v>57817</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7445,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685256</v>
+        <v>685576</v>
       </c>
       <c r="R67" t="n">
-        <v>7107175</v>
+        <v>7107009</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7543,10 +7543,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126890157</v>
+        <v>126889640</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7554,34 +7554,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685265</v>
+        <v>685311</v>
       </c>
       <c r="R68" t="n">
-        <v>7107114</v>
+        <v>7107020</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,12 +7628,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7753,45 +7753,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890091</v>
+        <v>126890188</v>
       </c>
       <c r="B70" t="n">
-        <v>78738</v>
+        <v>57761</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685268</v>
+        <v>685274</v>
       </c>
       <c r="R70" t="n">
-        <v>7107185</v>
+        <v>7107181</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7835,30 +7847,15 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7869,57 +7866,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890188</v>
+        <v>126890595</v>
       </c>
       <c r="B71" t="n">
-        <v>57761</v>
+        <v>91319</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685274</v>
+        <v>685417</v>
       </c>
       <c r="R71" t="n">
-        <v>7107181</v>
+        <v>7107135</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7966,12 +7951,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7982,45 +7967,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126890595</v>
+        <v>126890173</v>
       </c>
       <c r="B72" t="n">
-        <v>91245</v>
+        <v>91480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685417</v>
+        <v>685398</v>
       </c>
       <c r="R72" t="n">
-        <v>7107135</v>
+        <v>7106958</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8067,12 +8052,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8083,32 +8068,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126890173</v>
+        <v>126890157</v>
       </c>
       <c r="B73" t="n">
-        <v>91406</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8118,10 +8103,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685398</v>
+        <v>685265</v>
       </c>
       <c r="R73" t="n">
-        <v>7106958</v>
+        <v>7107114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8184,10 +8169,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126889640</v>
+        <v>126890197</v>
       </c>
       <c r="B74" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8195,34 +8180,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685311</v>
+        <v>685263</v>
       </c>
       <c r="R74" t="n">
-        <v>7107020</v>
+        <v>7107013</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8257,6 +8242,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8269,12 +8259,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8288,7 +8278,7 @@
         <v>126890620</v>
       </c>
       <c r="B75" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8386,10 +8376,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890197</v>
+        <v>126890091</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8397,34 +8387,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685263</v>
+        <v>685268</v>
       </c>
       <c r="R76" t="n">
-        <v>7107013</v>
+        <v>7107185</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8459,11 +8449,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8472,16 +8457,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8492,45 +8492,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890088</v>
+        <v>126890594</v>
       </c>
       <c r="B77" t="n">
-        <v>91210</v>
+        <v>79600</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685251</v>
+        <v>685372</v>
       </c>
       <c r="R77" t="n">
-        <v>7107154</v>
+        <v>7106953</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8574,30 +8574,15 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8608,50 +8593,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126890102</v>
+        <v>126890088</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>91284</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685393</v>
+        <v>685251</v>
       </c>
       <c r="R78" t="n">
-        <v>7107081</v>
+        <v>7107154</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8694,6 +8674,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8714,50 +8709,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126890094</v>
+        <v>126891642</v>
       </c>
       <c r="B79" t="n">
-        <v>57479</v>
+        <v>78769</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102976</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685274</v>
+        <v>685361</v>
       </c>
       <c r="R79" t="n">
-        <v>7107182</v>
+        <v>7107114</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8792,6 +8782,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8804,12 +8799,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8820,10 +8815,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890588</v>
+        <v>126893466</v>
       </c>
       <c r="B80" t="n">
-        <v>79598</v>
+        <v>78769</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,34 +8826,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685418</v>
+        <v>685256</v>
       </c>
       <c r="R80" t="n">
-        <v>7106975</v>
+        <v>7107043</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8893,24 +8888,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8921,10 +8922,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126893466</v>
+        <v>126890588</v>
       </c>
       <c r="B81" t="n">
-        <v>78738</v>
+        <v>79629</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8932,34 +8933,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685256</v>
+        <v>685418</v>
       </c>
       <c r="R81" t="n">
-        <v>7107043</v>
+        <v>7106975</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8994,30 +8995,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9028,10 +9023,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126891642</v>
+        <v>126890080</v>
       </c>
       <c r="B82" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,34 +9034,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685361</v>
+        <v>685217</v>
       </c>
       <c r="R82" t="n">
-        <v>7107114</v>
+        <v>7107067</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9101,11 +9101,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9118,12 +9113,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9134,7 +9129,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890080</v>
+        <v>126890102</v>
       </c>
       <c r="B83" t="n">
         <v>57657</v>
@@ -9165,7 +9160,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9174,10 +9169,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685217</v>
+        <v>685393</v>
       </c>
       <c r="R83" t="n">
-        <v>7107067</v>
+        <v>7107081</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9240,45 +9235,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890594</v>
+        <v>126890094</v>
       </c>
       <c r="B84" t="n">
-        <v>79569</v>
+        <v>57479</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>102976</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685372</v>
+        <v>685274</v>
       </c>
       <c r="R84" t="n">
-        <v>7106953</v>
+        <v>7107182</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,12 +9325,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9341,10 +9341,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890611</v>
+        <v>126890078</v>
       </c>
       <c r="B85" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9352,34 +9352,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685418</v>
+        <v>685255</v>
       </c>
       <c r="R85" t="n">
-        <v>7106975</v>
+        <v>7107048</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9423,15 +9423,30 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9445,7 +9460,7 @@
         <v>126890084</v>
       </c>
       <c r="B86" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9558,10 +9573,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126890612</v>
+        <v>126890611</v>
       </c>
       <c r="B87" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9593,10 +9608,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685371</v>
+        <v>685418</v>
       </c>
       <c r="R87" t="n">
-        <v>7107135</v>
+        <v>7106975</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9659,32 +9674,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126890598</v>
+        <v>126890612</v>
       </c>
       <c r="B88" t="n">
-        <v>80112</v>
+        <v>78770</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9694,10 +9709,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685154</v>
+        <v>685371</v>
       </c>
       <c r="R88" t="n">
-        <v>7107066</v>
+        <v>7107135</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9760,45 +9775,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126890078</v>
+        <v>126890598</v>
       </c>
       <c r="B89" t="n">
-        <v>79598</v>
+        <v>80143</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685255</v>
+        <v>685154</v>
       </c>
       <c r="R89" t="n">
-        <v>7107048</v>
+        <v>7107066</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,30 +9857,15 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9876,45 +9876,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126890099</v>
+        <v>126890178</v>
       </c>
       <c r="B90" t="n">
-        <v>80083</v>
+        <v>98353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685420</v>
+        <v>685495</v>
       </c>
       <c r="R90" t="n">
-        <v>7107121</v>
+        <v>7107045</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9958,30 +9958,15 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9992,10 +9977,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126890619</v>
+        <v>126893458</v>
       </c>
       <c r="B91" t="n">
-        <v>78738</v>
+        <v>57817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10003,34 +9988,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685146</v>
+        <v>685383</v>
       </c>
       <c r="R91" t="n">
-        <v>7107092</v>
+        <v>7107114</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10065,6 +10050,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10077,12 +10067,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10093,10 +10083,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126890628</v>
+        <v>126890190</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>80986</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10104,34 +10094,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685371</v>
+        <v>685223</v>
       </c>
       <c r="R92" t="n">
-        <v>7107135</v>
+        <v>7107071</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10178,12 +10168,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10194,10 +10184,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890190</v>
+        <v>126890628</v>
       </c>
       <c r="B93" t="n">
-        <v>80955</v>
+        <v>79011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10205,34 +10195,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685223</v>
+        <v>685371</v>
       </c>
       <c r="R93" t="n">
-        <v>7107071</v>
+        <v>7107135</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10279,12 +10269,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10295,45 +10285,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890178</v>
+        <v>126890625</v>
       </c>
       <c r="B94" t="n">
-        <v>98278</v>
+        <v>91337</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685495</v>
+        <v>685539</v>
       </c>
       <c r="R94" t="n">
-        <v>7107045</v>
+        <v>7107056</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10380,12 +10370,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10396,10 +10386,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890625</v>
+        <v>126893493</v>
       </c>
       <c r="B95" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10407,34 +10397,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685539</v>
+        <v>685266</v>
       </c>
       <c r="R95" t="n">
-        <v>7107056</v>
+        <v>7107184</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10481,12 +10471,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10497,10 +10487,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893493</v>
+        <v>126890099</v>
       </c>
       <c r="B96" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10508,34 +10498,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685266</v>
+        <v>685420</v>
       </c>
       <c r="R96" t="n">
-        <v>7107184</v>
+        <v>7107121</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,15 +10569,30 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10598,10 +10603,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893458</v>
+        <v>126890619</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>78769</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10609,34 +10614,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685383</v>
+        <v>685146</v>
       </c>
       <c r="R97" t="n">
-        <v>7107114</v>
+        <v>7107092</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10671,11 +10676,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10688,12 +10688,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890323</v>
+        <v>126890155</v>
       </c>
       <c r="B99" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10845,14 +10845,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685393</v>
+        <v>685312</v>
       </c>
       <c r="R99" t="n">
-        <v>7106997</v>
+        <v>7107169</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10887,11 +10887,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Mycket i gran</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -10904,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10920,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890614</v>
+        <v>126890323</v>
       </c>
       <c r="B100" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10931,34 +10926,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685368</v>
+        <v>685393</v>
       </c>
       <c r="R100" t="n">
-        <v>7107109</v>
+        <v>7106997</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10993,6 +10988,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Mycket i gran</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11005,12 +11005,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11021,10 +11021,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126890184</v>
+        <v>126893494</v>
       </c>
       <c r="B101" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11032,34 +11032,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685257</v>
+        <v>685374</v>
       </c>
       <c r="R101" t="n">
-        <v>7107113</v>
+        <v>7106951</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11106,12 +11106,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11125,7 +11125,7 @@
         <v>126889630</v>
       </c>
       <c r="B102" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126893494</v>
+        <v>126890614</v>
       </c>
       <c r="B103" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11234,34 +11234,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685374</v>
+        <v>685368</v>
       </c>
       <c r="R103" t="n">
-        <v>7106951</v>
+        <v>7107109</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126890149</v>
+        <v>126890184</v>
       </c>
       <c r="B104" t="n">
-        <v>91263</v>
+        <v>78770</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685396</v>
+        <v>685257</v>
       </c>
       <c r="R104" t="n">
-        <v>7107168</v>
+        <v>7107113</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126890155</v>
+        <v>126890149</v>
       </c>
       <c r="B105" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11460,10 +11460,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685312</v>
+        <v>685396</v>
       </c>
       <c r="R105" t="n">
-        <v>7107169</v>
+        <v>7107168</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126891177</v>
+        <v>126889621</v>
       </c>
       <c r="B106" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11537,34 +11537,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685232</v>
+        <v>685397</v>
       </c>
       <c r="R106" t="n">
-        <v>7107114</v>
+        <v>7107085</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11611,12 +11611,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11630,7 +11630,7 @@
         <v>126890093</v>
       </c>
       <c r="B107" t="n">
-        <v>80955</v>
+        <v>80986</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>126890633</v>
       </c>
       <c r="B108" t="n">
-        <v>75067</v>
+        <v>75127</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11844,10 +11844,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126889621</v>
+        <v>126890089</v>
       </c>
       <c r="B109" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11855,34 +11855,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685397</v>
+        <v>685254</v>
       </c>
       <c r="R109" t="n">
-        <v>7107085</v>
+        <v>7107171</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11929,12 +11929,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11945,10 +11945,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893465</v>
+        <v>126890327</v>
       </c>
       <c r="B110" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11976,14 +11976,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685211</v>
+        <v>685267</v>
       </c>
       <c r="R110" t="n">
-        <v>7107147</v>
+        <v>7107149</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12035,12 +12035,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12051,32 +12051,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126890161</v>
+        <v>126893465</v>
       </c>
       <c r="B111" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12086,10 +12086,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685360</v>
+        <v>685211</v>
       </c>
       <c r="R111" t="n">
-        <v>7107179</v>
+        <v>7107147</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Artnamn</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12157,10 +12157,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126890317</v>
+        <v>126890589</v>
       </c>
       <c r="B112" t="n">
-        <v>57657</v>
+        <v>79629</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12168,34 +12168,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685420</v>
+        <v>685289</v>
       </c>
       <c r="R112" t="n">
-        <v>7107002</v>
+        <v>7107194</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12230,11 +12230,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färsk ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12247,12 +12242,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12263,10 +12258,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126890327</v>
+        <v>126890317</v>
       </c>
       <c r="B113" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12274,21 +12269,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12298,10 +12293,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685267</v>
+        <v>685420</v>
       </c>
       <c r="R113" t="n">
-        <v>7107149</v>
+        <v>7107002</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12338,7 +12333,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Färsk ringhack på tall</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12358,7 +12353,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12369,45 +12364,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126891176</v>
+        <v>126890161</v>
       </c>
       <c r="B114" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685352</v>
+        <v>685360</v>
       </c>
       <c r="R114" t="n">
-        <v>7107016</v>
+        <v>7107179</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12442,6 +12437,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12454,12 +12454,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12470,10 +12470,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126890589</v>
+        <v>126891176</v>
       </c>
       <c r="B115" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12481,34 +12481,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685289</v>
+        <v>685352</v>
       </c>
       <c r="R115" t="n">
-        <v>7107194</v>
+        <v>7107016</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12555,12 +12555,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12571,10 +12571,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126890089</v>
+        <v>126891177</v>
       </c>
       <c r="B116" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12602,14 +12602,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685254</v>
+        <v>685232</v>
       </c>
       <c r="R116" t="n">
-        <v>7107171</v>
+        <v>7107114</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12656,12 +12656,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12672,45 +12672,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126890608</v>
+        <v>126890073</v>
       </c>
       <c r="B117" t="n">
-        <v>79004</v>
+        <v>79011</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685410</v>
+        <v>685306</v>
       </c>
       <c r="R117" t="n">
-        <v>7106989</v>
+        <v>7107003</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12757,12 +12757,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12773,10 +12773,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126891179</v>
+        <v>126891631</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12784,34 +12784,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685268</v>
+        <v>685262</v>
       </c>
       <c r="R118" t="n">
-        <v>7107012</v>
+        <v>7107166</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12846,6 +12850,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12858,12 +12867,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12874,10 +12883,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126891631</v>
+        <v>126891179</v>
       </c>
       <c r="B119" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12885,38 +12894,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685262</v>
+        <v>685268</v>
       </c>
       <c r="R119" t="n">
-        <v>7107166</v>
+        <v>7107012</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12951,11 +12956,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12968,12 +12968,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12984,45 +12984,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126890073</v>
+        <v>126890608</v>
       </c>
       <c r="B120" t="n">
-        <v>78980</v>
+        <v>79035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685306</v>
+        <v>685410</v>
       </c>
       <c r="R120" t="n">
-        <v>7107003</v>
+        <v>7106989</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13069,12 +13069,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13085,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126890086</v>
+        <v>126890158</v>
       </c>
       <c r="B121" t="n">
-        <v>79569</v>
+        <v>79011</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13096,34 +13096,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685221</v>
+        <v>685225</v>
       </c>
       <c r="R121" t="n">
-        <v>7107115</v>
+        <v>7107113</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13167,30 +13167,15 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13204,7 +13189,7 @@
         <v>126890154</v>
       </c>
       <c r="B122" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13302,10 +13287,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893491</v>
+        <v>126889634</v>
       </c>
       <c r="B123" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13313,34 +13298,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685369</v>
+        <v>685358</v>
       </c>
       <c r="R123" t="n">
-        <v>7107086</v>
+        <v>7106974</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13387,12 +13372,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13403,10 +13388,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126889634</v>
+        <v>126893491</v>
       </c>
       <c r="B124" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13414,34 +13399,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685358</v>
+        <v>685369</v>
       </c>
       <c r="R124" t="n">
-        <v>7106974</v>
+        <v>7107086</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13488,12 +13473,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13504,10 +13489,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126890158</v>
+        <v>126890086</v>
       </c>
       <c r="B125" t="n">
-        <v>78980</v>
+        <v>79600</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13515,34 +13500,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685225</v>
+        <v>685221</v>
       </c>
       <c r="R125" t="n">
-        <v>7107113</v>
+        <v>7107115</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13586,15 +13571,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13605,45 +13605,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893461</v>
+        <v>126890599</v>
       </c>
       <c r="B126" t="n">
-        <v>78647</v>
+        <v>98457</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685338</v>
+        <v>685411</v>
       </c>
       <c r="R126" t="n">
-        <v>7107092</v>
+        <v>7107223</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13678,30 +13678,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13712,10 +13706,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126893468</v>
+        <v>126889622</v>
       </c>
       <c r="B127" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13743,14 +13737,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685403</v>
+        <v>685254</v>
       </c>
       <c r="R127" t="n">
-        <v>7107031</v>
+        <v>7107050</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13785,11 +13779,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13802,12 +13791,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13818,10 +13807,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126890085</v>
+        <v>126893468</v>
       </c>
       <c r="B128" t="n">
-        <v>80955</v>
+        <v>78770</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13829,34 +13818,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685222</v>
+        <v>685403</v>
       </c>
       <c r="R128" t="n">
-        <v>7107058</v>
+        <v>7107031</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13891,6 +13880,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13899,31 +13893,16 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13934,10 +13913,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126889631</v>
+        <v>126890613</v>
       </c>
       <c r="B129" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13945,34 +13924,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685348</v>
+        <v>685370</v>
       </c>
       <c r="R129" t="n">
-        <v>7107202</v>
+        <v>7107120</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14019,12 +13998,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14035,10 +14014,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126890159</v>
+        <v>126890085</v>
       </c>
       <c r="B130" t="n">
-        <v>78980</v>
+        <v>80986</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14046,34 +14025,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685238</v>
+        <v>685222</v>
       </c>
       <c r="R130" t="n">
-        <v>7107094</v>
+        <v>7107058</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14117,15 +14096,30 @@
       <c r="AG130" t="b">
         <v>0</v>
       </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14136,10 +14130,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126890613</v>
+        <v>126893461</v>
       </c>
       <c r="B131" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14147,34 +14141,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685370</v>
+        <v>685338</v>
       </c>
       <c r="R131" t="n">
-        <v>7107120</v>
+        <v>7107092</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14209,24 +14203,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14237,10 +14237,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126889626</v>
+        <v>126890159</v>
       </c>
       <c r="B132" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14266,23 +14266,16 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685337</v>
+        <v>685238</v>
       </c>
       <c r="R132" t="n">
-        <v>7107187</v>
+        <v>7107094</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14323,19 +14316,18 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14346,10 +14338,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126889622</v>
+        <v>126890176</v>
       </c>
       <c r="B133" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14357,34 +14349,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685254</v>
+        <v>685413</v>
       </c>
       <c r="R133" t="n">
-        <v>7107050</v>
+        <v>7107035</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14431,12 +14423,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14447,45 +14439,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126889638</v>
+        <v>126890326</v>
       </c>
       <c r="B134" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685366</v>
+        <v>685271</v>
       </c>
       <c r="R134" t="n">
-        <v>7107208</v>
+        <v>7107170</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14520,6 +14512,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14532,12 +14529,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14548,32 +14545,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126889639</v>
+        <v>126889631</v>
       </c>
       <c r="B135" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14583,10 +14580,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685328</v>
+        <v>685348</v>
       </c>
       <c r="R135" t="n">
-        <v>7107189</v>
+        <v>7107202</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14638,7 +14635,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14649,45 +14646,52 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126890599</v>
+        <v>126889626</v>
       </c>
       <c r="B136" t="n">
-        <v>98382</v>
+        <v>79011</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685411</v>
+        <v>685337</v>
       </c>
       <c r="R136" t="n">
-        <v>7107223</v>
+        <v>7107187</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14728,18 +14732,19 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14750,45 +14755,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126890176</v>
+        <v>126889639</v>
       </c>
       <c r="B137" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685413</v>
+        <v>685328</v>
       </c>
       <c r="R137" t="n">
-        <v>7107035</v>
+        <v>7107189</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14835,12 +14840,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14851,45 +14856,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126890326</v>
+        <v>126889638</v>
       </c>
       <c r="B138" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685271</v>
+        <v>685366</v>
       </c>
       <c r="R138" t="n">
-        <v>7107170</v>
+        <v>7107208</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14924,11 +14929,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -14941,12 +14941,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14957,10 +14957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126890324</v>
+        <v>126890174</v>
       </c>
       <c r="B139" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14988,14 +14988,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685394</v>
+        <v>685415</v>
       </c>
       <c r="R139" t="n">
-        <v>7107061</v>
+        <v>7107015</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15030,11 +15030,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15047,12 +15042,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15063,10 +15058,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126889620</v>
+        <v>126890324</v>
       </c>
       <c r="B140" t="n">
-        <v>79569</v>
+        <v>79011</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15074,34 +15069,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685391</v>
+        <v>685394</v>
       </c>
       <c r="R140" t="n">
-        <v>7107082</v>
+        <v>7107061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15136,6 +15131,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15148,12 +15148,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15167,7 +15167,7 @@
         <v>126890593</v>
       </c>
       <c r="B141" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15265,10 +15265,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126890174</v>
+        <v>126889620</v>
       </c>
       <c r="B142" t="n">
-        <v>78980</v>
+        <v>79600</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15276,34 +15276,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685415</v>
+        <v>685391</v>
       </c>
       <c r="R142" t="n">
-        <v>7107015</v>
+        <v>7107082</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15366,10 +15366,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126890622</v>
+        <v>126891180</v>
       </c>
       <c r="B143" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15377,34 +15377,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685368</v>
+        <v>685372</v>
       </c>
       <c r="R143" t="n">
-        <v>7107109</v>
+        <v>7106948</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15467,10 +15467,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126891638</v>
+        <v>126890074</v>
       </c>
       <c r="B144" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15478,34 +15478,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685363</v>
+        <v>685303</v>
       </c>
       <c r="R144" t="n">
-        <v>7107112</v>
+        <v>7107030</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15552,12 +15552,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15568,10 +15568,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126891180</v>
+        <v>126890162</v>
       </c>
       <c r="B145" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15579,34 +15579,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685372</v>
+        <v>685401</v>
       </c>
       <c r="R145" t="n">
-        <v>7106948</v>
+        <v>7107105</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15653,12 +15653,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126890162</v>
+        <v>126890622</v>
       </c>
       <c r="B146" t="n">
-        <v>91245</v>
+        <v>78769</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15680,34 +15680,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685401</v>
+        <v>685368</v>
       </c>
       <c r="R146" t="n">
-        <v>7107105</v>
+        <v>7107109</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15770,10 +15770,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126890074</v>
+        <v>126890621</v>
       </c>
       <c r="B147" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15781,34 +15781,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685303</v>
+        <v>685370</v>
       </c>
       <c r="R147" t="n">
-        <v>7107030</v>
+        <v>7107120</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15855,12 +15855,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15871,10 +15871,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126890621</v>
+        <v>126891638</v>
       </c>
       <c r="B148" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15882,34 +15882,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685370</v>
+        <v>685363</v>
       </c>
       <c r="R148" t="n">
-        <v>7107120</v>
+        <v>7107112</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15956,12 +15956,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891648</v>
+        <v>126893460</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685260</v>
+        <v>685477</v>
       </c>
       <c r="R2" t="n">
-        <v>7107165</v>
+        <v>7107122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På späd gran</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890629</v>
+        <v>126893464</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,14 +812,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685283</v>
+        <v>685240</v>
       </c>
       <c r="R3" t="n">
-        <v>7107035</v>
+        <v>7107184</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,6 +854,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -866,12 +871,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -882,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893460</v>
+        <v>126891648</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,14 +918,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685477</v>
+        <v>685260</v>
       </c>
       <c r="R4" t="n">
-        <v>7107122</v>
+        <v>7107165</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På späd gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,12 +977,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893464</v>
+        <v>126890629</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,14 +1024,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685240</v>
+        <v>685283</v>
       </c>
       <c r="R5" t="n">
-        <v>7107184</v>
+        <v>7107035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,11 +1066,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890591</v>
+        <v>126890606</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685370</v>
+        <v>685377</v>
       </c>
       <c r="R6" t="n">
-        <v>7107120</v>
+        <v>7107099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,45 +1195,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890606</v>
+        <v>126891182</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685377</v>
+        <v>685327</v>
       </c>
       <c r="R7" t="n">
-        <v>7107099</v>
+        <v>7107186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,18 +1282,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1296,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893467</v>
+        <v>126890591</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,34 +1316,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685256</v>
+        <v>685370</v>
       </c>
       <c r="R8" t="n">
-        <v>7107058</v>
+        <v>7107120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,11 +1378,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1386,12 +1390,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1402,53 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126891182</v>
+        <v>126893467</v>
       </c>
       <c r="B9" t="n">
-        <v>98353</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685327</v>
+        <v>685256</v>
       </c>
       <c r="R9" t="n">
-        <v>7107186</v>
+        <v>7107058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,25 +1479,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890148</v>
+        <v>126890180</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685419</v>
+        <v>685259</v>
       </c>
       <c r="R10" t="n">
-        <v>7107117</v>
+        <v>7107109</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,6 +1583,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126889633</v>
+        <v>126890100</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>75138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685223</v>
+        <v>685405</v>
       </c>
       <c r="R11" t="n">
-        <v>7107049</v>
+        <v>7107108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1700,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1714,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890092</v>
+        <v>126890191</v>
       </c>
       <c r="B12" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1725,34 +1745,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685268</v>
+        <v>685257</v>
       </c>
       <c r="R12" t="n">
-        <v>7107182</v>
+        <v>7107109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,30 +1816,15 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1830,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890166</v>
+        <v>126890587</v>
       </c>
       <c r="B13" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,34 +1846,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685415</v>
+        <v>685398</v>
       </c>
       <c r="R13" t="n">
-        <v>7107111</v>
+        <v>7106998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,12 +1920,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1934,7 +1939,7 @@
         <v>126890071</v>
       </c>
       <c r="B14" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890180</v>
+        <v>126889633</v>
       </c>
       <c r="B15" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,34 +2063,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685259</v>
+        <v>685223</v>
       </c>
       <c r="R15" t="n">
-        <v>7107109</v>
+        <v>7107049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,11 +2125,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2137,12 +2137,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890100</v>
+        <v>126890148</v>
       </c>
       <c r="B16" t="n">
-        <v>75135</v>
+        <v>91343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685405</v>
+        <v>685419</v>
       </c>
       <c r="R16" t="n">
-        <v>7107108</v>
+        <v>7107117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,30 +2235,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2269,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890191</v>
+        <v>126890092</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,34 +2265,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685257</v>
+        <v>685268</v>
       </c>
       <c r="R17" t="n">
-        <v>7107109</v>
+        <v>7107182</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,15 +2336,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890587</v>
+        <v>126890166</v>
       </c>
       <c r="B18" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,34 +2381,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685398</v>
+        <v>685415</v>
       </c>
       <c r="R18" t="n">
-        <v>7106998</v>
+        <v>7107111</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,12 +2455,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2471,45 +2471,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890082</v>
+        <v>126890316</v>
       </c>
       <c r="B19" t="n">
-        <v>92609</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685213</v>
+        <v>685410</v>
       </c>
       <c r="R19" t="n">
-        <v>7107071</v>
+        <v>7106991</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,6 +2544,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2556,12 +2561,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2575,7 +2580,7 @@
         <v>126891185</v>
       </c>
       <c r="B20" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890316</v>
+        <v>126890200</v>
       </c>
       <c r="B21" t="n">
-        <v>79629</v>
+        <v>77992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,34 +2690,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685410</v>
+        <v>685218</v>
       </c>
       <c r="R21" t="n">
-        <v>7106991</v>
+        <v>7107060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,11 +2752,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2764,12 +2764,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2780,45 +2780,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890200</v>
+        <v>126890082</v>
       </c>
       <c r="B22" t="n">
-        <v>77989</v>
+        <v>92615</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685218</v>
+        <v>685213</v>
       </c>
       <c r="R22" t="n">
-        <v>7107060</v>
+        <v>7107071</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,12 +2865,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2884,7 +2884,7 @@
         <v>126890630</v>
       </c>
       <c r="B23" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890098</v>
+        <v>126890201</v>
       </c>
       <c r="B24" t="n">
-        <v>91319</v>
+        <v>78420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,34 +2993,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685407</v>
+        <v>685214</v>
       </c>
       <c r="R24" t="n">
-        <v>7107134</v>
+        <v>7107061</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,30 +3064,15 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3098,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890156</v>
+        <v>126890098</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3109,34 +3094,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685267</v>
+        <v>685407</v>
       </c>
       <c r="R25" t="n">
-        <v>7107114</v>
+        <v>7107134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,15 +3165,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3199,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890328</v>
+        <v>126890101</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,14 +3230,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685268</v>
+        <v>685405</v>
       </c>
       <c r="R26" t="n">
-        <v>7107110</v>
+        <v>7107108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890201</v>
+        <v>126890156</v>
       </c>
       <c r="B27" t="n">
-        <v>78417</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685214</v>
+        <v>685267</v>
       </c>
       <c r="R27" t="n">
-        <v>7107061</v>
+        <v>7107114</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,7 +3404,7 @@
         <v>126890075</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890101</v>
+        <v>126890328</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3533,14 +3533,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685405</v>
+        <v>685268</v>
       </c>
       <c r="R29" t="n">
-        <v>7107108</v>
+        <v>7107110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3587,12 +3587,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3606,7 +3606,7 @@
         <v>126891637</v>
       </c>
       <c r="B30" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126890627</v>
+        <v>126891394</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3715,34 +3715,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685410</v>
+        <v>685267</v>
       </c>
       <c r="R31" t="n">
-        <v>7106989</v>
+        <v>7107032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,12 +3789,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3805,10 +3805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890103</v>
+        <v>126890627</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,14 +3836,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685370</v>
+        <v>685410</v>
       </c>
       <c r="R32" t="n">
-        <v>7107029</v>
+        <v>7106989</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,12 +3890,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3909,7 +3909,7 @@
         <v>126890146</v>
       </c>
       <c r="B33" t="n">
-        <v>91792</v>
+        <v>91798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>126890081</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891394</v>
+        <v>126890103</v>
       </c>
       <c r="B35" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4119,34 +4119,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685267</v>
+        <v>685370</v>
       </c>
       <c r="R35" t="n">
-        <v>7107032</v>
+        <v>7107029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4193,12 +4193,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891178</v>
+        <v>126890196</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4349,14 +4349,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685220</v>
+        <v>685270</v>
       </c>
       <c r="R37" t="n">
-        <v>7107060</v>
+        <v>7107166</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4403,12 +4403,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891170</v>
+        <v>126891178</v>
       </c>
       <c r="B38" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685426</v>
+        <v>685220</v>
       </c>
       <c r="R38" t="n">
-        <v>7106971</v>
+        <v>7107060</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890615</v>
+        <v>126891640</v>
       </c>
       <c r="B39" t="n">
-        <v>80150</v>
+        <v>58027</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4531,34 +4531,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685399</v>
+        <v>685539</v>
       </c>
       <c r="R39" t="n">
-        <v>7107027</v>
+        <v>7107065</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4593,6 +4601,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4605,12 +4618,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4621,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890196</v>
+        <v>126891173</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4632,34 +4645,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685270</v>
+        <v>685248</v>
       </c>
       <c r="R40" t="n">
-        <v>7107166</v>
+        <v>7107014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4706,12 +4719,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4722,53 +4735,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126891640</v>
+        <v>126891170</v>
       </c>
       <c r="B41" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685539</v>
+        <v>685426</v>
       </c>
       <c r="R41" t="n">
-        <v>7107065</v>
+        <v>7106971</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,11 +4808,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4836,45 +4836,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891173</v>
+        <v>126890615</v>
       </c>
       <c r="B42" t="n">
-        <v>78770</v>
+        <v>80153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685248</v>
+        <v>685399</v>
       </c>
       <c r="R42" t="n">
-        <v>7107014</v>
+        <v>7107027</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4921,12 +4921,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4937,10 +4937,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126889641</v>
+        <v>126890169</v>
       </c>
       <c r="B43" t="n">
-        <v>78678</v>
+        <v>78772</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4948,34 +4948,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685348</v>
+        <v>685422</v>
       </c>
       <c r="R43" t="n">
-        <v>7106970</v>
+        <v>7107111</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,12 +5022,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890631</v>
+        <v>126890087</v>
       </c>
       <c r="B44" t="n">
-        <v>78678</v>
+        <v>79632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685215</v>
+        <v>685222</v>
       </c>
       <c r="R44" t="n">
-        <v>7107084</v>
+        <v>7107114</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5120,15 +5120,30 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5139,45 +5154,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126891169</v>
+        <v>126893463</v>
       </c>
       <c r="B45" t="n">
-        <v>91284</v>
+        <v>79632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685394</v>
+        <v>685387</v>
       </c>
       <c r="R45" t="n">
-        <v>7107163</v>
+        <v>7107051</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5212,6 +5227,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5224,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5240,10 +5260,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890325</v>
+        <v>126890147</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,34 +5271,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685363</v>
+        <v>685392</v>
       </c>
       <c r="R46" t="n">
-        <v>7107208</v>
+        <v>7107087</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5313,11 +5333,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5330,12 +5345,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5346,10 +5361,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890169</v>
+        <v>126890325</v>
       </c>
       <c r="B47" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,34 +5372,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685422</v>
+        <v>685363</v>
       </c>
       <c r="R47" t="n">
-        <v>7107111</v>
+        <v>7107208</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,6 +5434,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5431,12 +5451,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5447,45 +5467,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890087</v>
+        <v>126891169</v>
       </c>
       <c r="B48" t="n">
-        <v>79629</v>
+        <v>91290</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685222</v>
+        <v>685394</v>
       </c>
       <c r="R48" t="n">
-        <v>7107114</v>
+        <v>7107163</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,30 +5549,15 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5563,10 +5568,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893463</v>
+        <v>126889641</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>78681</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5574,34 +5579,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685387</v>
+        <v>685348</v>
       </c>
       <c r="R49" t="n">
-        <v>7107051</v>
+        <v>7106970</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,11 +5641,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5653,12 +5653,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890147</v>
+        <v>126890631</v>
       </c>
       <c r="B50" t="n">
-        <v>78769</v>
+        <v>78681</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5680,34 +5680,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685392</v>
+        <v>685215</v>
       </c>
       <c r="R50" t="n">
-        <v>7107087</v>
+        <v>7107084</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893490</v>
+        <v>126889632</v>
       </c>
       <c r="B51" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5781,34 +5781,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685403</v>
+        <v>685270</v>
       </c>
       <c r="R51" t="n">
-        <v>7107099</v>
+        <v>7107186</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,19 +5849,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5872,10 +5871,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126877810</v>
+        <v>126891181</v>
       </c>
       <c r="B52" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,37 +5882,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fäbodtjärnen, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685341</v>
+        <v>685396</v>
       </c>
       <c r="R52" t="n">
-        <v>7107003</v>
+        <v>7106961</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5940,19 +5939,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5967,57 +5956,61 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889632</v>
+        <v>126893459</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>105462</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685270</v>
+        <v>685327</v>
       </c>
       <c r="R53" t="n">
-        <v>7107186</v>
+        <v>7107177</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6052,24 +6045,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6080,10 +6079,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891181</v>
+        <v>126877810</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6091,37 +6090,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Fäbodtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685396</v>
+        <v>685341</v>
       </c>
       <c r="R54" t="n">
-        <v>7106961</v>
+        <v>7107003</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6148,9 +6147,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6165,26 +6174,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890083</v>
+        <v>126893490</v>
       </c>
       <c r="B55" t="n">
-        <v>78417</v>
+        <v>78773</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6192,34 +6197,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685222</v>
+        <v>685403</v>
       </c>
       <c r="R55" t="n">
-        <v>7107061</v>
+        <v>7107099</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6260,33 +6265,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6297,10 +6288,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126890590</v>
+        <v>126890083</v>
       </c>
       <c r="B56" t="n">
-        <v>79629</v>
+        <v>78420</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6308,34 +6299,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685371</v>
+        <v>685222</v>
       </c>
       <c r="R56" t="n">
-        <v>7107135</v>
+        <v>7107061</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6379,15 +6370,30 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6398,10 +6404,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890329</v>
+        <v>126890590</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6409,34 +6415,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685287</v>
+        <v>685371</v>
       </c>
       <c r="R57" t="n">
-        <v>7107034</v>
+        <v>7107135</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,11 +6477,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6488,12 +6489,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6504,45 +6505,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893459</v>
+        <v>126890329</v>
       </c>
       <c r="B58" t="n">
-        <v>105456</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685327</v>
+        <v>685287</v>
       </c>
       <c r="R58" t="n">
-        <v>7107177</v>
+        <v>7107034</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6579,7 +6580,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6588,19 +6589,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890185</v>
+        <v>126891393</v>
       </c>
       <c r="B59" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685259</v>
+        <v>685263</v>
       </c>
       <c r="R59" t="n">
-        <v>7107105</v>
+        <v>7107150</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6696,12 +6696,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6712,10 +6712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891174</v>
+        <v>126890586</v>
       </c>
       <c r="B60" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6723,34 +6723,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685430</v>
+        <v>685419</v>
       </c>
       <c r="R60" t="n">
-        <v>7106963</v>
+        <v>7107080</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6797,12 +6797,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6813,10 +6813,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126891393</v>
+        <v>126890618</v>
       </c>
       <c r="B61" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6824,34 +6824,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685263</v>
+        <v>685398</v>
       </c>
       <c r="R61" t="n">
-        <v>7107150</v>
+        <v>7106998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6898,12 +6898,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890586</v>
+        <v>126890592</v>
       </c>
       <c r="B62" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685419</v>
+        <v>685368</v>
       </c>
       <c r="R62" t="n">
-        <v>7107080</v>
+        <v>7107109</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890618</v>
+        <v>126890097</v>
       </c>
       <c r="B63" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7026,34 +7026,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685398</v>
+        <v>685305</v>
       </c>
       <c r="R63" t="n">
-        <v>7106998</v>
+        <v>7107176</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7097,15 +7097,30 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7116,10 +7131,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890592</v>
+        <v>126890597</v>
       </c>
       <c r="B64" t="n">
-        <v>79629</v>
+        <v>57817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,34 +7142,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685368</v>
+        <v>685576</v>
       </c>
       <c r="R64" t="n">
-        <v>7107109</v>
+        <v>7107009</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7220,7 +7243,7 @@
         <v>126890189</v>
       </c>
       <c r="B65" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7318,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890097</v>
+        <v>126890185</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7329,34 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685305</v>
+        <v>685259</v>
       </c>
       <c r="R66" t="n">
-        <v>7107176</v>
+        <v>7107105</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7400,30 +7423,15 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7434,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126890597</v>
+        <v>126891174</v>
       </c>
       <c r="B67" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7445,42 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685576</v>
+        <v>685430</v>
       </c>
       <c r="R67" t="n">
-        <v>7107009</v>
+        <v>7106963</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7543,10 +7543,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889640</v>
+        <v>126890620</v>
       </c>
       <c r="B68" t="n">
-        <v>78678</v>
+        <v>78772</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7554,34 +7554,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685311</v>
+        <v>685161</v>
       </c>
       <c r="R68" t="n">
-        <v>7107020</v>
+        <v>7107091</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,12 +7628,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7644,53 +7644,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890617</v>
+        <v>126890091</v>
       </c>
       <c r="B69" t="n">
-        <v>58027</v>
+        <v>78772</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685406</v>
+        <v>685268</v>
       </c>
       <c r="R69" t="n">
-        <v>7107034</v>
+        <v>7107185</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7734,15 +7726,30 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7866,10 +7873,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890595</v>
+        <v>126889640</v>
       </c>
       <c r="B71" t="n">
-        <v>91319</v>
+        <v>78681</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7877,34 +7884,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685417</v>
+        <v>685311</v>
       </c>
       <c r="R71" t="n">
-        <v>7107135</v>
+        <v>7107020</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7951,12 +7958,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7967,45 +7974,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126890173</v>
+        <v>126890595</v>
       </c>
       <c r="B72" t="n">
-        <v>91480</v>
+        <v>91325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685398</v>
+        <v>685417</v>
       </c>
       <c r="R72" t="n">
-        <v>7106958</v>
+        <v>7107135</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8052,12 +8059,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8071,7 +8078,7 @@
         <v>126890157</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8172,7 +8179,7 @@
         <v>126890197</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8275,45 +8282,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890620</v>
+        <v>126890173</v>
       </c>
       <c r="B75" t="n">
-        <v>78769</v>
+        <v>91486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685161</v>
+        <v>685398</v>
       </c>
       <c r="R75" t="n">
-        <v>7107091</v>
+        <v>7106958</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8360,12 +8367,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8376,45 +8383,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890091</v>
+        <v>126890617</v>
       </c>
       <c r="B76" t="n">
-        <v>78769</v>
+        <v>58027</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685268</v>
+        <v>685406</v>
       </c>
       <c r="R76" t="n">
-        <v>7107185</v>
+        <v>7107034</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8458,30 +8473,15 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8492,45 +8492,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890594</v>
+        <v>126890088</v>
       </c>
       <c r="B77" t="n">
-        <v>79600</v>
+        <v>91290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685372</v>
+        <v>685251</v>
       </c>
       <c r="R77" t="n">
-        <v>7106953</v>
+        <v>7107154</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8574,15 +8574,30 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8593,45 +8608,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126890088</v>
+        <v>126890102</v>
       </c>
       <c r="B78" t="n">
-        <v>91284</v>
+        <v>57657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685251</v>
+        <v>685393</v>
       </c>
       <c r="R78" t="n">
-        <v>7107154</v>
+        <v>7107081</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8674,21 +8694,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8709,10 +8714,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126891642</v>
+        <v>126890080</v>
       </c>
       <c r="B79" t="n">
-        <v>78769</v>
+        <v>57657</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8720,34 +8725,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685361</v>
+        <v>685217</v>
       </c>
       <c r="R79" t="n">
-        <v>7107114</v>
+        <v>7107067</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8782,11 +8792,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8799,12 +8804,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8815,45 +8820,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126893466</v>
+        <v>126890094</v>
       </c>
       <c r="B80" t="n">
-        <v>78769</v>
+        <v>57479</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>102976</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685256</v>
+        <v>685274</v>
       </c>
       <c r="R80" t="n">
-        <v>7107043</v>
+        <v>7107182</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8888,30 +8898,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8922,10 +8926,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890588</v>
+        <v>126891642</v>
       </c>
       <c r="B81" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8933,34 +8937,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685418</v>
+        <v>685361</v>
       </c>
       <c r="R81" t="n">
-        <v>7106975</v>
+        <v>7107114</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8995,6 +8999,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9007,12 +9016,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9023,10 +9032,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890080</v>
+        <v>126893466</v>
       </c>
       <c r="B82" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9034,39 +9043,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685217</v>
+        <v>685256</v>
       </c>
       <c r="R82" t="n">
-        <v>7107067</v>
+        <v>7107043</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9101,24 +9105,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9129,10 +9139,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890102</v>
+        <v>126890588</v>
       </c>
       <c r="B83" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9140,39 +9150,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685393</v>
+        <v>685418</v>
       </c>
       <c r="R83" t="n">
-        <v>7107081</v>
+        <v>7106975</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9219,12 +9224,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9235,50 +9240,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890094</v>
+        <v>126890594</v>
       </c>
       <c r="B84" t="n">
-        <v>57479</v>
+        <v>79603</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102976</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685274</v>
+        <v>685372</v>
       </c>
       <c r="R84" t="n">
-        <v>7107182</v>
+        <v>7106953</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,12 +9325,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9344,7 +9344,7 @@
         <v>126890078</v>
       </c>
       <c r="B85" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9457,45 +9457,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126890084</v>
+        <v>126890598</v>
       </c>
       <c r="B86" t="n">
-        <v>77989</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685223</v>
+        <v>685154</v>
       </c>
       <c r="R86" t="n">
-        <v>7107061</v>
+        <v>7107066</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9539,30 +9539,15 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9573,10 +9558,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126890611</v>
+        <v>126890084</v>
       </c>
       <c r="B87" t="n">
-        <v>78770</v>
+        <v>77992</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9584,34 +9569,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685418</v>
+        <v>685223</v>
       </c>
       <c r="R87" t="n">
-        <v>7106975</v>
+        <v>7107061</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9655,15 +9640,30 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9677,7 +9677,7 @@
         <v>126890612</v>
       </c>
       <c r="B88" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9775,32 +9775,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126890598</v>
+        <v>126890611</v>
       </c>
       <c r="B89" t="n">
-        <v>80143</v>
+        <v>78773</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9810,10 +9810,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685154</v>
+        <v>685418</v>
       </c>
       <c r="R89" t="n">
-        <v>7107066</v>
+        <v>7106975</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9876,45 +9876,49 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126890178</v>
+        <v>126891632</v>
       </c>
       <c r="B90" t="n">
-        <v>98353</v>
+        <v>57654</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685495</v>
+        <v>685370</v>
       </c>
       <c r="R90" t="n">
-        <v>7107045</v>
+        <v>7107190</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9949,6 +9953,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9961,12 +9970,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9977,10 +9986,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126893458</v>
+        <v>126890619</v>
       </c>
       <c r="B91" t="n">
-        <v>57817</v>
+        <v>78772</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9988,34 +9997,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685383</v>
+        <v>685146</v>
       </c>
       <c r="R91" t="n">
-        <v>7107114</v>
+        <v>7107092</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10050,11 +10059,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10067,12 +10071,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10086,7 +10090,7 @@
         <v>126890190</v>
       </c>
       <c r="B92" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10184,10 +10188,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890628</v>
+        <v>126890099</v>
       </c>
       <c r="B93" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10195,34 +10199,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685371</v>
+        <v>685420</v>
       </c>
       <c r="R93" t="n">
-        <v>7107135</v>
+        <v>7107121</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10266,15 +10270,30 @@
       <c r="AG93" t="b">
         <v>0</v>
       </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10285,10 +10304,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890625</v>
+        <v>126893458</v>
       </c>
       <c r="B94" t="n">
-        <v>91337</v>
+        <v>57817</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10296,34 +10315,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685539</v>
+        <v>685383</v>
       </c>
       <c r="R94" t="n">
-        <v>7107056</v>
+        <v>7107114</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10358,6 +10377,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10370,12 +10394,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10386,45 +10410,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893493</v>
+        <v>126890178</v>
       </c>
       <c r="B95" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685266</v>
+        <v>685495</v>
       </c>
       <c r="R95" t="n">
-        <v>7107184</v>
+        <v>7107045</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10471,12 +10495,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10487,10 +10511,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890099</v>
+        <v>126890628</v>
       </c>
       <c r="B96" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10498,34 +10522,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685420</v>
+        <v>685371</v>
       </c>
       <c r="R96" t="n">
-        <v>7107121</v>
+        <v>7107135</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10569,30 +10593,15 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10603,10 +10612,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126890619</v>
+        <v>126893493</v>
       </c>
       <c r="B97" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10614,34 +10623,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685146</v>
+        <v>685266</v>
       </c>
       <c r="R97" t="n">
-        <v>7107092</v>
+        <v>7107184</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10688,12 +10697,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10704,10 +10713,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126891632</v>
+        <v>126890625</v>
       </c>
       <c r="B98" t="n">
-        <v>57654</v>
+        <v>91343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10715,38 +10724,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685370</v>
+        <v>685539</v>
       </c>
       <c r="R98" t="n">
-        <v>7107190</v>
+        <v>7107056</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10781,11 +10786,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Bohål i gran. Långt ner.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10798,12 +10798,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890155</v>
+        <v>126890614</v>
       </c>
       <c r="B99" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,34 +10825,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685312</v>
+        <v>685368</v>
       </c>
       <c r="R99" t="n">
-        <v>7107169</v>
+        <v>7107109</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10899,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890323</v>
+        <v>126890184</v>
       </c>
       <c r="B100" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685393</v>
+        <v>685257</v>
       </c>
       <c r="R100" t="n">
-        <v>7106997</v>
+        <v>7107113</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10988,11 +10988,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Mycket i gran</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11005,12 +11000,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11021,10 +11016,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126893494</v>
+        <v>126890155</v>
       </c>
       <c r="B101" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11052,14 +11047,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685374</v>
+        <v>685312</v>
       </c>
       <c r="R101" t="n">
-        <v>7106951</v>
+        <v>7107169</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11106,12 +11101,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11122,10 +11117,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126889630</v>
+        <v>126890323</v>
       </c>
       <c r="B102" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11153,14 +11148,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685385</v>
+        <v>685393</v>
       </c>
       <c r="R102" t="n">
-        <v>7106995</v>
+        <v>7106997</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11195,6 +11190,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Mycket i gran</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126890614</v>
+        <v>126893494</v>
       </c>
       <c r="B103" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11234,34 +11234,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685368</v>
+        <v>685374</v>
       </c>
       <c r="R103" t="n">
-        <v>7107109</v>
+        <v>7106951</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126890184</v>
+        <v>126889630</v>
       </c>
       <c r="B104" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,34 +11335,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685257</v>
+        <v>685385</v>
       </c>
       <c r="R104" t="n">
-        <v>7107113</v>
+        <v>7106995</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11409,12 +11409,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11428,7 +11428,7 @@
         <v>126890149</v>
       </c>
       <c r="B105" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126889621</v>
+        <v>126890589</v>
       </c>
       <c r="B106" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11537,34 +11537,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685397</v>
+        <v>685289</v>
       </c>
       <c r="R106" t="n">
-        <v>7107085</v>
+        <v>7107194</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11611,12 +11611,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11630,7 +11630,7 @@
         <v>126890093</v>
       </c>
       <c r="B107" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>126890633</v>
       </c>
       <c r="B108" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>126890089</v>
       </c>
       <c r="B109" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11945,45 +11945,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126890327</v>
+        <v>126890161</v>
       </c>
       <c r="B110" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685267</v>
+        <v>685360</v>
       </c>
       <c r="R110" t="n">
-        <v>7107149</v>
+        <v>7107179</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Artnamn</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12035,12 +12035,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12051,10 +12051,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893465</v>
+        <v>126890327</v>
       </c>
       <c r="B111" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12082,14 +12082,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685211</v>
+        <v>685267</v>
       </c>
       <c r="R111" t="n">
-        <v>7107147</v>
+        <v>7107149</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12141,12 +12141,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12157,10 +12157,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126890589</v>
+        <v>126893465</v>
       </c>
       <c r="B112" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12168,34 +12168,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685289</v>
+        <v>685211</v>
       </c>
       <c r="R112" t="n">
-        <v>7107194</v>
+        <v>7107147</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12230,6 +12230,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12242,12 +12247,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12258,10 +12263,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126890317</v>
+        <v>126891176</v>
       </c>
       <c r="B113" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12269,21 +12274,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12293,10 +12298,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685420</v>
+        <v>685352</v>
       </c>
       <c r="R113" t="n">
-        <v>7107002</v>
+        <v>7107016</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12331,11 +12336,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Färsk ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12348,12 +12348,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12364,45 +12364,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126890161</v>
+        <v>126891177</v>
       </c>
       <c r="B114" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685360</v>
+        <v>685232</v>
       </c>
       <c r="R114" t="n">
-        <v>7107179</v>
+        <v>7107114</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12437,11 +12437,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12454,12 +12449,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12470,10 +12465,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126891176</v>
+        <v>126890317</v>
       </c>
       <c r="B115" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12481,21 +12476,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12505,10 +12500,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685352</v>
+        <v>685420</v>
       </c>
       <c r="R115" t="n">
-        <v>7107016</v>
+        <v>7107002</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12543,6 +12538,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färsk ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -12555,12 +12555,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12571,10 +12571,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126891177</v>
+        <v>126889621</v>
       </c>
       <c r="B116" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12582,34 +12582,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685232</v>
+        <v>685397</v>
       </c>
       <c r="R116" t="n">
-        <v>7107114</v>
+        <v>7107085</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12656,12 +12656,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12672,45 +12672,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126890073</v>
+        <v>126890608</v>
       </c>
       <c r="B117" t="n">
-        <v>79011</v>
+        <v>79038</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685306</v>
+        <v>685410</v>
       </c>
       <c r="R117" t="n">
-        <v>7107003</v>
+        <v>7106989</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12757,12 +12757,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12773,10 +12773,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126891631</v>
+        <v>126890073</v>
       </c>
       <c r="B118" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12784,38 +12784,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685262</v>
+        <v>685306</v>
       </c>
       <c r="R118" t="n">
-        <v>7107166</v>
+        <v>7107003</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12850,11 +12846,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12867,12 +12858,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12886,7 +12877,7 @@
         <v>126891179</v>
       </c>
       <c r="B119" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12984,45 +12975,49 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126890608</v>
+        <v>126891631</v>
       </c>
       <c r="B120" t="n">
-        <v>79035</v>
+        <v>57657</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685410</v>
+        <v>685262</v>
       </c>
       <c r="R120" t="n">
-        <v>7106989</v>
+        <v>7107166</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13057,6 +13052,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13069,12 +13069,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13088,7 +13088,7 @@
         <v>126890158</v>
       </c>
       <c r="B121" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>126890154</v>
       </c>
       <c r="B122" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>126889634</v>
       </c>
       <c r="B123" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13388,10 +13388,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893491</v>
+        <v>126890086</v>
       </c>
       <c r="B124" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13399,34 +13399,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685369</v>
+        <v>685221</v>
       </c>
       <c r="R124" t="n">
-        <v>7107086</v>
+        <v>7107115</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13470,15 +13470,30 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13489,10 +13504,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126890086</v>
+        <v>126893491</v>
       </c>
       <c r="B125" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13500,34 +13515,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685221</v>
+        <v>685369</v>
       </c>
       <c r="R125" t="n">
-        <v>7107115</v>
+        <v>7107086</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13571,30 +13586,15 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13605,45 +13605,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126890599</v>
+        <v>126890085</v>
       </c>
       <c r="B126" t="n">
-        <v>98457</v>
+        <v>80989</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>1049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685411</v>
+        <v>685222</v>
       </c>
       <c r="R126" t="n">
-        <v>7107223</v>
+        <v>7107058</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13687,15 +13687,30 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13706,10 +13721,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126889622</v>
+        <v>126893461</v>
       </c>
       <c r="B127" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13717,34 +13732,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685254</v>
+        <v>685338</v>
       </c>
       <c r="R127" t="n">
-        <v>7107050</v>
+        <v>7107092</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13779,24 +13794,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13807,10 +13828,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893468</v>
+        <v>126890159</v>
       </c>
       <c r="B128" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13818,21 +13839,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13842,10 +13863,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685403</v>
+        <v>685238</v>
       </c>
       <c r="R128" t="n">
-        <v>7107031</v>
+        <v>7107094</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13880,11 +13901,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13902,7 +13918,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13913,10 +13929,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126890613</v>
+        <v>126890176</v>
       </c>
       <c r="B129" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13924,34 +13940,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685370</v>
+        <v>685413</v>
       </c>
       <c r="R129" t="n">
-        <v>7107120</v>
+        <v>7107035</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13998,12 +14014,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14014,10 +14030,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126890085</v>
+        <v>126890326</v>
       </c>
       <c r="B130" t="n">
-        <v>80986</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14025,34 +14041,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685222</v>
+        <v>685271</v>
       </c>
       <c r="R130" t="n">
-        <v>7107058</v>
+        <v>7107170</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14087,6 +14103,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14095,31 +14116,16 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14130,45 +14136,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893461</v>
+        <v>126889639</v>
       </c>
       <c r="B131" t="n">
-        <v>78678</v>
+        <v>98359</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685338</v>
+        <v>685328</v>
       </c>
       <c r="R131" t="n">
-        <v>7107092</v>
+        <v>7107189</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14203,30 +14209,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14237,45 +14237,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126890159</v>
+        <v>126889638</v>
       </c>
       <c r="B132" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685238</v>
+        <v>685366</v>
       </c>
       <c r="R132" t="n">
-        <v>7107094</v>
+        <v>7107208</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14322,12 +14322,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14338,10 +14338,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126890176</v>
+        <v>126889626</v>
       </c>
       <c r="B133" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14367,16 +14367,23 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685413</v>
+        <v>685337</v>
       </c>
       <c r="R133" t="n">
-        <v>7107035</v>
+        <v>7107187</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14417,18 +14424,19 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14439,10 +14447,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126890326</v>
+        <v>126889631</v>
       </c>
       <c r="B134" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14470,14 +14478,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685271</v>
+        <v>685348</v>
       </c>
       <c r="R134" t="n">
-        <v>7107170</v>
+        <v>7107202</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14512,11 +14520,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14529,12 +14532,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14545,45 +14548,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126889631</v>
+        <v>126890599</v>
       </c>
       <c r="B135" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685348</v>
+        <v>685411</v>
       </c>
       <c r="R135" t="n">
-        <v>7107202</v>
+        <v>7107223</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14630,12 +14633,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14646,10 +14649,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126889626</v>
+        <v>126889622</v>
       </c>
       <c r="B136" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14657,41 +14660,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685337</v>
+        <v>685254</v>
       </c>
       <c r="R136" t="n">
-        <v>7107187</v>
+        <v>7107050</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14732,7 +14728,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14755,45 +14750,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126889639</v>
+        <v>126890613</v>
       </c>
       <c r="B137" t="n">
-        <v>98353</v>
+        <v>78773</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685328</v>
+        <v>685370</v>
       </c>
       <c r="R137" t="n">
-        <v>7107189</v>
+        <v>7107120</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14840,12 +14835,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14856,45 +14851,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126889638</v>
+        <v>126893468</v>
       </c>
       <c r="B138" t="n">
-        <v>98353</v>
+        <v>78773</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685366</v>
+        <v>685403</v>
       </c>
       <c r="R138" t="n">
-        <v>7107208</v>
+        <v>7107031</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14929,6 +14924,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -14941,12 +14941,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14957,10 +14957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126890174</v>
+        <v>126890324</v>
       </c>
       <c r="B139" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14988,14 +14988,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685415</v>
+        <v>685394</v>
       </c>
       <c r="R139" t="n">
-        <v>7107015</v>
+        <v>7107061</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15030,6 +15030,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15042,12 +15047,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15058,10 +15063,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126890324</v>
+        <v>126889620</v>
       </c>
       <c r="B140" t="n">
-        <v>79011</v>
+        <v>79603</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15069,34 +15074,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685394</v>
+        <v>685391</v>
       </c>
       <c r="R140" t="n">
-        <v>7107061</v>
+        <v>7107082</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15131,11 +15136,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15148,12 +15148,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist, Anne Siivola, Lotta Ihse, Jennica Andersson, Hedda Bring, Eleonor Johansson, Gunilla R Burke, kristina stenmarck, Alexandra Astafourova, Elin Kannerby, Lars-Erik Nilsson, Carl Jansson, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15167,7 +15167,7 @@
         <v>126890593</v>
       </c>
       <c r="B141" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15265,10 +15265,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126889620</v>
+        <v>126890174</v>
       </c>
       <c r="B142" t="n">
-        <v>79600</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15276,34 +15276,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685391</v>
+        <v>685415</v>
       </c>
       <c r="R142" t="n">
-        <v>7107082</v>
+        <v>7107015</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15366,10 +15366,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126891180</v>
+        <v>126890622</v>
       </c>
       <c r="B143" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15377,34 +15377,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685372</v>
+        <v>685368</v>
       </c>
       <c r="R143" t="n">
-        <v>7106948</v>
+        <v>7107109</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15467,10 +15467,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126890074</v>
+        <v>126890621</v>
       </c>
       <c r="B144" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15478,34 +15478,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685303</v>
+        <v>685370</v>
       </c>
       <c r="R144" t="n">
-        <v>7107030</v>
+        <v>7107120</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15552,12 +15552,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15568,10 +15568,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126890162</v>
+        <v>126890074</v>
       </c>
       <c r="B145" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15579,34 +15579,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685401</v>
+        <v>685303</v>
       </c>
       <c r="R145" t="n">
-        <v>7107105</v>
+        <v>7107030</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15653,12 +15653,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126890622</v>
+        <v>126891180</v>
       </c>
       <c r="B146" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15680,34 +15680,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685368</v>
+        <v>685372</v>
       </c>
       <c r="R146" t="n">
-        <v>7107109</v>
+        <v>7106948</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15770,10 +15770,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126890621</v>
+        <v>126891638</v>
       </c>
       <c r="B147" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15781,34 +15781,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685370</v>
+        <v>685363</v>
       </c>
       <c r="R147" t="n">
-        <v>7107120</v>
+        <v>7107112</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15855,12 +15855,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15871,10 +15871,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126891638</v>
+        <v>126890162</v>
       </c>
       <c r="B148" t="n">
-        <v>78770</v>
+        <v>91325</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15882,34 +15882,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685363</v>
+        <v>685401</v>
       </c>
       <c r="R148" t="n">
-        <v>7107112</v>
+        <v>7107105</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15956,12 +15956,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126893460</v>
+        <v>126890591</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685477</v>
+        <v>685370</v>
       </c>
       <c r="R2" t="n">
-        <v>7107122</v>
+        <v>7107120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +748,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126893464</v>
+        <v>126890606</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685240</v>
+        <v>685377</v>
       </c>
       <c r="R3" t="n">
-        <v>7107184</v>
+        <v>7107099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,11 +849,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1094,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890606</v>
+        <v>126893460</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685377</v>
+        <v>685477</v>
       </c>
       <c r="R6" t="n">
-        <v>7107099</v>
+        <v>7107122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1157,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1179,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1195,53 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126891182</v>
+        <v>126893464</v>
       </c>
       <c r="B7" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685327</v>
+        <v>685240</v>
       </c>
       <c r="R7" t="n">
-        <v>7107186</v>
+        <v>7107184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,25 +1263,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Alexandra Astafourova, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1305,45 +1296,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890591</v>
+        <v>126891182</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685370</v>
+        <v>685327</v>
       </c>
       <c r="R8" t="n">
-        <v>7107120</v>
+        <v>7107186</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,18 +1383,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890180</v>
+        <v>126890148</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>91343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685259</v>
+        <v>685419</v>
       </c>
       <c r="R10" t="n">
-        <v>7107109</v>
+        <v>7107117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,11 +1585,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890100</v>
+        <v>126890092</v>
       </c>
       <c r="B11" t="n">
-        <v>75138</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685405</v>
+        <v>685268</v>
       </c>
       <c r="R11" t="n">
-        <v>7107108</v>
+        <v>7107182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,17 +1697,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1734,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890191</v>
+        <v>126890166</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685257</v>
+        <v>685415</v>
       </c>
       <c r="R12" t="n">
-        <v>7107109</v>
+        <v>7107111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1819,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1835,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890587</v>
+        <v>126890071</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,34 +1841,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685398</v>
+        <v>685346</v>
       </c>
       <c r="R13" t="n">
-        <v>7106998</v>
+        <v>7106969</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,15 +1912,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1936,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890071</v>
+        <v>126889633</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,34 +1957,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685346</v>
+        <v>685223</v>
       </c>
       <c r="R14" t="n">
-        <v>7106969</v>
+        <v>7107049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,30 +2028,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2052,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889633</v>
+        <v>126890180</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,34 +2058,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685223</v>
+        <v>685259</v>
       </c>
       <c r="R15" t="n">
-        <v>7107049</v>
+        <v>7107109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,6 +2120,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2137,12 +2137,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890148</v>
+        <v>126890100</v>
       </c>
       <c r="B16" t="n">
-        <v>91343</v>
+        <v>75138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685419</v>
+        <v>685405</v>
       </c>
       <c r="R16" t="n">
-        <v>7107117</v>
+        <v>7107108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,15 +2235,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2254,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890092</v>
+        <v>126890191</v>
       </c>
       <c r="B17" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,34 +2280,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685268</v>
+        <v>685257</v>
       </c>
       <c r="R17" t="n">
-        <v>7107182</v>
+        <v>7107109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,30 +2351,15 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890166</v>
+        <v>126890587</v>
       </c>
       <c r="B18" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,34 +2381,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685415</v>
+        <v>685398</v>
       </c>
       <c r="R18" t="n">
-        <v>7107111</v>
+        <v>7106998</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,12 +2455,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2471,45 +2471,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890316</v>
+        <v>126890082</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685410</v>
+        <v>685213</v>
       </c>
       <c r="R19" t="n">
-        <v>7106991</v>
+        <v>7107071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,11 +2544,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2561,12 +2556,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2577,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891185</v>
+        <v>126890316</v>
       </c>
       <c r="B20" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,21 +2583,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2612,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685417</v>
+        <v>685410</v>
       </c>
       <c r="R20" t="n">
-        <v>7106968</v>
+        <v>7106991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2650,25 +2645,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2679,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890200</v>
+        <v>126891185</v>
       </c>
       <c r="B21" t="n">
-        <v>77992</v>
+        <v>78420</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,34 +2689,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685218</v>
+        <v>685417</v>
       </c>
       <c r="R21" t="n">
-        <v>7107060</v>
+        <v>7106968</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,18 +2757,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2780,45 +2780,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890082</v>
+        <v>126890200</v>
       </c>
       <c r="B22" t="n">
-        <v>92615</v>
+        <v>77992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685213</v>
+        <v>685218</v>
       </c>
       <c r="R22" t="n">
-        <v>7107071</v>
+        <v>7107060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,12 +2865,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890201</v>
+        <v>126890098</v>
       </c>
       <c r="B24" t="n">
-        <v>78420</v>
+        <v>91325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,34 +2993,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685214</v>
+        <v>685407</v>
       </c>
       <c r="R24" t="n">
-        <v>7107061</v>
+        <v>7107134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,15 +3064,30 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3083,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890098</v>
+        <v>126890156</v>
       </c>
       <c r="B25" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,34 +3109,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685407</v>
+        <v>685267</v>
       </c>
       <c r="R25" t="n">
-        <v>7107134</v>
+        <v>7107114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,30 +3180,15 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3199,7 +3199,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890101</v>
+        <v>126890328</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3230,14 +3230,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685405</v>
+        <v>685268</v>
       </c>
       <c r="R26" t="n">
-        <v>7107108</v>
+        <v>7107110</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3300,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890156</v>
+        <v>126890101</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3331,14 +3331,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685267</v>
+        <v>685405</v>
       </c>
       <c r="R27" t="n">
-        <v>7107114</v>
+        <v>7107108</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3385,12 +3385,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890328</v>
+        <v>126890201</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,34 +3513,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685268</v>
+        <v>685214</v>
       </c>
       <c r="R29" t="n">
-        <v>7107110</v>
+        <v>7107061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3587,12 +3587,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3805,10 +3805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890627</v>
+        <v>126890146</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>91798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3816,34 +3816,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685410</v>
+        <v>685217</v>
       </c>
       <c r="R32" t="n">
-        <v>7106989</v>
+        <v>7107070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,12 +3890,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3906,10 +3906,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890146</v>
+        <v>126890627</v>
       </c>
       <c r="B33" t="n">
-        <v>91798</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3917,34 +3917,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685217</v>
+        <v>685410</v>
       </c>
       <c r="R33" t="n">
-        <v>7107070</v>
+        <v>7106989</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3991,12 +3991,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4318,45 +4318,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890196</v>
+        <v>126891640</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685270</v>
+        <v>685539</v>
       </c>
       <c r="R37" t="n">
-        <v>7107166</v>
+        <v>7107065</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,6 +4399,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4403,12 +4416,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4419,7 +4432,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891178</v>
+        <v>126890196</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4450,14 +4463,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685220</v>
+        <v>685270</v>
       </c>
       <c r="R38" t="n">
-        <v>7107060</v>
+        <v>7107166</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4517,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4520,53 +4533,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891640</v>
+        <v>126891178</v>
       </c>
       <c r="B39" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685539</v>
+        <v>685220</v>
       </c>
       <c r="R39" t="n">
-        <v>7107065</v>
+        <v>7107060</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4601,11 +4606,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4618,12 +4618,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891173</v>
+        <v>126891170</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685248</v>
+        <v>685426</v>
       </c>
       <c r="R40" t="n">
-        <v>7107014</v>
+        <v>7106971</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4735,45 +4735,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126891170</v>
+        <v>126890615</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>80153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685426</v>
+        <v>685399</v>
       </c>
       <c r="R41" t="n">
-        <v>7106971</v>
+        <v>7107027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4836,45 +4836,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126890615</v>
+        <v>126891173</v>
       </c>
       <c r="B42" t="n">
-        <v>80153</v>
+        <v>78773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685399</v>
+        <v>685248</v>
       </c>
       <c r="R42" t="n">
-        <v>7107027</v>
+        <v>7107014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4921,12 +4921,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5361,10 +5361,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890325</v>
+        <v>126889641</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5372,34 +5372,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685363</v>
+        <v>685348</v>
       </c>
       <c r="R47" t="n">
-        <v>7107208</v>
+        <v>7106970</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5434,11 +5434,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5451,12 +5446,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5467,45 +5462,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126891169</v>
+        <v>126890631</v>
       </c>
       <c r="B48" t="n">
-        <v>91290</v>
+        <v>78681</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685394</v>
+        <v>685215</v>
       </c>
       <c r="R48" t="n">
-        <v>7107163</v>
+        <v>7107084</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5552,12 +5547,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5568,45 +5563,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126889641</v>
+        <v>126891169</v>
       </c>
       <c r="B49" t="n">
-        <v>78681</v>
+        <v>91290</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685348</v>
+        <v>685394</v>
       </c>
       <c r="R49" t="n">
-        <v>7106970</v>
+        <v>7107163</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5653,12 +5648,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5669,10 +5664,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890631</v>
+        <v>126890325</v>
       </c>
       <c r="B50" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5680,34 +5675,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685215</v>
+        <v>685363</v>
       </c>
       <c r="R50" t="n">
-        <v>7107084</v>
+        <v>7107208</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5742,6 +5737,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5770,45 +5770,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889632</v>
+        <v>126893459</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>105462</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685270</v>
+        <v>685327</v>
       </c>
       <c r="R51" t="n">
-        <v>7107186</v>
+        <v>7107177</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5843,24 +5843,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5871,7 +5877,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891181</v>
+        <v>126889632</v>
       </c>
       <c r="B52" t="n">
         <v>79014</v>
@@ -5902,14 +5908,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685396</v>
+        <v>685270</v>
       </c>
       <c r="R52" t="n">
-        <v>7106961</v>
+        <v>7107186</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5956,12 +5962,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5972,45 +5978,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893459</v>
+        <v>126890329</v>
       </c>
       <c r="B53" t="n">
-        <v>105462</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685327</v>
+        <v>685287</v>
       </c>
       <c r="R53" t="n">
-        <v>7107177</v>
+        <v>7107034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6047,7 +6053,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6056,19 +6062,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6079,10 +6084,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126877810</v>
+        <v>126891181</v>
       </c>
       <c r="B54" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6090,37 +6095,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fäbodtjärnen, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685341</v>
+        <v>685396</v>
       </c>
       <c r="R54" t="n">
-        <v>7107003</v>
+        <v>7106961</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6147,19 +6152,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6174,22 +6169,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893490</v>
+        <v>126890083</v>
       </c>
       <c r="B55" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6197,34 +6196,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685403</v>
+        <v>685222</v>
       </c>
       <c r="R55" t="n">
-        <v>7107099</v>
+        <v>7107061</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6265,19 +6264,33 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6288,10 +6301,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126890083</v>
+        <v>126890590</v>
       </c>
       <c r="B56" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6299,34 +6312,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685222</v>
+        <v>685371</v>
       </c>
       <c r="R56" t="n">
-        <v>7107061</v>
+        <v>7107135</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6370,30 +6383,15 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6404,10 +6402,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126890590</v>
+        <v>126877810</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6415,37 +6413,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Fäbodtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685371</v>
+        <v>685341</v>
       </c>
       <c r="R57" t="n">
-        <v>7107135</v>
+        <v>7107003</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6472,9 +6470,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6489,26 +6497,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126890329</v>
+        <v>126893490</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6516,21 +6520,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6540,10 +6544,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685287</v>
+        <v>685403</v>
       </c>
       <c r="R58" t="n">
-        <v>7107034</v>
+        <v>7107099</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6578,29 +6582,25 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7015,10 +7015,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890097</v>
+        <v>126890189</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7026,34 +7026,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685305</v>
+        <v>685256</v>
       </c>
       <c r="R63" t="n">
-        <v>7107176</v>
+        <v>7107175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7097,30 +7097,15 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7131,10 +7116,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890597</v>
+        <v>126890097</v>
       </c>
       <c r="B64" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7142,42 +7127,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685576</v>
+        <v>685305</v>
       </c>
       <c r="R64" t="n">
-        <v>7107009</v>
+        <v>7107176</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7221,15 +7198,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,10 +7232,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890189</v>
+        <v>126890597</v>
       </c>
       <c r="B65" t="n">
-        <v>80989</v>
+        <v>57817</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7251,34 +7243,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685256</v>
+        <v>685576</v>
       </c>
       <c r="R65" t="n">
-        <v>7107175</v>
+        <v>7107009</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7325,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7873,45 +7873,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126889640</v>
+        <v>126890617</v>
       </c>
       <c r="B71" t="n">
-        <v>78681</v>
+        <v>58027</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685311</v>
+        <v>685406</v>
       </c>
       <c r="R71" t="n">
-        <v>7107020</v>
+        <v>7107034</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7958,12 +7966,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7974,10 +7982,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126890595</v>
+        <v>126889640</v>
       </c>
       <c r="B72" t="n">
-        <v>91325</v>
+        <v>78681</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7985,34 +7993,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685417</v>
+        <v>685311</v>
       </c>
       <c r="R72" t="n">
-        <v>7107135</v>
+        <v>7107020</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8059,12 +8067,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8075,32 +8083,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126890157</v>
+        <v>126890173</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>91486</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8110,10 +8118,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685265</v>
+        <v>685398</v>
       </c>
       <c r="R73" t="n">
-        <v>7107114</v>
+        <v>7106958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8176,10 +8184,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890197</v>
+        <v>126890595</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8187,34 +8195,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685263</v>
+        <v>685417</v>
       </c>
       <c r="R74" t="n">
-        <v>7107013</v>
+        <v>7107135</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8249,11 +8257,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8266,12 +8269,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8282,32 +8285,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890173</v>
+        <v>126890157</v>
       </c>
       <c r="B75" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8317,10 +8320,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685398</v>
+        <v>685265</v>
       </c>
       <c r="R75" t="n">
-        <v>7106958</v>
+        <v>7107114</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8372,7 +8375,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8383,53 +8386,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890617</v>
+        <v>126890197</v>
       </c>
       <c r="B76" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685406</v>
+        <v>685263</v>
       </c>
       <c r="R76" t="n">
-        <v>7107034</v>
+        <v>7107013</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8464,6 +8459,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8476,12 +8476,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8608,10 +8608,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126890102</v>
+        <v>126891642</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8619,39 +8619,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685393</v>
+        <v>685361</v>
       </c>
       <c r="R78" t="n">
-        <v>7107081</v>
+        <v>7107114</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8686,6 +8681,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8698,12 +8698,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8714,10 +8714,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126890080</v>
+        <v>126893466</v>
       </c>
       <c r="B79" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8725,39 +8725,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685217</v>
+        <v>685256</v>
       </c>
       <c r="R79" t="n">
-        <v>7107067</v>
+        <v>7107043</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8792,24 +8787,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8820,50 +8821,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890094</v>
+        <v>126890588</v>
       </c>
       <c r="B80" t="n">
-        <v>57479</v>
+        <v>79632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102976</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685274</v>
+        <v>685418</v>
       </c>
       <c r="R80" t="n">
-        <v>7107182</v>
+        <v>7106975</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8910,12 +8906,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8926,10 +8922,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126891642</v>
+        <v>126890102</v>
       </c>
       <c r="B81" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,34 +8933,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685361</v>
+        <v>685393</v>
       </c>
       <c r="R81" t="n">
-        <v>7107114</v>
+        <v>7107081</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8999,11 +9000,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9016,12 +9012,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9032,10 +9028,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126893466</v>
+        <v>126890080</v>
       </c>
       <c r="B82" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9043,34 +9039,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685256</v>
+        <v>685217</v>
       </c>
       <c r="R82" t="n">
-        <v>7107043</v>
+        <v>7107067</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9105,30 +9106,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9139,45 +9134,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890588</v>
+        <v>126890094</v>
       </c>
       <c r="B83" t="n">
-        <v>79632</v>
+        <v>57479</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>102976</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685418</v>
+        <v>685274</v>
       </c>
       <c r="R83" t="n">
-        <v>7106975</v>
+        <v>7107182</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9224,12 +9224,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9876,10 +9876,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126891632</v>
+        <v>126890625</v>
       </c>
       <c r="B90" t="n">
-        <v>57654</v>
+        <v>91343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9887,38 +9887,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685370</v>
+        <v>685539</v>
       </c>
       <c r="R90" t="n">
-        <v>7107190</v>
+        <v>7107056</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9953,11 +9949,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Bohål i gran. Långt ner.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9970,12 +9961,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9986,10 +9977,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126890619</v>
+        <v>126890190</v>
       </c>
       <c r="B91" t="n">
-        <v>78772</v>
+        <v>80989</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9997,34 +9988,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685146</v>
+        <v>685223</v>
       </c>
       <c r="R91" t="n">
-        <v>7107092</v>
+        <v>7107071</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10071,12 +10062,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10087,10 +10078,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126890190</v>
+        <v>126893493</v>
       </c>
       <c r="B92" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,34 +10089,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685223</v>
+        <v>685266</v>
       </c>
       <c r="R92" t="n">
-        <v>7107071</v>
+        <v>7107184</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10172,12 +10163,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10188,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890099</v>
+        <v>126890628</v>
       </c>
       <c r="B93" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10199,34 +10190,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685420</v>
+        <v>685371</v>
       </c>
       <c r="R93" t="n">
-        <v>7107121</v>
+        <v>7107135</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10270,30 +10261,15 @@
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10304,10 +10280,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893458</v>
+        <v>126890619</v>
       </c>
       <c r="B94" t="n">
-        <v>57817</v>
+        <v>78772</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10315,34 +10291,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685383</v>
+        <v>685146</v>
       </c>
       <c r="R94" t="n">
-        <v>7107114</v>
+        <v>7107092</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10377,11 +10353,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10394,12 +10365,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10410,45 +10381,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890178</v>
+        <v>126890099</v>
       </c>
       <c r="B95" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685495</v>
+        <v>685420</v>
       </c>
       <c r="R95" t="n">
-        <v>7107045</v>
+        <v>7107121</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10492,15 +10463,30 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10511,10 +10497,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890628</v>
+        <v>126891632</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10522,34 +10508,38 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685371</v>
+        <v>685370</v>
       </c>
       <c r="R96" t="n">
-        <v>7107135</v>
+        <v>7107190</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,6 +10574,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10596,12 +10591,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10612,45 +10607,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893493</v>
+        <v>126890178</v>
       </c>
       <c r="B97" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685266</v>
+        <v>685495</v>
       </c>
       <c r="R97" t="n">
-        <v>7107184</v>
+        <v>7107045</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10697,12 +10692,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10713,10 +10708,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126890625</v>
+        <v>126893458</v>
       </c>
       <c r="B98" t="n">
-        <v>91343</v>
+        <v>57817</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10724,34 +10719,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685539</v>
+        <v>685383</v>
       </c>
       <c r="R98" t="n">
-        <v>7107056</v>
+        <v>7107114</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10786,6 +10781,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10798,12 +10798,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890614</v>
+        <v>126890149</v>
       </c>
       <c r="B99" t="n">
-        <v>78773</v>
+        <v>91343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,34 +10825,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685368</v>
+        <v>685396</v>
       </c>
       <c r="R99" t="n">
-        <v>7107109</v>
+        <v>7107168</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10899,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890184</v>
+        <v>126890155</v>
       </c>
       <c r="B100" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10926,21 +10926,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685257</v>
+        <v>685312</v>
       </c>
       <c r="R100" t="n">
-        <v>7107113</v>
+        <v>7107169</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11016,7 +11016,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126890155</v>
+        <v>126890323</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11047,14 +11047,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685312</v>
+        <v>685393</v>
       </c>
       <c r="R101" t="n">
-        <v>7107169</v>
+        <v>7106997</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11089,6 +11089,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Mycket i gran</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11101,12 +11106,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11117,7 +11122,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126890323</v>
+        <v>126893494</v>
       </c>
       <c r="B102" t="n">
         <v>79014</v>
@@ -11152,10 +11157,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685393</v>
+        <v>685374</v>
       </c>
       <c r="R102" t="n">
-        <v>7106997</v>
+        <v>7106951</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11190,11 +11195,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Mycket i gran</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,7 +11223,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126893494</v>
+        <v>126889630</v>
       </c>
       <c r="B103" t="n">
         <v>79014</v>
@@ -11254,14 +11254,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685374</v>
+        <v>685385</v>
       </c>
       <c r="R103" t="n">
-        <v>7106951</v>
+        <v>7106995</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126889630</v>
+        <v>126890614</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,34 +11335,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685385</v>
+        <v>685368</v>
       </c>
       <c r="R104" t="n">
-        <v>7106995</v>
+        <v>7107109</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11409,12 +11409,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126890149</v>
+        <v>126890184</v>
       </c>
       <c r="B105" t="n">
-        <v>91343</v>
+        <v>78773</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11460,10 +11460,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685396</v>
+        <v>685257</v>
       </c>
       <c r="R105" t="n">
-        <v>7107168</v>
+        <v>7107113</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126890589</v>
+        <v>126890093</v>
       </c>
       <c r="B106" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11537,34 +11537,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685289</v>
+        <v>685268</v>
       </c>
       <c r="R106" t="n">
-        <v>7107194</v>
+        <v>7107183</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11608,15 +11608,30 @@
       <c r="AG106" t="b">
         <v>0</v>
       </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11627,10 +11642,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126890093</v>
+        <v>126890633</v>
       </c>
       <c r="B107" t="n">
-        <v>80989</v>
+        <v>75130</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11638,34 +11653,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685268</v>
+        <v>685311</v>
       </c>
       <c r="R107" t="n">
-        <v>7107183</v>
+        <v>7107013</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11709,30 +11724,15 @@
       <c r="AG107" t="b">
         <v>0</v>
       </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11743,45 +11743,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126890633</v>
+        <v>126890161</v>
       </c>
       <c r="B108" t="n">
-        <v>75130</v>
+        <v>91290</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685311</v>
+        <v>685360</v>
       </c>
       <c r="R108" t="n">
-        <v>7107013</v>
+        <v>7107179</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11816,6 +11816,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11828,12 +11833,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11844,7 +11849,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126890089</v>
+        <v>126891176</v>
       </c>
       <c r="B109" t="n">
         <v>79014</v>
@@ -11875,14 +11880,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685254</v>
+        <v>685352</v>
       </c>
       <c r="R109" t="n">
-        <v>7107171</v>
+        <v>7107016</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11929,12 +11934,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11945,45 +11950,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126890161</v>
+        <v>126890327</v>
       </c>
       <c r="B110" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685360</v>
+        <v>685267</v>
       </c>
       <c r="R110" t="n">
-        <v>7107179</v>
+        <v>7107149</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12020,7 +12025,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Artnamn</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12035,12 +12040,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12051,7 +12056,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126890327</v>
+        <v>126890089</v>
       </c>
       <c r="B111" t="n">
         <v>79014</v>
@@ -12082,14 +12087,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685267</v>
+        <v>685254</v>
       </c>
       <c r="R111" t="n">
-        <v>7107149</v>
+        <v>7107171</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12124,11 +12129,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12141,12 +12141,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12157,7 +12157,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893465</v>
+        <v>126891177</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12188,14 +12188,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685211</v>
+        <v>685232</v>
       </c>
       <c r="R112" t="n">
-        <v>7107147</v>
+        <v>7107114</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12230,11 +12230,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12247,12 +12242,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12263,7 +12258,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126891176</v>
+        <v>126893465</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12294,14 +12289,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685352</v>
+        <v>685211</v>
       </c>
       <c r="R113" t="n">
-        <v>7107016</v>
+        <v>7107147</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12336,6 +12331,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12348,12 +12348,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12364,10 +12364,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126891177</v>
+        <v>126890589</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12375,34 +12375,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685232</v>
+        <v>685289</v>
       </c>
       <c r="R114" t="n">
-        <v>7107114</v>
+        <v>7107194</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12449,12 +12449,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12672,45 +12672,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126890608</v>
+        <v>126891631</v>
       </c>
       <c r="B117" t="n">
-        <v>79038</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685410</v>
+        <v>685262</v>
       </c>
       <c r="R117" t="n">
-        <v>7106989</v>
+        <v>7107166</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12745,6 +12749,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12757,12 +12766,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12773,7 +12782,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126890073</v>
+        <v>126891179</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12804,14 +12813,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685306</v>
+        <v>685268</v>
       </c>
       <c r="R118" t="n">
-        <v>7107003</v>
+        <v>7107012</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12858,12 +12867,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12874,7 +12883,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126891179</v>
+        <v>126890073</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12905,14 +12914,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685268</v>
+        <v>685306</v>
       </c>
       <c r="R119" t="n">
-        <v>7107012</v>
+        <v>7107003</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12959,12 +12968,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12975,49 +12984,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126891631</v>
+        <v>126890608</v>
       </c>
       <c r="B120" t="n">
-        <v>57657</v>
+        <v>79038</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685262</v>
+        <v>685410</v>
       </c>
       <c r="R120" t="n">
-        <v>7107166</v>
+        <v>7106989</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13052,11 +13057,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13069,12 +13069,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13085,7 +13085,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126890158</v>
+        <v>126889634</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13116,14 +13116,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685225</v>
+        <v>685358</v>
       </c>
       <c r="R121" t="n">
-        <v>7107113</v>
+        <v>7106974</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13170,12 +13170,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13287,7 +13287,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126889634</v>
+        <v>126890158</v>
       </c>
       <c r="B123" t="n">
         <v>79014</v>
@@ -13318,14 +13318,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685358</v>
+        <v>685225</v>
       </c>
       <c r="R123" t="n">
-        <v>7106974</v>
+        <v>7107113</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13372,12 +13372,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13388,10 +13388,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126890086</v>
+        <v>126893491</v>
       </c>
       <c r="B124" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13399,34 +13399,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685221</v>
+        <v>685369</v>
       </c>
       <c r="R124" t="n">
-        <v>7107115</v>
+        <v>7107086</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13470,30 +13470,15 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13504,10 +13489,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893491</v>
+        <v>126890086</v>
       </c>
       <c r="B125" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13515,34 +13500,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685369</v>
+        <v>685221</v>
       </c>
       <c r="R125" t="n">
-        <v>7107086</v>
+        <v>7107115</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13586,15 +13571,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13929,7 +13929,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126890176</v>
+        <v>126889626</v>
       </c>
       <c r="B129" t="n">
         <v>79014</v>
@@ -13958,16 +13958,23 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685413</v>
+        <v>685337</v>
       </c>
       <c r="R129" t="n">
-        <v>7107035</v>
+        <v>7107187</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14008,18 +14015,19 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14030,7 +14038,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126890326</v>
+        <v>126889631</v>
       </c>
       <c r="B130" t="n">
         <v>79014</v>
@@ -14061,14 +14069,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685271</v>
+        <v>685348</v>
       </c>
       <c r="R130" t="n">
-        <v>7107170</v>
+        <v>7107202</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14103,11 +14111,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14120,12 +14123,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14136,45 +14139,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126889639</v>
+        <v>126890326</v>
       </c>
       <c r="B131" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685328</v>
+        <v>685271</v>
       </c>
       <c r="R131" t="n">
-        <v>7107189</v>
+        <v>7107170</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14209,6 +14212,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -14221,12 +14229,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14237,45 +14245,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126889638</v>
+        <v>126890176</v>
       </c>
       <c r="B132" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685366</v>
+        <v>685413</v>
       </c>
       <c r="R132" t="n">
-        <v>7107208</v>
+        <v>7107035</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14322,12 +14330,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14338,52 +14346,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126889626</v>
+        <v>126889639</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685337</v>
+        <v>685328</v>
       </c>
       <c r="R133" t="n">
-        <v>7107187</v>
+        <v>7107189</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14424,7 +14425,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14447,32 +14447,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126889631</v>
+        <v>126889638</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685348</v>
+        <v>685366</v>
       </c>
       <c r="R134" t="n">
-        <v>7107202</v>
+        <v>7107208</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14957,7 +14957,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126890324</v>
+        <v>126890174</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -14988,14 +14988,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685394</v>
+        <v>685415</v>
       </c>
       <c r="R139" t="n">
-        <v>7107061</v>
+        <v>7107015</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15030,11 +15030,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15047,12 +15042,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15063,10 +15058,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126889620</v>
+        <v>126890324</v>
       </c>
       <c r="B140" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15074,34 +15069,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685391</v>
+        <v>685394</v>
       </c>
       <c r="R140" t="n">
-        <v>7107082</v>
+        <v>7107061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15136,6 +15131,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15148,12 +15148,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15164,7 +15164,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126890593</v>
+        <v>126889620</v>
       </c>
       <c r="B141" t="n">
         <v>79603</v>
@@ -15195,14 +15195,14 @@
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685219</v>
+        <v>685391</v>
       </c>
       <c r="R141" t="n">
-        <v>7107117</v>
+        <v>7107082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15249,12 +15249,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15265,10 +15265,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126890174</v>
+        <v>126890593</v>
       </c>
       <c r="B142" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15276,34 +15276,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685415</v>
+        <v>685219</v>
       </c>
       <c r="R142" t="n">
-        <v>7107015</v>
+        <v>7107117</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15366,10 +15366,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126890622</v>
+        <v>126890162</v>
       </c>
       <c r="B143" t="n">
-        <v>78772</v>
+        <v>91325</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15377,34 +15377,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685368</v>
+        <v>685401</v>
       </c>
       <c r="R143" t="n">
-        <v>7107109</v>
+        <v>7107105</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15467,10 +15467,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126890621</v>
+        <v>126891180</v>
       </c>
       <c r="B144" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15478,34 +15478,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685370</v>
+        <v>685372</v>
       </c>
       <c r="R144" t="n">
-        <v>7107120</v>
+        <v>7106948</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15552,12 +15552,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126891180</v>
+        <v>126890622</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15680,34 +15680,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685372</v>
+        <v>685368</v>
       </c>
       <c r="R146" t="n">
-        <v>7106948</v>
+        <v>7107109</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15770,10 +15770,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126891638</v>
+        <v>126890621</v>
       </c>
       <c r="B147" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15781,34 +15781,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685363</v>
+        <v>685370</v>
       </c>
       <c r="R147" t="n">
-        <v>7107112</v>
+        <v>7107120</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15855,12 +15855,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15871,10 +15871,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126890162</v>
+        <v>126891638</v>
       </c>
       <c r="B148" t="n">
-        <v>91325</v>
+        <v>78773</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15882,34 +15882,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685401</v>
+        <v>685363</v>
       </c>
       <c r="R148" t="n">
-        <v>7107105</v>
+        <v>7107112</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15956,12 +15956,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126890591</v>
+        <v>126890606</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685370</v>
+        <v>685377</v>
       </c>
       <c r="R2" t="n">
-        <v>7107120</v>
+        <v>7107099</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890606</v>
+        <v>126891182</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685377</v>
+        <v>685327</v>
       </c>
       <c r="R3" t="n">
-        <v>7107099</v>
+        <v>7107186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,18 +863,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,7 +886,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126891648</v>
+        <v>126893460</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -908,14 +917,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685260</v>
+        <v>685477</v>
       </c>
       <c r="R4" t="n">
-        <v>7107165</v>
+        <v>7107122</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +961,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På späd gran</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,12 +976,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -983,7 +992,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890629</v>
+        <v>126891648</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1014,14 +1023,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685283</v>
+        <v>685260</v>
       </c>
       <c r="R5" t="n">
-        <v>7107035</v>
+        <v>7107165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1065,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På späd gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1068,12 +1082,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1084,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126893460</v>
+        <v>126890629</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1115,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685477</v>
+        <v>685283</v>
       </c>
       <c r="R6" t="n">
-        <v>7107122</v>
+        <v>7107035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1171,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,12 +1183,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1296,53 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126891182</v>
+        <v>126890591</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685327</v>
+        <v>685370</v>
       </c>
       <c r="R8" t="n">
-        <v>7107186</v>
+        <v>7107120</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,19 +1384,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890098</v>
+        <v>126890156</v>
       </c>
       <c r="B24" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,34 +2993,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685407</v>
+        <v>685267</v>
       </c>
       <c r="R24" t="n">
-        <v>7107134</v>
+        <v>7107114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,30 +3064,15 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3098,7 +3083,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890156</v>
+        <v>126890328</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3129,14 +3114,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685267</v>
+        <v>685268</v>
       </c>
       <c r="R25" t="n">
-        <v>7107114</v>
+        <v>7107110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,12 +3168,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3199,10 +3184,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890328</v>
+        <v>126890098</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,34 +3195,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685268</v>
+        <v>685407</v>
       </c>
       <c r="R26" t="n">
-        <v>7107110</v>
+        <v>7107134</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,15 +3266,30 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3704,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126891394</v>
+        <v>126890146</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>91798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685267</v>
+        <v>685217</v>
       </c>
       <c r="R31" t="n">
-        <v>7107032</v>
+        <v>7107070</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,12 +3789,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3805,10 +3805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890146</v>
+        <v>126890627</v>
       </c>
       <c r="B32" t="n">
-        <v>91798</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3816,34 +3816,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685217</v>
+        <v>685410</v>
       </c>
       <c r="R32" t="n">
-        <v>7107070</v>
+        <v>7106989</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,12 +3890,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3906,7 +3906,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890627</v>
+        <v>126890081</v>
       </c>
       <c r="B33" t="n">
         <v>79014</v>
@@ -3937,14 +3937,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685410</v>
+        <v>685215</v>
       </c>
       <c r="R33" t="n">
-        <v>7106989</v>
+        <v>7107071</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3991,12 +3991,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4007,7 +4007,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126890081</v>
+        <v>126890103</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685215</v>
+        <v>685370</v>
       </c>
       <c r="R34" t="n">
-        <v>7107071</v>
+        <v>7107029</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4108,10 +4108,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890103</v>
+        <v>126891394</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4119,34 +4119,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685370</v>
+        <v>685267</v>
       </c>
       <c r="R35" t="n">
-        <v>7107029</v>
+        <v>7107032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4193,12 +4193,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126891393</v>
+        <v>126890189</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685263</v>
+        <v>685256</v>
       </c>
       <c r="R59" t="n">
-        <v>7107150</v>
+        <v>7107175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6696,12 +6696,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6712,10 +6712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890586</v>
+        <v>126890097</v>
       </c>
       <c r="B60" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6723,34 +6723,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685419</v>
+        <v>685305</v>
       </c>
       <c r="R60" t="n">
-        <v>7107080</v>
+        <v>7107176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6794,15 +6794,30 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6813,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890618</v>
+        <v>126890597</v>
       </c>
       <c r="B61" t="n">
-        <v>78772</v>
+        <v>57817</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6824,34 +6839,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685398</v>
+        <v>685576</v>
       </c>
       <c r="R61" t="n">
-        <v>7106998</v>
+        <v>7107009</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6914,10 +6937,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890592</v>
+        <v>126890185</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6925,34 +6948,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685368</v>
+        <v>685259</v>
       </c>
       <c r="R62" t="n">
-        <v>7107109</v>
+        <v>7107105</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6999,12 +7022,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7015,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890189</v>
+        <v>126891174</v>
       </c>
       <c r="B63" t="n">
-        <v>80989</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7026,34 +7049,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685256</v>
+        <v>685430</v>
       </c>
       <c r="R63" t="n">
-        <v>7107175</v>
+        <v>7106963</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7100,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7116,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890097</v>
+        <v>126891393</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7127,34 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685305</v>
+        <v>685263</v>
       </c>
       <c r="R64" t="n">
-        <v>7107176</v>
+        <v>7107150</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7198,30 +7221,15 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7232,10 +7240,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890597</v>
+        <v>126890586</v>
       </c>
       <c r="B65" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7243,42 +7251,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685576</v>
+        <v>685419</v>
       </c>
       <c r="R65" t="n">
-        <v>7107009</v>
+        <v>7107080</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890185</v>
+        <v>126890618</v>
       </c>
       <c r="B66" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685259</v>
+        <v>685398</v>
       </c>
       <c r="R66" t="n">
-        <v>7107105</v>
+        <v>7106998</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126891174</v>
+        <v>126890592</v>
       </c>
       <c r="B67" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685430</v>
+        <v>685368</v>
       </c>
       <c r="R67" t="n">
-        <v>7106963</v>
+        <v>7107109</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -9977,10 +9977,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126890190</v>
+        <v>126893493</v>
       </c>
       <c r="B91" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9988,34 +9988,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685223</v>
+        <v>685266</v>
       </c>
       <c r="R91" t="n">
-        <v>7107071</v>
+        <v>7107184</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10062,12 +10062,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10078,7 +10078,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893493</v>
+        <v>126890628</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -10109,14 +10109,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685266</v>
+        <v>685371</v>
       </c>
       <c r="R92" t="n">
-        <v>7107184</v>
+        <v>7107135</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10163,12 +10163,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10179,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890628</v>
+        <v>126891632</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10190,34 +10190,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685371</v>
+        <v>685370</v>
       </c>
       <c r="R93" t="n">
-        <v>7107135</v>
+        <v>7107190</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10252,6 +10256,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10264,12 +10273,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10280,10 +10289,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890619</v>
+        <v>126893458</v>
       </c>
       <c r="B94" t="n">
-        <v>78772</v>
+        <v>57817</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10291,34 +10300,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685146</v>
+        <v>685383</v>
       </c>
       <c r="R94" t="n">
-        <v>7107092</v>
+        <v>7107114</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10353,6 +10362,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10365,12 +10379,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10381,45 +10395,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890099</v>
+        <v>126890178</v>
       </c>
       <c r="B95" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685420</v>
+        <v>685495</v>
       </c>
       <c r="R95" t="n">
-        <v>7107121</v>
+        <v>7107045</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10463,30 +10477,15 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10497,10 +10496,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126891632</v>
+        <v>126890190</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>80989</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10508,38 +10507,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685370</v>
+        <v>685223</v>
       </c>
       <c r="R96" t="n">
-        <v>7107190</v>
+        <v>7107071</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10574,11 +10569,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Bohål i gran. Långt ner.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10591,12 +10581,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10607,45 +10597,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126890178</v>
+        <v>126890619</v>
       </c>
       <c r="B97" t="n">
-        <v>98359</v>
+        <v>78772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685495</v>
+        <v>685146</v>
       </c>
       <c r="R97" t="n">
-        <v>7107045</v>
+        <v>7107092</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10692,12 +10682,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10708,10 +10698,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893458</v>
+        <v>126890099</v>
       </c>
       <c r="B98" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10719,34 +10709,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685383</v>
+        <v>685420</v>
       </c>
       <c r="R98" t="n">
-        <v>7107114</v>
+        <v>7107121</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10781,11 +10771,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10794,16 +10779,31 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890149</v>
+        <v>126890155</v>
       </c>
       <c r="B99" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,21 +10825,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10849,10 +10849,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685396</v>
+        <v>685312</v>
       </c>
       <c r="R99" t="n">
-        <v>7107168</v>
+        <v>7107169</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10915,7 +10915,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890155</v>
+        <v>126890323</v>
       </c>
       <c r="B100" t="n">
         <v>79014</v>
@@ -10946,14 +10946,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685312</v>
+        <v>685393</v>
       </c>
       <c r="R100" t="n">
-        <v>7107169</v>
+        <v>7106997</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10988,6 +10988,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Mycket i gran</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11000,12 +11005,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11016,7 +11021,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126890323</v>
+        <v>126893494</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11051,10 +11056,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685393</v>
+        <v>685374</v>
       </c>
       <c r="R101" t="n">
-        <v>7106997</v>
+        <v>7106951</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11089,11 +11094,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Mycket i gran</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11106,12 +11106,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11122,7 +11122,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126893494</v>
+        <v>126889630</v>
       </c>
       <c r="B102" t="n">
         <v>79014</v>
@@ -11153,14 +11153,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685374</v>
+        <v>685385</v>
       </c>
       <c r="R102" t="n">
-        <v>7106951</v>
+        <v>7106995</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126889630</v>
+        <v>126890149</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11234,34 +11234,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685385</v>
+        <v>685396</v>
       </c>
       <c r="R103" t="n">
-        <v>7106995</v>
+        <v>7107168</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12672,10 +12672,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126891631</v>
+        <v>126891179</v>
       </c>
       <c r="B117" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12683,38 +12683,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685262</v>
+        <v>685268</v>
       </c>
       <c r="R117" t="n">
-        <v>7107166</v>
+        <v>7107012</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12749,11 +12745,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12766,12 +12757,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12782,7 +12773,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126891179</v>
+        <v>126890073</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12813,14 +12804,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685268</v>
+        <v>685306</v>
       </c>
       <c r="R118" t="n">
-        <v>7107012</v>
+        <v>7107003</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12867,12 +12858,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12883,45 +12874,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126890073</v>
+        <v>126890608</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685306</v>
+        <v>685410</v>
       </c>
       <c r="R119" t="n">
-        <v>7107003</v>
+        <v>7106989</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12968,12 +12959,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12984,45 +12975,49 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126890608</v>
+        <v>126891631</v>
       </c>
       <c r="B120" t="n">
-        <v>79038</v>
+        <v>57657</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685410</v>
+        <v>685262</v>
       </c>
       <c r="R120" t="n">
-        <v>7106989</v>
+        <v>7107166</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13057,6 +13052,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13069,12 +13069,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13085,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126889634</v>
+        <v>126890086</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13096,34 +13096,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685358</v>
+        <v>685221</v>
       </c>
       <c r="R121" t="n">
-        <v>7106974</v>
+        <v>7107115</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13167,15 +13167,30 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13186,7 +13201,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126890154</v>
+        <v>126889634</v>
       </c>
       <c r="B122" t="n">
         <v>79014</v>
@@ -13217,14 +13232,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685361</v>
+        <v>685358</v>
       </c>
       <c r="R122" t="n">
-        <v>7107207</v>
+        <v>7106974</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13271,12 +13286,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13287,7 +13302,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126890158</v>
+        <v>126890154</v>
       </c>
       <c r="B123" t="n">
         <v>79014</v>
@@ -13322,10 +13337,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685225</v>
+        <v>685361</v>
       </c>
       <c r="R123" t="n">
-        <v>7107113</v>
+        <v>7107207</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13388,10 +13403,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893491</v>
+        <v>126890158</v>
       </c>
       <c r="B124" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13399,34 +13414,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685369</v>
+        <v>685225</v>
       </c>
       <c r="R124" t="n">
-        <v>7107086</v>
+        <v>7107113</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13473,12 +13488,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13489,10 +13504,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126890086</v>
+        <v>126893491</v>
       </c>
       <c r="B125" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13500,34 +13515,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685221</v>
+        <v>685369</v>
       </c>
       <c r="R125" t="n">
-        <v>7107115</v>
+        <v>7107086</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13571,30 +13586,15 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13605,45 +13605,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126890085</v>
+        <v>126890599</v>
       </c>
       <c r="B126" t="n">
-        <v>80989</v>
+        <v>98463</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1049</v>
+        <v>221952</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685222</v>
+        <v>685411</v>
       </c>
       <c r="R126" t="n">
-        <v>7107058</v>
+        <v>7107223</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13687,30 +13687,15 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13721,10 +13706,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126893461</v>
+        <v>126889622</v>
       </c>
       <c r="B127" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13732,34 +13717,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685338</v>
+        <v>685254</v>
       </c>
       <c r="R127" t="n">
-        <v>7107092</v>
+        <v>7107050</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13794,30 +13779,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13828,10 +13807,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126890159</v>
+        <v>126890613</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13839,34 +13818,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685238</v>
+        <v>685370</v>
       </c>
       <c r="R128" t="n">
-        <v>7107094</v>
+        <v>7107120</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13913,12 +13892,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13929,10 +13908,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126889626</v>
+        <v>126893468</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13940,41 +13919,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685337</v>
+        <v>685403</v>
       </c>
       <c r="R129" t="n">
-        <v>7107187</v>
+        <v>7107031</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14009,25 +13981,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14038,7 +14014,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126889631</v>
+        <v>126890159</v>
       </c>
       <c r="B130" t="n">
         <v>79014</v>
@@ -14069,14 +14045,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685348</v>
+        <v>685238</v>
       </c>
       <c r="R130" t="n">
-        <v>7107202</v>
+        <v>7107094</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14123,12 +14099,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14139,7 +14115,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126890326</v>
+        <v>126889626</v>
       </c>
       <c r="B131" t="n">
         <v>79014</v>
@@ -14168,16 +14144,23 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685271</v>
+        <v>685337</v>
       </c>
       <c r="R131" t="n">
-        <v>7107170</v>
+        <v>7107187</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14212,29 +14195,25 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14245,7 +14224,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126890176</v>
+        <v>126889631</v>
       </c>
       <c r="B132" t="n">
         <v>79014</v>
@@ -14276,14 +14255,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685413</v>
+        <v>685348</v>
       </c>
       <c r="R132" t="n">
-        <v>7107035</v>
+        <v>7107202</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14330,12 +14309,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14346,45 +14325,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126889639</v>
+        <v>126890326</v>
       </c>
       <c r="B133" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685328</v>
+        <v>685271</v>
       </c>
       <c r="R133" t="n">
-        <v>7107189</v>
+        <v>7107170</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14419,6 +14398,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14431,12 +14415,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14447,45 +14431,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126889638</v>
+        <v>126890176</v>
       </c>
       <c r="B134" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685366</v>
+        <v>685413</v>
       </c>
       <c r="R134" t="n">
-        <v>7107208</v>
+        <v>7107035</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14532,12 +14516,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14548,10 +14532,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126890599</v>
+        <v>126889639</v>
       </c>
       <c r="B135" t="n">
-        <v>98463</v>
+        <v>98359</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14559,34 +14543,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685411</v>
+        <v>685328</v>
       </c>
       <c r="R135" t="n">
-        <v>7107223</v>
+        <v>7107189</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14633,12 +14617,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14649,32 +14633,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126889622</v>
+        <v>126889638</v>
       </c>
       <c r="B136" t="n">
-        <v>78773</v>
+        <v>98359</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14684,10 +14668,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685254</v>
+        <v>685366</v>
       </c>
       <c r="R136" t="n">
-        <v>7107050</v>
+        <v>7107208</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14750,10 +14734,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126890613</v>
+        <v>126890085</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>80989</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14761,34 +14745,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685370</v>
+        <v>685222</v>
       </c>
       <c r="R137" t="n">
-        <v>7107120</v>
+        <v>7107058</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14832,15 +14816,30 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14851,10 +14850,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126893468</v>
+        <v>126893461</v>
       </c>
       <c r="B138" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14862,21 +14861,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14886,10 +14885,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685403</v>
+        <v>685338</v>
       </c>
       <c r="R138" t="n">
-        <v>7107031</v>
+        <v>7107092</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14935,6 +14934,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14946,7 +14946,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -15467,7 +15467,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126891180</v>
+        <v>126890074</v>
       </c>
       <c r="B144" t="n">
         <v>79014</v>
@@ -15498,14 +15498,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685372</v>
+        <v>685303</v>
       </c>
       <c r="R144" t="n">
-        <v>7106948</v>
+        <v>7107030</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15552,12 +15552,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15568,7 +15568,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126890074</v>
+        <v>126891180</v>
       </c>
       <c r="B145" t="n">
         <v>79014</v>
@@ -15599,14 +15599,14 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685303</v>
+        <v>685372</v>
       </c>
       <c r="R145" t="n">
-        <v>7107030</v>
+        <v>7106948</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15653,12 +15653,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -776,53 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126891182</v>
+        <v>126891648</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685327</v>
+        <v>685260</v>
       </c>
       <c r="R3" t="n">
-        <v>7107186</v>
+        <v>7107165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,25 +849,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På späd gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -886,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893460</v>
+        <v>126890629</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -917,14 +913,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685477</v>
+        <v>685283</v>
       </c>
       <c r="R4" t="n">
-        <v>7107122</v>
+        <v>7107035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,11 +955,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -976,12 +967,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -992,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126891648</v>
+        <v>126890591</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,34 +994,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685260</v>
+        <v>685370</v>
       </c>
       <c r="R5" t="n">
-        <v>7107165</v>
+        <v>7107120</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,11 +1056,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På späd gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1082,12 +1068,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1098,7 +1084,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890629</v>
+        <v>126893460</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1129,14 +1115,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685283</v>
+        <v>685477</v>
       </c>
       <c r="R6" t="n">
-        <v>7107035</v>
+        <v>7107122</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,6 +1157,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1183,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1294,7 +1285,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1305,45 +1296,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126890591</v>
+        <v>126891182</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685370</v>
+        <v>685327</v>
       </c>
       <c r="R8" t="n">
-        <v>7107120</v>
+        <v>7107186</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,18 +1383,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126890148</v>
+        <v>126889633</v>
       </c>
       <c r="B10" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,34 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685419</v>
+        <v>685223</v>
       </c>
       <c r="R10" t="n">
-        <v>7107117</v>
+        <v>7107049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1597,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890092</v>
+        <v>126890071</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685268</v>
+        <v>685346</v>
       </c>
       <c r="R11" t="n">
-        <v>7107182</v>
+        <v>7106969</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890166</v>
+        <v>126890148</v>
       </c>
       <c r="B12" t="n">
-        <v>78773</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685415</v>
+        <v>685419</v>
       </c>
       <c r="R12" t="n">
-        <v>7107111</v>
+        <v>7107117</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1830,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890071</v>
+        <v>126890180</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,34 +1841,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685346</v>
+        <v>685259</v>
       </c>
       <c r="R13" t="n">
-        <v>7106969</v>
+        <v>7107109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1903,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1911,31 +1916,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1946,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126889633</v>
+        <v>126890100</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,34 +1947,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685223</v>
+        <v>685405</v>
       </c>
       <c r="R14" t="n">
-        <v>7107049</v>
+        <v>7107108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,15 +2018,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2047,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890180</v>
+        <v>126890191</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,21 +2063,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,7 +2087,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685259</v>
+        <v>685257</v>
       </c>
       <c r="R15" t="n">
         <v>7107109</v>
@@ -2118,11 +2123,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890100</v>
+        <v>126890587</v>
       </c>
       <c r="B16" t="n">
-        <v>75138</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685405</v>
+        <v>685398</v>
       </c>
       <c r="R16" t="n">
-        <v>7107108</v>
+        <v>7106998</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,30 +2235,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2269,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890191</v>
+        <v>126890166</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,21 +2265,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685257</v>
+        <v>685415</v>
       </c>
       <c r="R17" t="n">
-        <v>7107109</v>
+        <v>7107111</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890587</v>
+        <v>126890092</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,34 +2366,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685398</v>
+        <v>685268</v>
       </c>
       <c r="R18" t="n">
-        <v>7106998</v>
+        <v>7107182</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,15 +2437,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2471,45 +2471,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890082</v>
+        <v>126890200</v>
       </c>
       <c r="B19" t="n">
-        <v>92615</v>
+        <v>77992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685213</v>
+        <v>685218</v>
       </c>
       <c r="R19" t="n">
-        <v>7107071</v>
+        <v>7107060</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2556,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2780,45 +2780,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890200</v>
+        <v>126890630</v>
       </c>
       <c r="B22" t="n">
-        <v>77992</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685218</v>
+        <v>685421</v>
       </c>
       <c r="R22" t="n">
-        <v>7107060</v>
+        <v>7107205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,12 +2865,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2881,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126890630</v>
+        <v>126890082</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>92616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,34 +2892,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685421</v>
+        <v>685213</v>
       </c>
       <c r="R23" t="n">
-        <v>7107205</v>
+        <v>7107071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,12 +2966,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2982,7 +2982,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890156</v>
+        <v>126890101</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -3013,14 +3013,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685267</v>
+        <v>685405</v>
       </c>
       <c r="R24" t="n">
-        <v>7107114</v>
+        <v>7107108</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3067,12 +3067,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3083,7 +3083,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890328</v>
+        <v>126890156</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3114,14 +3114,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685268</v>
+        <v>685267</v>
       </c>
       <c r="R25" t="n">
-        <v>7107110</v>
+        <v>7107114</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3168,12 +3168,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3184,10 +3184,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890098</v>
+        <v>126890075</v>
       </c>
       <c r="B26" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,21 +3195,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685407</v>
+        <v>685334</v>
       </c>
       <c r="R26" t="n">
-        <v>7107134</v>
+        <v>7107003</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,21 +3265,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3300,7 +3285,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890101</v>
+        <v>126890328</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3331,14 +3316,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685405</v>
+        <v>685268</v>
       </c>
       <c r="R27" t="n">
-        <v>7107108</v>
+        <v>7107110</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3385,12 +3370,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3401,10 +3386,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890075</v>
+        <v>126890201</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,34 +3397,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685334</v>
+        <v>685214</v>
       </c>
       <c r="R28" t="n">
-        <v>7107003</v>
+        <v>7107061</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,12 +3471,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3502,10 +3487,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890201</v>
+        <v>126890098</v>
       </c>
       <c r="B29" t="n">
-        <v>78420</v>
+        <v>91326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,34 +3498,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685214</v>
+        <v>685407</v>
       </c>
       <c r="R29" t="n">
-        <v>7107061</v>
+        <v>7107134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,15 +3569,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3707,7 +3707,7 @@
         <v>126890146</v>
       </c>
       <c r="B31" t="n">
-        <v>91798</v>
+        <v>91799</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126891640</v>
+        <v>126890615</v>
       </c>
       <c r="B37" t="n">
-        <v>58027</v>
+        <v>80153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,42 +4329,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685539</v>
+        <v>685399</v>
       </c>
       <c r="R37" t="n">
-        <v>7107065</v>
+        <v>7107027</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4399,11 +4391,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4416,12 +4403,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4735,10 +4722,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890615</v>
+        <v>126891640</v>
       </c>
       <c r="B41" t="n">
-        <v>80153</v>
+        <v>58027</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4746,34 +4733,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685399</v>
+        <v>685539</v>
       </c>
       <c r="R41" t="n">
-        <v>7107027</v>
+        <v>7107065</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4808,6 +4803,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5361,45 +5361,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126889641</v>
+        <v>126891169</v>
       </c>
       <c r="B47" t="n">
-        <v>78681</v>
+        <v>91291</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685348</v>
+        <v>685394</v>
       </c>
       <c r="R47" t="n">
-        <v>7106970</v>
+        <v>7107163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5446,12 +5446,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890631</v>
+        <v>126890325</v>
       </c>
       <c r="B48" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5473,34 +5473,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685215</v>
+        <v>685363</v>
       </c>
       <c r="R48" t="n">
-        <v>7107084</v>
+        <v>7107208</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5535,6 +5535,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5547,12 +5552,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5563,45 +5568,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126891169</v>
+        <v>126890631</v>
       </c>
       <c r="B49" t="n">
-        <v>91290</v>
+        <v>78681</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685394</v>
+        <v>685215</v>
       </c>
       <c r="R49" t="n">
-        <v>7107163</v>
+        <v>7107084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5648,12 +5653,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5664,10 +5669,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890325</v>
+        <v>126889641</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5675,34 +5680,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685363</v>
+        <v>685348</v>
       </c>
       <c r="R50" t="n">
-        <v>7107208</v>
+        <v>7106970</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5737,11 +5742,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5773,7 +5773,7 @@
         <v>126893459</v>
       </c>
       <c r="B51" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890189</v>
+        <v>126890097</v>
       </c>
       <c r="B59" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,34 +6622,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685256</v>
+        <v>685305</v>
       </c>
       <c r="R59" t="n">
-        <v>7107175</v>
+        <v>7107176</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6693,15 +6693,30 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6712,10 +6727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890097</v>
+        <v>126890189</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6723,34 +6738,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685305</v>
+        <v>685256</v>
       </c>
       <c r="R60" t="n">
-        <v>7107176</v>
+        <v>7107175</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6794,30 +6809,15 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890185</v>
+        <v>126891393</v>
       </c>
       <c r="B62" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685259</v>
+        <v>685263</v>
       </c>
       <c r="R62" t="n">
-        <v>7107105</v>
+        <v>7107150</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7022,12 +7022,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7038,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126891174</v>
+        <v>126890586</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,34 +7049,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685430</v>
+        <v>685419</v>
       </c>
       <c r="R63" t="n">
-        <v>7106963</v>
+        <v>7107080</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126891393</v>
+        <v>126890618</v>
       </c>
       <c r="B64" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,34 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685263</v>
+        <v>685398</v>
       </c>
       <c r="R64" t="n">
-        <v>7107150</v>
+        <v>7106998</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,7 +7240,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890586</v>
+        <v>126890592</v>
       </c>
       <c r="B65" t="n">
         <v>79632</v>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685419</v>
+        <v>685368</v>
       </c>
       <c r="R65" t="n">
-        <v>7107080</v>
+        <v>7107109</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890618</v>
+        <v>126890185</v>
       </c>
       <c r="B66" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685398</v>
+        <v>685259</v>
       </c>
       <c r="R66" t="n">
-        <v>7106998</v>
+        <v>7107105</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126890592</v>
+        <v>126891174</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685368</v>
+        <v>685430</v>
       </c>
       <c r="R67" t="n">
-        <v>7107109</v>
+        <v>7106963</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7543,10 +7543,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126890620</v>
+        <v>126890157</v>
       </c>
       <c r="B68" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7554,34 +7554,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685161</v>
+        <v>685265</v>
       </c>
       <c r="R68" t="n">
-        <v>7107091</v>
+        <v>7107114</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,12 +7628,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7644,7 +7644,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890091</v>
+        <v>126890620</v>
       </c>
       <c r="B69" t="n">
         <v>78772</v>
@@ -7675,14 +7675,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685268</v>
+        <v>685161</v>
       </c>
       <c r="R69" t="n">
-        <v>7107185</v>
+        <v>7107091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7726,30 +7726,15 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7760,57 +7745,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890188</v>
+        <v>126890091</v>
       </c>
       <c r="B70" t="n">
-        <v>57761</v>
+        <v>78772</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685274</v>
+        <v>685268</v>
       </c>
       <c r="R70" t="n">
-        <v>7107181</v>
+        <v>7107185</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7854,15 +7827,30 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7873,53 +7861,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890617</v>
+        <v>126890197</v>
       </c>
       <c r="B71" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685406</v>
+        <v>685263</v>
       </c>
       <c r="R71" t="n">
-        <v>7107034</v>
+        <v>7107013</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7954,6 +7934,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7966,12 +7951,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7982,45 +7967,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126889640</v>
+        <v>126890173</v>
       </c>
       <c r="B72" t="n">
-        <v>78681</v>
+        <v>91487</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685311</v>
+        <v>685398</v>
       </c>
       <c r="R72" t="n">
-        <v>7107020</v>
+        <v>7106958</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8067,12 +8052,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8083,45 +8068,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126890173</v>
+        <v>126889640</v>
       </c>
       <c r="B73" t="n">
-        <v>91486</v>
+        <v>78681</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685398</v>
+        <v>685311</v>
       </c>
       <c r="R73" t="n">
-        <v>7106958</v>
+        <v>7107020</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8168,12 +8153,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8187,7 +8172,7 @@
         <v>126890595</v>
       </c>
       <c r="B74" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8285,45 +8270,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890157</v>
+        <v>126890188</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>57761</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685265</v>
+        <v>685274</v>
       </c>
       <c r="R75" t="n">
-        <v>7107114</v>
+        <v>7107181</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8375,7 +8372,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8386,45 +8383,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890197</v>
+        <v>126890617</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685263</v>
+        <v>685406</v>
       </c>
       <c r="R76" t="n">
-        <v>7107013</v>
+        <v>7107034</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8459,11 +8464,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8476,12 +8476,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8492,45 +8492,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890088</v>
+        <v>126891642</v>
       </c>
       <c r="B77" t="n">
-        <v>91290</v>
+        <v>78772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685251</v>
+        <v>685361</v>
       </c>
       <c r="R77" t="n">
-        <v>7107154</v>
+        <v>7107114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8565,6 +8565,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8573,31 +8578,16 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8608,7 +8598,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126891642</v>
+        <v>126893466</v>
       </c>
       <c r="B78" t="n">
         <v>78772</v>
@@ -8639,14 +8629,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685361</v>
+        <v>685256</v>
       </c>
       <c r="R78" t="n">
-        <v>7107114</v>
+        <v>7107043</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8683,7 +8673,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På kolad silverhögstubbe</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8692,18 +8682,19 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8714,10 +8705,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126893466</v>
+        <v>126890588</v>
       </c>
       <c r="B79" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8725,34 +8716,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685256</v>
+        <v>685418</v>
       </c>
       <c r="R79" t="n">
-        <v>7107043</v>
+        <v>7106975</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8787,30 +8778,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8821,45 +8806,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890588</v>
+        <v>126890094</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>57479</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>102976</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685418</v>
+        <v>685274</v>
       </c>
       <c r="R80" t="n">
-        <v>7106975</v>
+        <v>7107182</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8906,12 +8896,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8922,10 +8912,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890102</v>
+        <v>126890594</v>
       </c>
       <c r="B81" t="n">
-        <v>57657</v>
+        <v>79603</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8933,39 +8923,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685393</v>
+        <v>685372</v>
       </c>
       <c r="R81" t="n">
-        <v>7107081</v>
+        <v>7106953</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9012,12 +8997,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9028,7 +9013,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890080</v>
+        <v>126890102</v>
       </c>
       <c r="B82" t="n">
         <v>57657</v>
@@ -9059,7 +9044,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9068,10 +9053,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685217</v>
+        <v>685393</v>
       </c>
       <c r="R82" t="n">
-        <v>7107067</v>
+        <v>7107081</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9134,27 +9119,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890094</v>
+        <v>126890080</v>
       </c>
       <c r="B83" t="n">
-        <v>57479</v>
+        <v>57657</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9165,7 +9150,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9174,10 +9159,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685274</v>
+        <v>685217</v>
       </c>
       <c r="R83" t="n">
-        <v>7107182</v>
+        <v>7107067</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,7 +9214,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9240,45 +9225,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890594</v>
+        <v>126890088</v>
       </c>
       <c r="B84" t="n">
-        <v>79603</v>
+        <v>91291</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685372</v>
+        <v>685251</v>
       </c>
       <c r="R84" t="n">
-        <v>7106953</v>
+        <v>7107154</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9322,15 +9307,30 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9341,10 +9341,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890078</v>
+        <v>126890612</v>
       </c>
       <c r="B85" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9352,34 +9352,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685255</v>
+        <v>685371</v>
       </c>
       <c r="R85" t="n">
-        <v>7107048</v>
+        <v>7107135</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9423,30 +9423,15 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9457,32 +9442,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126890598</v>
+        <v>126890611</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9492,10 +9477,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685154</v>
+        <v>685418</v>
       </c>
       <c r="R86" t="n">
-        <v>7107066</v>
+        <v>7106975</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9674,32 +9659,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126890612</v>
+        <v>126890598</v>
       </c>
       <c r="B88" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9709,10 +9694,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685371</v>
+        <v>685154</v>
       </c>
       <c r="R88" t="n">
-        <v>7107135</v>
+        <v>7107066</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9775,10 +9760,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126890611</v>
+        <v>126890078</v>
       </c>
       <c r="B89" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9786,34 +9771,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685418</v>
+        <v>685255</v>
       </c>
       <c r="R89" t="n">
-        <v>7106975</v>
+        <v>7107048</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9857,15 +9842,30 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9876,45 +9876,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126890625</v>
+        <v>126890178</v>
       </c>
       <c r="B90" t="n">
-        <v>91343</v>
+        <v>98360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685539</v>
+        <v>685495</v>
       </c>
       <c r="R90" t="n">
-        <v>7107056</v>
+        <v>7107045</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9961,12 +9961,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9977,10 +9977,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126893493</v>
+        <v>126891632</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9988,34 +9988,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685266</v>
+        <v>685370</v>
       </c>
       <c r="R91" t="n">
-        <v>7107184</v>
+        <v>7107190</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10050,6 +10054,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10062,12 +10071,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10078,10 +10087,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126890628</v>
+        <v>126890190</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10089,34 +10098,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685371</v>
+        <v>685223</v>
       </c>
       <c r="R92" t="n">
-        <v>7107135</v>
+        <v>7107071</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10163,12 +10172,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10179,10 +10188,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126891632</v>
+        <v>126890625</v>
       </c>
       <c r="B93" t="n">
-        <v>57654</v>
+        <v>91344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10190,38 +10199,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685370</v>
+        <v>685539</v>
       </c>
       <c r="R93" t="n">
-        <v>7107190</v>
+        <v>7107056</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10256,11 +10261,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Bohål i gran. Långt ner.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10273,12 +10273,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10289,10 +10289,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893458</v>
+        <v>126893493</v>
       </c>
       <c r="B94" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10300,34 +10300,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685383</v>
+        <v>685266</v>
       </c>
       <c r="R94" t="n">
-        <v>7107114</v>
+        <v>7107184</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,11 +10362,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10379,12 +10374,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10395,45 +10390,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890178</v>
+        <v>126890628</v>
       </c>
       <c r="B95" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685495</v>
+        <v>685371</v>
       </c>
       <c r="R95" t="n">
-        <v>7107045</v>
+        <v>7107135</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10480,12 +10475,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10496,10 +10491,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890190</v>
+        <v>126890099</v>
       </c>
       <c r="B96" t="n">
-        <v>80989</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10507,34 +10502,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685223</v>
+        <v>685420</v>
       </c>
       <c r="R96" t="n">
-        <v>7107071</v>
+        <v>7107121</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10578,15 +10573,30 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10698,10 +10708,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126890099</v>
+        <v>126893458</v>
       </c>
       <c r="B98" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10709,34 +10719,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685420</v>
+        <v>685383</v>
       </c>
       <c r="R98" t="n">
-        <v>7107121</v>
+        <v>7107114</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10771,6 +10781,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10779,31 +10794,16 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890155</v>
+        <v>126890149</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,21 +10825,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10849,10 +10849,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685312</v>
+        <v>685396</v>
       </c>
       <c r="R99" t="n">
-        <v>7107169</v>
+        <v>7107168</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,7 +10915,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890323</v>
+        <v>126890155</v>
       </c>
       <c r="B100" t="n">
         <v>79014</v>
@@ -10946,14 +10946,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685393</v>
+        <v>685312</v>
       </c>
       <c r="R100" t="n">
-        <v>7106997</v>
+        <v>7107169</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10988,11 +10988,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Mycket i gran</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11005,12 +11000,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11021,7 +11016,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126893494</v>
+        <v>126890323</v>
       </c>
       <c r="B101" t="n">
         <v>79014</v>
@@ -11056,10 +11051,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685374</v>
+        <v>685393</v>
       </c>
       <c r="R101" t="n">
-        <v>7106951</v>
+        <v>7106997</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11094,6 +11089,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Mycket i gran</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11106,12 +11106,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11122,7 +11122,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126889630</v>
+        <v>126893494</v>
       </c>
       <c r="B102" t="n">
         <v>79014</v>
@@ -11153,14 +11153,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685385</v>
+        <v>685374</v>
       </c>
       <c r="R102" t="n">
-        <v>7106995</v>
+        <v>7106951</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126890149</v>
+        <v>126889630</v>
       </c>
       <c r="B103" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11234,34 +11234,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685396</v>
+        <v>685385</v>
       </c>
       <c r="R103" t="n">
-        <v>7107168</v>
+        <v>7106995</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11526,10 +11526,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126890093</v>
+        <v>126890317</v>
       </c>
       <c r="B106" t="n">
-        <v>80989</v>
+        <v>57657</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11537,34 +11537,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685268</v>
+        <v>685420</v>
       </c>
       <c r="R106" t="n">
-        <v>7107183</v>
+        <v>7107002</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11599,6 +11599,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färsk ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11607,31 +11612,16 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11642,45 +11632,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126890633</v>
+        <v>126890161</v>
       </c>
       <c r="B107" t="n">
-        <v>75130</v>
+        <v>91291</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685311</v>
+        <v>685360</v>
       </c>
       <c r="R107" t="n">
-        <v>7107013</v>
+        <v>7107179</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11715,6 +11705,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11727,12 +11722,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11743,45 +11738,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126890161</v>
+        <v>126891176</v>
       </c>
       <c r="B108" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685360</v>
+        <v>685352</v>
       </c>
       <c r="R108" t="n">
-        <v>7107179</v>
+        <v>7107016</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11816,11 +11811,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11833,12 +11823,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11849,7 +11839,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126891176</v>
+        <v>126890089</v>
       </c>
       <c r="B109" t="n">
         <v>79014</v>
@@ -11880,14 +11870,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685352</v>
+        <v>685254</v>
       </c>
       <c r="R109" t="n">
-        <v>7107016</v>
+        <v>7107171</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11934,12 +11924,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11950,7 +11940,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126890327</v>
+        <v>126891177</v>
       </c>
       <c r="B110" t="n">
         <v>79014</v>
@@ -11985,10 +11975,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685267</v>
+        <v>685232</v>
       </c>
       <c r="R110" t="n">
-        <v>7107149</v>
+        <v>7107114</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12023,11 +12013,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12040,12 +12025,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12056,7 +12041,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126890089</v>
+        <v>126890327</v>
       </c>
       <c r="B111" t="n">
         <v>79014</v>
@@ -12087,14 +12072,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685254</v>
+        <v>685267</v>
       </c>
       <c r="R111" t="n">
-        <v>7107171</v>
+        <v>7107149</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12129,6 +12114,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12141,12 +12131,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12157,7 +12147,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126891177</v>
+        <v>126893465</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12188,14 +12178,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685232</v>
+        <v>685211</v>
       </c>
       <c r="R112" t="n">
-        <v>7107114</v>
+        <v>7107147</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12230,6 +12220,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12242,12 +12237,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12258,10 +12253,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126893465</v>
+        <v>126890633</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>75130</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12269,34 +12264,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685211</v>
+        <v>685311</v>
       </c>
       <c r="R113" t="n">
-        <v>7107147</v>
+        <v>7107013</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12331,11 +12326,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12348,12 +12338,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12364,10 +12354,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126890589</v>
+        <v>126890093</v>
       </c>
       <c r="B114" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12375,34 +12365,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685289</v>
+        <v>685268</v>
       </c>
       <c r="R114" t="n">
-        <v>7107194</v>
+        <v>7107183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12446,15 +12436,30 @@
       <c r="AG114" t="b">
         <v>0</v>
       </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12465,10 +12470,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126890317</v>
+        <v>126889621</v>
       </c>
       <c r="B115" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12476,34 +12481,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685420</v>
+        <v>685397</v>
       </c>
       <c r="R115" t="n">
-        <v>7107002</v>
+        <v>7107085</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12538,11 +12543,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Färsk ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -12555,12 +12555,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12571,10 +12571,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126889621</v>
+        <v>126890589</v>
       </c>
       <c r="B116" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12582,34 +12582,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685397</v>
+        <v>685289</v>
       </c>
       <c r="R116" t="n">
-        <v>7107085</v>
+        <v>7107194</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12656,12 +12656,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12672,10 +12672,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126891179</v>
+        <v>126891631</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12683,34 +12683,38 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685268</v>
+        <v>685262</v>
       </c>
       <c r="R117" t="n">
-        <v>7107012</v>
+        <v>7107166</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12745,6 +12749,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12757,12 +12766,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12773,45 +12782,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126890073</v>
+        <v>126890608</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685306</v>
+        <v>685410</v>
       </c>
       <c r="R118" t="n">
-        <v>7107003</v>
+        <v>7106989</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12858,12 +12867,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12874,45 +12883,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126890608</v>
+        <v>126890073</v>
       </c>
       <c r="B119" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685410</v>
+        <v>685306</v>
       </c>
       <c r="R119" t="n">
-        <v>7106989</v>
+        <v>7107003</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12959,12 +12968,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12975,10 +12984,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126891631</v>
+        <v>126891179</v>
       </c>
       <c r="B120" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12986,38 +12995,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685262</v>
+        <v>685268</v>
       </c>
       <c r="R120" t="n">
-        <v>7107166</v>
+        <v>7107012</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13052,11 +13057,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13069,12 +13069,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13085,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126890086</v>
+        <v>126893491</v>
       </c>
       <c r="B121" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13096,34 +13096,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685221</v>
+        <v>685369</v>
       </c>
       <c r="R121" t="n">
-        <v>7107115</v>
+        <v>7107086</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13167,30 +13167,15 @@
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13302,7 +13287,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126890154</v>
+        <v>126890158</v>
       </c>
       <c r="B123" t="n">
         <v>79014</v>
@@ -13337,10 +13322,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685361</v>
+        <v>685225</v>
       </c>
       <c r="R123" t="n">
-        <v>7107207</v>
+        <v>7107113</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13392,7 +13377,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13403,7 +13388,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126890158</v>
+        <v>126890154</v>
       </c>
       <c r="B124" t="n">
         <v>79014</v>
@@ -13438,10 +13423,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685225</v>
+        <v>685361</v>
       </c>
       <c r="R124" t="n">
-        <v>7107113</v>
+        <v>7107207</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13493,7 +13478,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13504,10 +13489,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893491</v>
+        <v>126890086</v>
       </c>
       <c r="B125" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13515,34 +13500,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685369</v>
+        <v>685221</v>
       </c>
       <c r="R125" t="n">
-        <v>7107086</v>
+        <v>7107115</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13586,15 +13571,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13605,45 +13605,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126890599</v>
+        <v>126890159</v>
       </c>
       <c r="B126" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685411</v>
+        <v>685238</v>
       </c>
       <c r="R126" t="n">
-        <v>7107223</v>
+        <v>7107094</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13690,12 +13690,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13706,10 +13706,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126889622</v>
+        <v>126889626</v>
       </c>
       <c r="B127" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13717,34 +13717,41 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685254</v>
+        <v>685337</v>
       </c>
       <c r="R127" t="n">
-        <v>7107050</v>
+        <v>7107187</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13785,6 +13792,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13807,10 +13815,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126890613</v>
+        <v>126893461</v>
       </c>
       <c r="B128" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13818,34 +13826,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685370</v>
+        <v>685338</v>
       </c>
       <c r="R128" t="n">
-        <v>7107120</v>
+        <v>7107092</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13880,24 +13888,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13908,10 +13922,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126893468</v>
+        <v>126890085</v>
       </c>
       <c r="B129" t="n">
-        <v>78773</v>
+        <v>80989</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13919,34 +13933,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685403</v>
+        <v>685222</v>
       </c>
       <c r="R129" t="n">
-        <v>7107031</v>
+        <v>7107058</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13981,11 +13995,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -13994,16 +14003,31 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14014,10 +14038,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126890159</v>
+        <v>126889622</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14025,34 +14049,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685238</v>
+        <v>685254</v>
       </c>
       <c r="R130" t="n">
-        <v>7107094</v>
+        <v>7107050</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14099,12 +14123,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14115,10 +14139,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126889626</v>
+        <v>126890613</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14126,41 +14150,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685337</v>
+        <v>685370</v>
       </c>
       <c r="R131" t="n">
-        <v>7107187</v>
+        <v>7107120</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14201,19 +14218,18 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14224,10 +14240,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126889631</v>
+        <v>126893468</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14235,34 +14251,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685348</v>
+        <v>685403</v>
       </c>
       <c r="R132" t="n">
-        <v>7107202</v>
+        <v>7107031</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14297,6 +14313,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14309,12 +14330,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14325,45 +14346,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126890326</v>
+        <v>126890599</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685271</v>
+        <v>685411</v>
       </c>
       <c r="R133" t="n">
-        <v>7107170</v>
+        <v>7107223</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14398,11 +14419,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14415,12 +14431,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14431,7 +14447,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126890176</v>
+        <v>126889631</v>
       </c>
       <c r="B134" t="n">
         <v>79014</v>
@@ -14462,14 +14478,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685413</v>
+        <v>685348</v>
       </c>
       <c r="R134" t="n">
-        <v>7107035</v>
+        <v>7107202</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14516,12 +14532,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14532,45 +14548,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126889639</v>
+        <v>126890176</v>
       </c>
       <c r="B135" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685328</v>
+        <v>685413</v>
       </c>
       <c r="R135" t="n">
-        <v>7107189</v>
+        <v>7107035</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14617,12 +14633,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14633,45 +14649,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126889638</v>
+        <v>126890326</v>
       </c>
       <c r="B136" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685366</v>
+        <v>685271</v>
       </c>
       <c r="R136" t="n">
-        <v>7107208</v>
+        <v>7107170</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14706,6 +14722,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14718,12 +14739,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14734,45 +14755,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126890085</v>
+        <v>126889639</v>
       </c>
       <c r="B137" t="n">
-        <v>80989</v>
+        <v>98360</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1049</v>
+        <v>219790</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685222</v>
+        <v>685328</v>
       </c>
       <c r="R137" t="n">
-        <v>7107058</v>
+        <v>7107189</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14816,30 +14837,15 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14850,45 +14856,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126893461</v>
+        <v>126889638</v>
       </c>
       <c r="B138" t="n">
-        <v>78681</v>
+        <v>98360</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685338</v>
+        <v>685366</v>
       </c>
       <c r="R138" t="n">
-        <v>7107092</v>
+        <v>7107208</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14923,30 +14929,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Carl Jansson, Lotta Ihse, Torbjörn Söderquist, kristina stenmarck, Jennica Andersson, Anne Siivola, Lars-Erik Nilsson, Gunilla R Burke, Hedda Bring, Elin Kannerby, Beke Regelin, Eleonor Johansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14957,10 +14957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126890174</v>
+        <v>126890593</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14968,34 +14968,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685415</v>
+        <v>685219</v>
       </c>
       <c r="R139" t="n">
-        <v>7107015</v>
+        <v>7107117</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15042,12 +15042,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15058,7 +15058,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126890324</v>
+        <v>126890174</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -15089,14 +15089,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685394</v>
+        <v>685415</v>
       </c>
       <c r="R140" t="n">
-        <v>7107061</v>
+        <v>7107015</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15131,11 +15131,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15148,12 +15143,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15164,10 +15159,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126889620</v>
+        <v>126890324</v>
       </c>
       <c r="B141" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15175,34 +15170,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685391</v>
+        <v>685394</v>
       </c>
       <c r="R141" t="n">
-        <v>7107082</v>
+        <v>7107061</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15237,6 +15232,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15249,12 +15249,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15265,7 +15265,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126890593</v>
+        <v>126889620</v>
       </c>
       <c r="B142" t="n">
         <v>79603</v>
@@ -15296,14 +15296,14 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685219</v>
+        <v>685391</v>
       </c>
       <c r="R142" t="n">
-        <v>7107117</v>
+        <v>7107082</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15366,10 +15366,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126890162</v>
+        <v>126890622</v>
       </c>
       <c r="B143" t="n">
-        <v>91325</v>
+        <v>78772</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15377,34 +15377,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685401</v>
+        <v>685368</v>
       </c>
       <c r="R143" t="n">
-        <v>7107105</v>
+        <v>7107109</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15467,10 +15467,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126890074</v>
+        <v>126890621</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15478,34 +15478,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685303</v>
+        <v>685370</v>
       </c>
       <c r="R144" t="n">
-        <v>7107030</v>
+        <v>7107120</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15552,12 +15552,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126890622</v>
+        <v>126890074</v>
       </c>
       <c r="B146" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15680,34 +15680,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685368</v>
+        <v>685303</v>
       </c>
       <c r="R146" t="n">
-        <v>7107109</v>
+        <v>7107030</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15770,10 +15770,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126890621</v>
+        <v>126890162</v>
       </c>
       <c r="B147" t="n">
-        <v>78772</v>
+        <v>91326</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15781,34 +15781,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685370</v>
+        <v>685401</v>
       </c>
       <c r="R147" t="n">
-        <v>7107120</v>
+        <v>7107105</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15855,12 +15855,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890101</v>
+        <v>126890098</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685405</v>
+        <v>685407</v>
       </c>
       <c r="R24" t="n">
-        <v>7107108</v>
+        <v>7107134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,6 +3063,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3083,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890156</v>
+        <v>126891637</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,34 +3109,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685267</v>
+        <v>685419</v>
       </c>
       <c r="R25" t="n">
-        <v>7107114</v>
+        <v>7107106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3168,12 +3183,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3184,7 +3199,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890075</v>
+        <v>126890101</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3219,10 +3234,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685334</v>
+        <v>685405</v>
       </c>
       <c r="R26" t="n">
-        <v>7107003</v>
+        <v>7107108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3285,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890328</v>
+        <v>126890156</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3316,14 +3331,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685268</v>
+        <v>685267</v>
       </c>
       <c r="R27" t="n">
-        <v>7107110</v>
+        <v>7107114</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,12 +3385,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3386,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890201</v>
+        <v>126890075</v>
       </c>
       <c r="B28" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3397,34 +3412,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685214</v>
+        <v>685334</v>
       </c>
       <c r="R28" t="n">
-        <v>7107061</v>
+        <v>7107003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,12 +3486,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3487,10 +3502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890098</v>
+        <v>126890328</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,34 +3513,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685407</v>
+        <v>685268</v>
       </c>
       <c r="R29" t="n">
-        <v>7107134</v>
+        <v>7107110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,30 +3584,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126891637</v>
+        <v>126890201</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,34 +3614,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685419</v>
+        <v>685214</v>
       </c>
       <c r="R30" t="n">
-        <v>7107106</v>
+        <v>7107061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,12 +3688,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3805,45 +3805,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890627</v>
+        <v>126890616</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685410</v>
+        <v>685576</v>
       </c>
       <c r="R32" t="n">
-        <v>7106989</v>
+        <v>7107009</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,7 +3914,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890081</v>
+        <v>126890627</v>
       </c>
       <c r="B33" t="n">
         <v>79014</v>
@@ -3937,14 +3945,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685215</v>
+        <v>685410</v>
       </c>
       <c r="R33" t="n">
-        <v>7107071</v>
+        <v>7106989</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3991,12 +3999,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4007,7 +4015,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126890103</v>
+        <v>126890081</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4042,10 +4050,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685370</v>
+        <v>685215</v>
       </c>
       <c r="R34" t="n">
-        <v>7107029</v>
+        <v>7107071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4097,7 +4105,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4108,10 +4116,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891394</v>
+        <v>126890103</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4119,34 +4127,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685267</v>
+        <v>685370</v>
       </c>
       <c r="R35" t="n">
-        <v>7107032</v>
+        <v>7107029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4193,12 +4201,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4209,53 +4217,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126890616</v>
+        <v>126891394</v>
       </c>
       <c r="B36" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685576</v>
+        <v>685267</v>
       </c>
       <c r="R36" t="n">
-        <v>7107009</v>
+        <v>7107032</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4302,12 +4302,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890196</v>
+        <v>126891170</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4430,34 +4430,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685270</v>
+        <v>685426</v>
       </c>
       <c r="R38" t="n">
-        <v>7107166</v>
+        <v>7106971</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4504,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4520,45 +4520,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891178</v>
+        <v>126891640</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685220</v>
+        <v>685539</v>
       </c>
       <c r="R39" t="n">
-        <v>7107060</v>
+        <v>7107065</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4593,6 +4601,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4605,12 +4618,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4621,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891170</v>
+        <v>126891173</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4632,21 +4645,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4656,10 +4669,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685426</v>
+        <v>685248</v>
       </c>
       <c r="R40" t="n">
-        <v>7106971</v>
+        <v>7107014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,53 +4735,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126891640</v>
+        <v>126890196</v>
       </c>
       <c r="B41" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685539</v>
+        <v>685270</v>
       </c>
       <c r="R41" t="n">
-        <v>7107065</v>
+        <v>7107166</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,11 +4808,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891173</v>
+        <v>126891178</v>
       </c>
       <c r="B42" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685248</v>
+        <v>685220</v>
       </c>
       <c r="R42" t="n">
-        <v>7107014</v>
+        <v>7107060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4937,45 +4937,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890169</v>
+        <v>126891169</v>
       </c>
       <c r="B43" t="n">
-        <v>78772</v>
+        <v>91291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685422</v>
+        <v>685394</v>
       </c>
       <c r="R43" t="n">
-        <v>7107111</v>
+        <v>7107163</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,12 +5022,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890087</v>
+        <v>126890325</v>
       </c>
       <c r="B44" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685222</v>
+        <v>685363</v>
       </c>
       <c r="R44" t="n">
-        <v>7107114</v>
+        <v>7107208</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,6 +5111,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5119,31 +5124,16 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5154,10 +5144,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893463</v>
+        <v>126890169</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5165,21 +5155,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5189,10 +5179,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685387</v>
+        <v>685422</v>
       </c>
       <c r="R45" t="n">
-        <v>7107051</v>
+        <v>7107111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5227,11 +5217,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5249,7 +5234,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5260,10 +5245,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890147</v>
+        <v>126890087</v>
       </c>
       <c r="B46" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5271,34 +5256,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685392</v>
+        <v>685222</v>
       </c>
       <c r="R46" t="n">
-        <v>7107087</v>
+        <v>7107114</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5342,15 +5327,30 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5361,45 +5361,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126891169</v>
+        <v>126893463</v>
       </c>
       <c r="B47" t="n">
-        <v>91291</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685394</v>
+        <v>685387</v>
       </c>
       <c r="R47" t="n">
-        <v>7107163</v>
+        <v>7107051</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5434,6 +5434,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5446,12 +5451,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5462,10 +5467,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890325</v>
+        <v>126890147</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5473,34 +5478,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685363</v>
+        <v>685392</v>
       </c>
       <c r="R48" t="n">
-        <v>7107208</v>
+        <v>7107087</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5535,11 +5540,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5552,12 +5552,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890097</v>
+        <v>126890185</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,34 +6622,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685305</v>
+        <v>685259</v>
       </c>
       <c r="R59" t="n">
-        <v>7107176</v>
+        <v>7107105</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6693,30 +6693,15 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6727,10 +6712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890189</v>
+        <v>126890097</v>
       </c>
       <c r="B60" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6738,34 +6723,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685256</v>
+        <v>685305</v>
       </c>
       <c r="R60" t="n">
-        <v>7107175</v>
+        <v>7107176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6809,15 +6794,30 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6828,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890597</v>
+        <v>126890189</v>
       </c>
       <c r="B61" t="n">
-        <v>57817</v>
+        <v>80989</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,42 +6839,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685576</v>
+        <v>685256</v>
       </c>
       <c r="R61" t="n">
-        <v>7107009</v>
+        <v>7107175</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6921,12 +6913,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6937,10 +6929,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126891393</v>
+        <v>126890597</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6948,34 +6940,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685263</v>
+        <v>685576</v>
       </c>
       <c r="R62" t="n">
-        <v>7107150</v>
+        <v>7107009</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7022,12 +7022,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7038,7 +7038,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890586</v>
+        <v>126891393</v>
       </c>
       <c r="B63" t="n">
         <v>79632</v>
@@ -7069,14 +7069,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685419</v>
+        <v>685263</v>
       </c>
       <c r="R63" t="n">
-        <v>7107080</v>
+        <v>7107150</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890618</v>
+        <v>126890586</v>
       </c>
       <c r="B64" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,21 +7150,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685398</v>
+        <v>685419</v>
       </c>
       <c r="R64" t="n">
-        <v>7106998</v>
+        <v>7107080</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890592</v>
+        <v>126890618</v>
       </c>
       <c r="B65" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685368</v>
+        <v>685398</v>
       </c>
       <c r="R65" t="n">
-        <v>7107109</v>
+        <v>7106998</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890185</v>
+        <v>126890592</v>
       </c>
       <c r="B66" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685259</v>
+        <v>685368</v>
       </c>
       <c r="R66" t="n">
-        <v>7107105</v>
+        <v>7107109</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8270,10 +8270,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890188</v>
+        <v>126890617</v>
       </c>
       <c r="B75" t="n">
-        <v>57761</v>
+        <v>58027</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8281,16 +8281,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8298,29 +8298,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685274</v>
+        <v>685406</v>
       </c>
       <c r="R75" t="n">
-        <v>7107181</v>
+        <v>7107034</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8367,12 +8363,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8383,10 +8379,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890617</v>
+        <v>126890188</v>
       </c>
       <c r="B76" t="n">
-        <v>58027</v>
+        <v>57761</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8394,16 +8390,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8411,25 +8407,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685406</v>
+        <v>685274</v>
       </c>
       <c r="R76" t="n">
-        <v>7107034</v>
+        <v>7107181</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8476,12 +8476,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8492,10 +8492,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126891642</v>
+        <v>126890102</v>
       </c>
       <c r="B77" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8503,34 +8503,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685361</v>
+        <v>685393</v>
       </c>
       <c r="R77" t="n">
-        <v>7107114</v>
+        <v>7107081</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8565,11 +8570,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8582,12 +8582,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8598,10 +8598,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126893466</v>
+        <v>126890080</v>
       </c>
       <c r="B78" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8609,34 +8609,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685256</v>
+        <v>685217</v>
       </c>
       <c r="R78" t="n">
-        <v>7107043</v>
+        <v>7107067</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8671,30 +8676,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8705,45 +8704,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126890588</v>
+        <v>126890088</v>
       </c>
       <c r="B79" t="n">
-        <v>79632</v>
+        <v>91291</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685418</v>
+        <v>685251</v>
       </c>
       <c r="R79" t="n">
-        <v>7106975</v>
+        <v>7107154</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8787,15 +8786,30 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8806,50 +8820,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890094</v>
+        <v>126891642</v>
       </c>
       <c r="B80" t="n">
-        <v>57479</v>
+        <v>78772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102976</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685274</v>
+        <v>685361</v>
       </c>
       <c r="R80" t="n">
-        <v>7107182</v>
+        <v>7107114</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8884,6 +8893,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8896,12 +8910,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8912,10 +8926,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890594</v>
+        <v>126893466</v>
       </c>
       <c r="B81" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8923,34 +8937,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685372</v>
+        <v>685256</v>
       </c>
       <c r="R81" t="n">
-        <v>7106953</v>
+        <v>7107043</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,24 +8999,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9013,10 +9033,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890102</v>
+        <v>126890588</v>
       </c>
       <c r="B82" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9024,39 +9044,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685393</v>
+        <v>685418</v>
       </c>
       <c r="R82" t="n">
-        <v>7107081</v>
+        <v>7106975</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,12 +9118,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9119,27 +9134,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890080</v>
+        <v>126890094</v>
       </c>
       <c r="B83" t="n">
-        <v>57657</v>
+        <v>57479</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9150,7 +9165,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9159,10 +9174,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685217</v>
+        <v>685274</v>
       </c>
       <c r="R83" t="n">
-        <v>7107067</v>
+        <v>7107182</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9225,45 +9240,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890088</v>
+        <v>126890594</v>
       </c>
       <c r="B84" t="n">
-        <v>91291</v>
+        <v>79603</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685251</v>
+        <v>685372</v>
       </c>
       <c r="R84" t="n">
-        <v>7107154</v>
+        <v>7106953</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9307,30 +9322,15 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9876,32 +9876,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126890178</v>
+        <v>126893458</v>
       </c>
       <c r="B90" t="n">
-        <v>98360</v>
+        <v>57817</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9911,10 +9911,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685495</v>
+        <v>685383</v>
       </c>
       <c r="R90" t="n">
-        <v>7107045</v>
+        <v>7107114</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9949,6 +9949,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9966,7 +9971,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9977,10 +9982,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126891632</v>
+        <v>126890625</v>
       </c>
       <c r="B91" t="n">
-        <v>57654</v>
+        <v>91344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9988,38 +9993,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685370</v>
+        <v>685539</v>
       </c>
       <c r="R91" t="n">
-        <v>7107190</v>
+        <v>7107056</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10054,11 +10055,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Bohål i gran. Långt ner.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10071,12 +10067,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10087,10 +10083,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126890190</v>
+        <v>126891632</v>
       </c>
       <c r="B92" t="n">
-        <v>80989</v>
+        <v>57654</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,34 +10094,38 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685223</v>
+        <v>685370</v>
       </c>
       <c r="R92" t="n">
-        <v>7107071</v>
+        <v>7107190</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10160,6 +10160,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10172,12 +10177,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10188,10 +10193,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890625</v>
+        <v>126893493</v>
       </c>
       <c r="B93" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10199,34 +10204,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685539</v>
+        <v>685266</v>
       </c>
       <c r="R93" t="n">
-        <v>7107056</v>
+        <v>7107184</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10273,12 +10278,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10289,7 +10294,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893493</v>
+        <v>126890628</v>
       </c>
       <c r="B94" t="n">
         <v>79014</v>
@@ -10320,14 +10325,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685266</v>
+        <v>685371</v>
       </c>
       <c r="R94" t="n">
-        <v>7107184</v>
+        <v>7107135</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10374,12 +10379,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10390,10 +10395,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890628</v>
+        <v>126890099</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10401,34 +10406,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685371</v>
+        <v>685420</v>
       </c>
       <c r="R95" t="n">
-        <v>7107135</v>
+        <v>7107121</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,15 +10477,30 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10491,10 +10511,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890099</v>
+        <v>126890619</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10502,34 +10522,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685420</v>
+        <v>685146</v>
       </c>
       <c r="R96" t="n">
-        <v>7107121</v>
+        <v>7107092</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10573,30 +10593,15 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10607,10 +10612,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126890619</v>
+        <v>126890190</v>
       </c>
       <c r="B97" t="n">
-        <v>78772</v>
+        <v>80989</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10618,34 +10623,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685146</v>
+        <v>685223</v>
       </c>
       <c r="R97" t="n">
-        <v>7107092</v>
+        <v>7107071</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10692,12 +10697,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10708,32 +10713,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893458</v>
+        <v>126890178</v>
       </c>
       <c r="B98" t="n">
-        <v>57817</v>
+        <v>98360</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10743,10 +10748,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685383</v>
+        <v>685495</v>
       </c>
       <c r="R98" t="n">
-        <v>7107114</v>
+        <v>7107045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10781,11 +10786,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -13085,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893491</v>
+        <v>126889634</v>
       </c>
       <c r="B121" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13096,34 +13096,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685369</v>
+        <v>685358</v>
       </c>
       <c r="R121" t="n">
-        <v>7107086</v>
+        <v>7106974</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13170,12 +13170,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13186,7 +13186,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126889634</v>
+        <v>126890154</v>
       </c>
       <c r="B122" t="n">
         <v>79014</v>
@@ -13217,14 +13217,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685358</v>
+        <v>685361</v>
       </c>
       <c r="R122" t="n">
-        <v>7106974</v>
+        <v>7107207</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13271,12 +13271,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13287,10 +13287,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126890158</v>
+        <v>126890086</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13298,34 +13298,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685225</v>
+        <v>685221</v>
       </c>
       <c r="R123" t="n">
-        <v>7107113</v>
+        <v>7107115</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13369,15 +13369,30 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13388,7 +13403,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126890154</v>
+        <v>126890158</v>
       </c>
       <c r="B124" t="n">
         <v>79014</v>
@@ -13423,10 +13438,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685361</v>
+        <v>685225</v>
       </c>
       <c r="R124" t="n">
-        <v>7107207</v>
+        <v>7107113</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13489,10 +13504,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126890086</v>
+        <v>126893491</v>
       </c>
       <c r="B125" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13500,34 +13515,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685221</v>
+        <v>685369</v>
       </c>
       <c r="R125" t="n">
-        <v>7107115</v>
+        <v>7107086</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13571,30 +13586,15 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14957,10 +14957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126890593</v>
+        <v>126890174</v>
       </c>
       <c r="B139" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14968,34 +14968,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685219</v>
+        <v>685415</v>
       </c>
       <c r="R139" t="n">
-        <v>7107117</v>
+        <v>7107015</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15042,12 +15042,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15058,7 +15058,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126890174</v>
+        <v>126890324</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -15089,14 +15089,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685415</v>
+        <v>685394</v>
       </c>
       <c r="R140" t="n">
-        <v>7107015</v>
+        <v>7107061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15131,6 +15131,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15143,12 +15148,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15159,10 +15164,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126890324</v>
+        <v>126889620</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15170,34 +15175,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685394</v>
+        <v>685391</v>
       </c>
       <c r="R141" t="n">
-        <v>7107061</v>
+        <v>7107082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15232,11 +15237,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15249,12 +15249,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15265,7 +15265,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126889620</v>
+        <v>126890593</v>
       </c>
       <c r="B142" t="n">
         <v>79603</v>
@@ -15296,14 +15296,14 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685391</v>
+        <v>685219</v>
       </c>
       <c r="R142" t="n">
-        <v>7107082</v>
+        <v>7107117</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15568,10 +15568,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126891180</v>
+        <v>126891638</v>
       </c>
       <c r="B145" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15579,21 +15579,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15603,10 +15603,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685372</v>
+        <v>685363</v>
       </c>
       <c r="R145" t="n">
-        <v>7106948</v>
+        <v>7107112</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15653,12 +15653,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15669,7 +15669,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126890074</v>
+        <v>126891180</v>
       </c>
       <c r="B146" t="n">
         <v>79014</v>
@@ -15700,14 +15700,14 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685303</v>
+        <v>685372</v>
       </c>
       <c r="R146" t="n">
-        <v>7107030</v>
+        <v>7106948</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15770,10 +15770,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126890162</v>
+        <v>126890074</v>
       </c>
       <c r="B147" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15781,34 +15781,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685401</v>
+        <v>685303</v>
       </c>
       <c r="R147" t="n">
-        <v>7107105</v>
+        <v>7107030</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15855,12 +15855,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15871,10 +15871,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126891638</v>
+        <v>126890162</v>
       </c>
       <c r="B148" t="n">
-        <v>78773</v>
+        <v>91326</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15882,34 +15882,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685363</v>
+        <v>685401</v>
       </c>
       <c r="R148" t="n">
-        <v>7107112</v>
+        <v>7107105</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15956,12 +15956,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126890606</v>
+        <v>126890591</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685377</v>
+        <v>685370</v>
       </c>
       <c r="R2" t="n">
-        <v>7107099</v>
+        <v>7107120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126891648</v>
+        <v>126890629</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -807,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685260</v>
+        <v>685283</v>
       </c>
       <c r="R3" t="n">
-        <v>7107165</v>
+        <v>7107035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,11 +849,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På späd gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -866,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -882,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890629</v>
+        <v>126893464</v>
       </c>
       <c r="B4" t="n">
         <v>79014</v>
@@ -913,14 +908,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685283</v>
+        <v>685240</v>
       </c>
       <c r="R4" t="n">
-        <v>7107035</v>
+        <v>7107184</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +950,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -967,12 +967,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -983,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126890591</v>
+        <v>126893460</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,34 +994,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685370</v>
+        <v>685477</v>
       </c>
       <c r="R5" t="n">
-        <v>7107120</v>
+        <v>7107122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1056,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1068,12 +1073,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1084,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126893460</v>
+        <v>126891648</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1115,14 +1120,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685477</v>
+        <v>685260</v>
       </c>
       <c r="R6" t="n">
-        <v>7107122</v>
+        <v>7107165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,7 +1164,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På späd gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893464</v>
+        <v>126890606</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685240</v>
+        <v>685377</v>
       </c>
       <c r="R7" t="n">
-        <v>7107184</v>
+        <v>7107099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,11 +1268,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,12 +1280,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126889633</v>
+        <v>126890071</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,34 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685223</v>
+        <v>685346</v>
       </c>
       <c r="R10" t="n">
-        <v>7107049</v>
+        <v>7106969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,15 +1594,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890071</v>
+        <v>126890148</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685346</v>
+        <v>685419</v>
       </c>
       <c r="R11" t="n">
-        <v>7106969</v>
+        <v>7107117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,30 +1710,15 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890148</v>
+        <v>126889633</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,34 +1740,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685419</v>
+        <v>685223</v>
       </c>
       <c r="R12" t="n">
-        <v>7107117</v>
+        <v>7107049</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,12 +1814,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890100</v>
+        <v>126890191</v>
       </c>
       <c r="B14" t="n">
-        <v>75138</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,34 +1947,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685405</v>
+        <v>685257</v>
       </c>
       <c r="R14" t="n">
-        <v>7107108</v>
+        <v>7107109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,30 +2018,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2052,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890191</v>
+        <v>126890587</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,34 +2048,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685257</v>
+        <v>685398</v>
       </c>
       <c r="R15" t="n">
-        <v>7107109</v>
+        <v>7106998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,12 +2122,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2153,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890587</v>
+        <v>126890100</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>75138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,34 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685398</v>
+        <v>685405</v>
       </c>
       <c r="R16" t="n">
-        <v>7106998</v>
+        <v>7107108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,15 +2220,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2254,7 +2254,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890166</v>
+        <v>126890092</v>
       </c>
       <c r="B17" t="n">
         <v>78773</v>
@@ -2285,14 +2285,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685415</v>
+        <v>685268</v>
       </c>
       <c r="R17" t="n">
-        <v>7107111</v>
+        <v>7107182</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,15 +2336,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2355,7 +2370,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890092</v>
+        <v>126890166</v>
       </c>
       <c r="B18" t="n">
         <v>78773</v>
@@ -2386,14 +2401,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685268</v>
+        <v>685415</v>
       </c>
       <c r="R18" t="n">
-        <v>7107182</v>
+        <v>7107111</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,30 +2452,15 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,45 +2572,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890316</v>
+        <v>126890082</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685410</v>
+        <v>685213</v>
       </c>
       <c r="R20" t="n">
-        <v>7106991</v>
+        <v>7107071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,11 +2645,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2662,12 +2657,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2678,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891185</v>
+        <v>126890316</v>
       </c>
       <c r="B21" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685417</v>
+        <v>685410</v>
       </c>
       <c r="R21" t="n">
-        <v>7106968</v>
+        <v>7106991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,25 +2746,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2780,45 +2779,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890630</v>
+        <v>126891185</v>
       </c>
       <c r="B22" t="n">
-        <v>98360</v>
+        <v>78420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685421</v>
+        <v>685417</v>
       </c>
       <c r="R22" t="n">
-        <v>7107205</v>
+        <v>7106968</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,18 +2858,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2881,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126890082</v>
+        <v>126890630</v>
       </c>
       <c r="B23" t="n">
-        <v>92616</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,34 +2892,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685213</v>
+        <v>685421</v>
       </c>
       <c r="R23" t="n">
-        <v>7107071</v>
+        <v>7107205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,12 +2966,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891637</v>
+        <v>126890075</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3109,34 +3109,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685419</v>
+        <v>685334</v>
       </c>
       <c r="R25" t="n">
-        <v>7107106</v>
+        <v>7107003</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,12 +3183,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3401,7 +3401,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890075</v>
+        <v>126890328</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3432,14 +3432,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685334</v>
+        <v>685268</v>
       </c>
       <c r="R28" t="n">
-        <v>7107003</v>
+        <v>7107110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,12 +3486,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890328</v>
+        <v>126890201</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,34 +3513,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685268</v>
+        <v>685214</v>
       </c>
       <c r="R29" t="n">
-        <v>7107110</v>
+        <v>7107061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3587,12 +3587,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126890201</v>
+        <v>126891637</v>
       </c>
       <c r="B30" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,34 +3614,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685214</v>
+        <v>685419</v>
       </c>
       <c r="R30" t="n">
-        <v>7107061</v>
+        <v>7107106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,12 +3688,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3805,53 +3805,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890616</v>
+        <v>126890627</v>
       </c>
       <c r="B32" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685576</v>
+        <v>685410</v>
       </c>
       <c r="R32" t="n">
-        <v>7107009</v>
+        <v>7106989</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3914,10 +3906,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126890627</v>
+        <v>126891394</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3925,34 +3917,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685410</v>
+        <v>685267</v>
       </c>
       <c r="R33" t="n">
-        <v>7106989</v>
+        <v>7107032</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3999,12 +3991,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4206,7 +4198,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4217,45 +4209,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126891394</v>
+        <v>126890616</v>
       </c>
       <c r="B36" t="n">
-        <v>79632</v>
+        <v>58027</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685267</v>
+        <v>685576</v>
       </c>
       <c r="R36" t="n">
-        <v>7107032</v>
+        <v>7107009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4302,12 +4302,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891170</v>
+        <v>126890196</v>
       </c>
       <c r="B38" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4430,34 +4430,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685426</v>
+        <v>685270</v>
       </c>
       <c r="R38" t="n">
-        <v>7106971</v>
+        <v>7107166</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4504,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4520,53 +4520,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891640</v>
+        <v>126891178</v>
       </c>
       <c r="B39" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685539</v>
+        <v>685220</v>
       </c>
       <c r="R39" t="n">
-        <v>7107065</v>
+        <v>7107060</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4601,11 +4593,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4618,12 +4605,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4634,10 +4621,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891173</v>
+        <v>126891170</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4645,21 +4632,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4669,10 +4656,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685248</v>
+        <v>685426</v>
       </c>
       <c r="R40" t="n">
-        <v>7107014</v>
+        <v>7106971</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4735,45 +4722,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126890196</v>
+        <v>126891640</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685270</v>
+        <v>685539</v>
       </c>
       <c r="R41" t="n">
-        <v>7107166</v>
+        <v>7107065</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4808,6 +4803,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891178</v>
+        <v>126891173</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685220</v>
+        <v>685248</v>
       </c>
       <c r="R42" t="n">
-        <v>7107060</v>
+        <v>7107014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5770,45 +5770,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893459</v>
+        <v>126893490</v>
       </c>
       <c r="B51" t="n">
-        <v>105463</v>
+        <v>78773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221725</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685327</v>
+        <v>685403</v>
       </c>
       <c r="R51" t="n">
-        <v>7107177</v>
+        <v>7107099</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5843,11 +5843,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5861,12 +5856,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5978,10 +5973,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890329</v>
+        <v>126890590</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5989,34 +5984,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685287</v>
+        <v>685371</v>
       </c>
       <c r="R53" t="n">
-        <v>7107034</v>
+        <v>7107135</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6051,11 +6046,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6068,12 +6058,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6084,7 +6074,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891181</v>
+        <v>126890329</v>
       </c>
       <c r="B54" t="n">
         <v>79014</v>
@@ -6119,10 +6109,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685396</v>
+        <v>685287</v>
       </c>
       <c r="R54" t="n">
-        <v>7106961</v>
+        <v>7107034</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6157,6 +6147,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6169,12 +6164,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6290,7 +6285,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6301,10 +6296,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126890590</v>
+        <v>126891181</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6312,34 +6307,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685371</v>
+        <v>685396</v>
       </c>
       <c r="R56" t="n">
-        <v>7107135</v>
+        <v>7106961</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6386,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6402,48 +6397,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126877810</v>
+        <v>126893459</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>105463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>221725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fäbodtjärnen, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685341</v>
+        <v>685327</v>
       </c>
       <c r="R57" t="n">
-        <v>7107003</v>
+        <v>7107177</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6470,19 +6465,14 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>10:01</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6491,25 +6481,30 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893490</v>
+        <v>126877810</v>
       </c>
       <c r="B58" t="n">
         <v>78773</v>
@@ -6540,17 +6535,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Fäbodtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685403</v>
+        <v>685341</v>
       </c>
       <c r="R58" t="n">
-        <v>7107099</v>
+        <v>7107003</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6577,44 +6572,49 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890185</v>
+        <v>126890597</v>
       </c>
       <c r="B59" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,34 +6622,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685259</v>
+        <v>685576</v>
       </c>
       <c r="R59" t="n">
-        <v>7107105</v>
+        <v>7107009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6696,12 +6704,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6817,7 +6825,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6828,10 +6836,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890189</v>
+        <v>126891393</v>
       </c>
       <c r="B61" t="n">
-        <v>80989</v>
+        <v>79632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,21 +6847,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6871,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685256</v>
+        <v>685263</v>
       </c>
       <c r="R61" t="n">
-        <v>7107175</v>
+        <v>7107150</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6913,12 +6921,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6929,10 +6937,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890597</v>
+        <v>126890586</v>
       </c>
       <c r="B62" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6940,42 +6948,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685576</v>
+        <v>685419</v>
       </c>
       <c r="R62" t="n">
-        <v>7107009</v>
+        <v>7107080</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7038,10 +7038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126891393</v>
+        <v>126890618</v>
       </c>
       <c r="B63" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,34 +7049,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685263</v>
+        <v>685398</v>
       </c>
       <c r="R63" t="n">
-        <v>7107150</v>
+        <v>7106998</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,7 +7139,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890586</v>
+        <v>126890592</v>
       </c>
       <c r="B64" t="n">
         <v>79632</v>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685419</v>
+        <v>685368</v>
       </c>
       <c r="R64" t="n">
-        <v>7107080</v>
+        <v>7107109</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890618</v>
+        <v>126890185</v>
       </c>
       <c r="B65" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7251,34 +7251,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685398</v>
+        <v>685259</v>
       </c>
       <c r="R65" t="n">
-        <v>7106998</v>
+        <v>7107105</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7325,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890592</v>
+        <v>126891174</v>
       </c>
       <c r="B66" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685368</v>
+        <v>685430</v>
       </c>
       <c r="R66" t="n">
-        <v>7107109</v>
+        <v>7106963</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126891174</v>
+        <v>126890189</v>
       </c>
       <c r="B67" t="n">
-        <v>78773</v>
+        <v>80989</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685430</v>
+        <v>685256</v>
       </c>
       <c r="R67" t="n">
-        <v>7106963</v>
+        <v>7107175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7543,10 +7543,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126890157</v>
+        <v>126889640</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7554,34 +7554,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685265</v>
+        <v>685311</v>
       </c>
       <c r="R68" t="n">
-        <v>7107114</v>
+        <v>7107020</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,12 +7628,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7644,45 +7644,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890620</v>
+        <v>126890617</v>
       </c>
       <c r="B69" t="n">
-        <v>78772</v>
+        <v>58027</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685161</v>
+        <v>685406</v>
       </c>
       <c r="R69" t="n">
-        <v>7107091</v>
+        <v>7107034</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7745,45 +7753,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890091</v>
+        <v>126890188</v>
       </c>
       <c r="B70" t="n">
-        <v>78772</v>
+        <v>57761</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685268</v>
+        <v>685274</v>
       </c>
       <c r="R70" t="n">
-        <v>7107185</v>
+        <v>7107181</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7827,30 +7847,15 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7861,10 +7866,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890197</v>
+        <v>126890595</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7872,34 +7877,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685263</v>
+        <v>685417</v>
       </c>
       <c r="R71" t="n">
-        <v>7107013</v>
+        <v>7107135</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7934,11 +7939,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7951,12 +7951,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8068,10 +8068,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126889640</v>
+        <v>126890157</v>
       </c>
       <c r="B73" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8079,34 +8079,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685311</v>
+        <v>685265</v>
       </c>
       <c r="R73" t="n">
-        <v>7107020</v>
+        <v>7107114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8153,12 +8153,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8169,10 +8169,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890595</v>
+        <v>126890197</v>
       </c>
       <c r="B74" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8180,34 +8180,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685417</v>
+        <v>685263</v>
       </c>
       <c r="R74" t="n">
-        <v>7107135</v>
+        <v>7107013</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8242,6 +8242,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8254,12 +8259,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8270,53 +8275,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890617</v>
+        <v>126890620</v>
       </c>
       <c r="B75" t="n">
-        <v>58027</v>
+        <v>78772</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685406</v>
+        <v>685161</v>
       </c>
       <c r="R75" t="n">
-        <v>7107034</v>
+        <v>7107091</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8379,57 +8376,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890188</v>
+        <v>126890091</v>
       </c>
       <c r="B76" t="n">
-        <v>57761</v>
+        <v>78772</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685274</v>
+        <v>685268</v>
       </c>
       <c r="R76" t="n">
-        <v>7107181</v>
+        <v>7107185</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8473,15 +8458,30 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8492,10 +8492,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890102</v>
+        <v>126891642</v>
       </c>
       <c r="B77" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8503,39 +8503,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685393</v>
+        <v>685361</v>
       </c>
       <c r="R77" t="n">
-        <v>7107081</v>
+        <v>7107114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,6 +8565,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8582,12 +8582,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8598,10 +8598,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126890080</v>
+        <v>126893466</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8609,39 +8609,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685217</v>
+        <v>685256</v>
       </c>
       <c r="R78" t="n">
-        <v>7107067</v>
+        <v>7107043</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8676,24 +8671,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8704,45 +8705,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126890088</v>
+        <v>126890588</v>
       </c>
       <c r="B79" t="n">
-        <v>91291</v>
+        <v>79632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685251</v>
+        <v>685418</v>
       </c>
       <c r="R79" t="n">
-        <v>7107154</v>
+        <v>7106975</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8786,30 +8787,15 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8820,10 +8806,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126891642</v>
+        <v>126890102</v>
       </c>
       <c r="B80" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8831,34 +8817,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685361</v>
+        <v>685393</v>
       </c>
       <c r="R80" t="n">
-        <v>7107114</v>
+        <v>7107081</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8893,11 +8884,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8910,12 +8896,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8926,10 +8912,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126893466</v>
+        <v>126890080</v>
       </c>
       <c r="B81" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,34 +8923,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685256</v>
+        <v>685217</v>
       </c>
       <c r="R81" t="n">
-        <v>7107043</v>
+        <v>7107067</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8999,30 +8990,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9033,10 +9018,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890588</v>
+        <v>126890594</v>
       </c>
       <c r="B82" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9044,21 +9029,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9068,10 +9053,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685418</v>
+        <v>685372</v>
       </c>
       <c r="R82" t="n">
-        <v>7106975</v>
+        <v>7106953</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9134,50 +9119,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890094</v>
+        <v>126890088</v>
       </c>
       <c r="B83" t="n">
-        <v>57479</v>
+        <v>91291</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102976</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685274</v>
+        <v>685251</v>
       </c>
       <c r="R83" t="n">
-        <v>7107182</v>
+        <v>7107154</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9221,6 +9201,21 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
@@ -9229,7 +9224,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9240,45 +9235,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890594</v>
+        <v>126890094</v>
       </c>
       <c r="B84" t="n">
-        <v>79603</v>
+        <v>57479</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>102976</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685372</v>
+        <v>685274</v>
       </c>
       <c r="R84" t="n">
-        <v>7106953</v>
+        <v>7107182</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,12 +9325,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9543,45 +9543,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126890084</v>
+        <v>126890598</v>
       </c>
       <c r="B87" t="n">
-        <v>77992</v>
+        <v>80146</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685223</v>
+        <v>685154</v>
       </c>
       <c r="R87" t="n">
-        <v>7107061</v>
+        <v>7107066</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9625,30 +9625,15 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9659,45 +9644,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126890598</v>
+        <v>126890084</v>
       </c>
       <c r="B88" t="n">
-        <v>80146</v>
+        <v>77992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685154</v>
+        <v>685223</v>
       </c>
       <c r="R88" t="n">
-        <v>7107066</v>
+        <v>7107061</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9741,15 +9726,30 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9876,10 +9876,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126893458</v>
+        <v>126890628</v>
       </c>
       <c r="B90" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9887,34 +9887,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685383</v>
+        <v>685371</v>
       </c>
       <c r="R90" t="n">
-        <v>7107114</v>
+        <v>7107135</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9949,11 +9949,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9966,12 +9961,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9982,10 +9977,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126890625</v>
+        <v>126893493</v>
       </c>
       <c r="B91" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9993,34 +9988,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685539</v>
+        <v>685266</v>
       </c>
       <c r="R91" t="n">
-        <v>7107056</v>
+        <v>7107184</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10067,12 +10062,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10083,10 +10078,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126891632</v>
+        <v>126893458</v>
       </c>
       <c r="B92" t="n">
-        <v>57654</v>
+        <v>57817</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10094,38 +10089,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685370</v>
+        <v>685383</v>
       </c>
       <c r="R92" t="n">
-        <v>7107190</v>
+        <v>7107114</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10162,7 +10153,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Bohål i gran. Långt ner.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10177,12 +10168,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10193,10 +10184,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893493</v>
+        <v>126890190</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10204,34 +10195,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685266</v>
+        <v>685223</v>
       </c>
       <c r="R93" t="n">
-        <v>7107184</v>
+        <v>7107071</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10278,12 +10269,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10294,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890628</v>
+        <v>126890625</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10305,21 +10296,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10329,10 +10320,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685371</v>
+        <v>685539</v>
       </c>
       <c r="R94" t="n">
-        <v>7107135</v>
+        <v>7107056</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10395,10 +10386,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890099</v>
+        <v>126890619</v>
       </c>
       <c r="B95" t="n">
-        <v>80117</v>
+        <v>78772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10406,34 +10397,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685420</v>
+        <v>685146</v>
       </c>
       <c r="R95" t="n">
-        <v>7107121</v>
+        <v>7107092</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10477,30 +10468,15 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10511,10 +10487,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890619</v>
+        <v>126890099</v>
       </c>
       <c r="B96" t="n">
-        <v>78772</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10522,34 +10498,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685146</v>
+        <v>685420</v>
       </c>
       <c r="R96" t="n">
-        <v>7107092</v>
+        <v>7107121</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10593,15 +10569,30 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10612,10 +10603,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126890190</v>
+        <v>126891632</v>
       </c>
       <c r="B97" t="n">
-        <v>80989</v>
+        <v>57654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10623,34 +10614,38 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685223</v>
+        <v>685370</v>
       </c>
       <c r="R97" t="n">
-        <v>7107071</v>
+        <v>7107190</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10685,6 +10680,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10697,12 +10697,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890149</v>
+        <v>126890614</v>
       </c>
       <c r="B99" t="n">
-        <v>91344</v>
+        <v>78773</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,34 +10825,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685396</v>
+        <v>685368</v>
       </c>
       <c r="R99" t="n">
-        <v>7107168</v>
+        <v>7107109</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10899,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890155</v>
+        <v>126890184</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10926,21 +10926,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685312</v>
+        <v>685257</v>
       </c>
       <c r="R100" t="n">
-        <v>7107169</v>
+        <v>7107113</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11122,10 +11122,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126893494</v>
+        <v>126890149</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11133,34 +11133,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685374</v>
+        <v>685396</v>
       </c>
       <c r="R102" t="n">
-        <v>7106951</v>
+        <v>7107168</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,7 +11223,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126889630</v>
+        <v>126890155</v>
       </c>
       <c r="B103" t="n">
         <v>79014</v>
@@ -11254,14 +11254,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685385</v>
+        <v>685312</v>
       </c>
       <c r="R103" t="n">
-        <v>7106995</v>
+        <v>7107169</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126890614</v>
+        <v>126889630</v>
       </c>
       <c r="B104" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,34 +11335,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685368</v>
+        <v>685385</v>
       </c>
       <c r="R104" t="n">
-        <v>7107109</v>
+        <v>7106995</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11409,12 +11409,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126890184</v>
+        <v>126893494</v>
       </c>
       <c r="B105" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11436,34 +11436,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685257</v>
+        <v>685374</v>
       </c>
       <c r="R105" t="n">
-        <v>7107113</v>
+        <v>7106951</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11510,12 +11510,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11526,45 +11526,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126890317</v>
+        <v>126890161</v>
       </c>
       <c r="B106" t="n">
-        <v>57657</v>
+        <v>91291</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685420</v>
+        <v>685360</v>
       </c>
       <c r="R106" t="n">
-        <v>7107002</v>
+        <v>7107179</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Färsk ringhack på tall</t>
+          <t>Artnamn</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11616,12 +11616,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11632,45 +11632,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126890161</v>
+        <v>126891176</v>
       </c>
       <c r="B107" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685360</v>
+        <v>685352</v>
       </c>
       <c r="R107" t="n">
-        <v>7107179</v>
+        <v>7107016</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11705,11 +11705,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11722,12 +11717,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11738,7 +11733,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126891176</v>
+        <v>126890089</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11769,14 +11764,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685352</v>
+        <v>685254</v>
       </c>
       <c r="R108" t="n">
-        <v>7107016</v>
+        <v>7107171</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11823,12 +11818,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11839,7 +11834,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126890089</v>
+        <v>126891177</v>
       </c>
       <c r="B109" t="n">
         <v>79014</v>
@@ -11870,14 +11865,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685254</v>
+        <v>685232</v>
       </c>
       <c r="R109" t="n">
-        <v>7107171</v>
+        <v>7107114</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11924,12 +11919,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Carl Jansson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11940,7 +11935,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126891177</v>
+        <v>126890327</v>
       </c>
       <c r="B110" t="n">
         <v>79014</v>
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685232</v>
+        <v>685267</v>
       </c>
       <c r="R110" t="n">
-        <v>7107114</v>
+        <v>7107149</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12013,6 +12008,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12025,12 +12025,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12041,7 +12041,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126890327</v>
+        <v>126893465</v>
       </c>
       <c r="B111" t="n">
         <v>79014</v>
@@ -12072,14 +12072,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685267</v>
+        <v>685211</v>
       </c>
       <c r="R111" t="n">
-        <v>7107149</v>
+        <v>7107147</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12131,12 +12131,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12147,10 +12147,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893465</v>
+        <v>126889621</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12158,34 +12158,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685211</v>
+        <v>685397</v>
       </c>
       <c r="R112" t="n">
-        <v>7107147</v>
+        <v>7107085</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12220,11 +12220,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12237,12 +12232,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12470,10 +12465,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126889621</v>
+        <v>126890589</v>
       </c>
       <c r="B115" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12481,34 +12476,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685397</v>
+        <v>685289</v>
       </c>
       <c r="R115" t="n">
-        <v>7107085</v>
+        <v>7107194</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12555,12 +12550,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12571,10 +12566,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126890589</v>
+        <v>126890317</v>
       </c>
       <c r="B116" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12582,34 +12577,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685289</v>
+        <v>685420</v>
       </c>
       <c r="R116" t="n">
-        <v>7107194</v>
+        <v>7107002</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12644,6 +12639,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färsk ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -12656,12 +12656,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12672,49 +12672,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126891631</v>
+        <v>126890608</v>
       </c>
       <c r="B117" t="n">
-        <v>57657</v>
+        <v>79038</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685262</v>
+        <v>685410</v>
       </c>
       <c r="R117" t="n">
-        <v>7107166</v>
+        <v>7106989</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12749,11 +12745,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12766,12 +12757,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12782,45 +12773,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126890608</v>
+        <v>126890073</v>
       </c>
       <c r="B118" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685410</v>
+        <v>685306</v>
       </c>
       <c r="R118" t="n">
-        <v>7106989</v>
+        <v>7107003</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12867,12 +12858,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12883,7 +12874,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126890073</v>
+        <v>126891179</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12914,14 +12905,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685306</v>
+        <v>685268</v>
       </c>
       <c r="R119" t="n">
-        <v>7107003</v>
+        <v>7107012</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12968,12 +12959,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12984,10 +12975,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126891179</v>
+        <v>126891631</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12995,34 +12986,38 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685268</v>
+        <v>685262</v>
       </c>
       <c r="R120" t="n">
-        <v>7107012</v>
+        <v>7107166</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13057,6 +13052,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -13069,12 +13069,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13085,7 +13085,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126889634</v>
+        <v>126890154</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13116,14 +13116,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685358</v>
+        <v>685361</v>
       </c>
       <c r="R121" t="n">
-        <v>7106974</v>
+        <v>7107207</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13170,12 +13170,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13186,7 +13186,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126890154</v>
+        <v>126889634</v>
       </c>
       <c r="B122" t="n">
         <v>79014</v>
@@ -13217,14 +13217,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685361</v>
+        <v>685358</v>
       </c>
       <c r="R122" t="n">
-        <v>7107207</v>
+        <v>7106974</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13271,12 +13271,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13287,10 +13287,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126890086</v>
+        <v>126890158</v>
       </c>
       <c r="B123" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13298,34 +13298,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685221</v>
+        <v>685225</v>
       </c>
       <c r="R123" t="n">
-        <v>7107115</v>
+        <v>7107113</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13369,30 +13369,15 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13403,10 +13388,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126890158</v>
+        <v>126890086</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13414,34 +13399,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685225</v>
+        <v>685221</v>
       </c>
       <c r="R124" t="n">
-        <v>7107113</v>
+        <v>7107115</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13485,15 +13470,30 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13605,10 +13605,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126890159</v>
+        <v>126893461</v>
       </c>
       <c r="B126" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13616,21 +13616,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685238</v>
+        <v>685338</v>
       </c>
       <c r="R126" t="n">
-        <v>7107094</v>
+        <v>7107092</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13678,12 +13678,18 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13695,7 +13701,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13706,10 +13712,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126889626</v>
+        <v>126890085</v>
       </c>
       <c r="B127" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13717,41 +13723,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685337</v>
+        <v>685222</v>
       </c>
       <c r="R127" t="n">
-        <v>7107187</v>
+        <v>7107058</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13792,19 +13791,33 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13815,10 +13828,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893461</v>
+        <v>126889626</v>
       </c>
       <c r="B128" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13826,34 +13839,41 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685338</v>
+        <v>685337</v>
       </c>
       <c r="R128" t="n">
-        <v>7107092</v>
+        <v>7107187</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13888,11 +13908,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13906,12 +13921,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13922,10 +13937,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126890085</v>
+        <v>126890176</v>
       </c>
       <c r="B129" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13933,34 +13948,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685222</v>
+        <v>685413</v>
       </c>
       <c r="R129" t="n">
-        <v>7107058</v>
+        <v>7107035</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14004,30 +14019,15 @@
       <c r="AG129" t="b">
         <v>0</v>
       </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14038,10 +14038,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126889622</v>
+        <v>126890159</v>
       </c>
       <c r="B130" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14049,34 +14049,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685254</v>
+        <v>685238</v>
       </c>
       <c r="R130" t="n">
-        <v>7107050</v>
+        <v>7107094</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14123,12 +14123,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14139,10 +14139,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126890613</v>
+        <v>126889631</v>
       </c>
       <c r="B131" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14150,34 +14150,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685370</v>
+        <v>685348</v>
       </c>
       <c r="R131" t="n">
-        <v>7107120</v>
+        <v>7107202</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14224,12 +14224,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14240,10 +14240,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893468</v>
+        <v>126890326</v>
       </c>
       <c r="B132" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14251,34 +14251,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685403</v>
+        <v>685271</v>
       </c>
       <c r="R132" t="n">
-        <v>7107031</v>
+        <v>7107170</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14330,12 +14330,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14447,32 +14447,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126889631</v>
+        <v>126889639</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685348</v>
+        <v>685328</v>
       </c>
       <c r="R134" t="n">
-        <v>7107202</v>
+        <v>7107189</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14548,45 +14548,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126890176</v>
+        <v>126889638</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685413</v>
+        <v>685366</v>
       </c>
       <c r="R135" t="n">
-        <v>7107035</v>
+        <v>7107208</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14633,12 +14633,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14649,10 +14649,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126890326</v>
+        <v>126889622</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14660,34 +14660,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685271</v>
+        <v>685254</v>
       </c>
       <c r="R136" t="n">
-        <v>7107170</v>
+        <v>7107050</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14722,11 +14722,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14739,12 +14734,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14755,45 +14750,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126889639</v>
+        <v>126890613</v>
       </c>
       <c r="B137" t="n">
-        <v>98360</v>
+        <v>78773</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685328</v>
+        <v>685370</v>
       </c>
       <c r="R137" t="n">
-        <v>7107189</v>
+        <v>7107120</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14840,12 +14835,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14856,45 +14851,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126889638</v>
+        <v>126893468</v>
       </c>
       <c r="B138" t="n">
-        <v>98360</v>
+        <v>78773</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685366</v>
+        <v>685403</v>
       </c>
       <c r="R138" t="n">
-        <v>7107208</v>
+        <v>7107031</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14929,6 +14924,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -14941,12 +14941,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14957,10 +14957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126890174</v>
+        <v>126889620</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14968,34 +14968,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685415</v>
+        <v>685391</v>
       </c>
       <c r="R139" t="n">
-        <v>7107015</v>
+        <v>7107082</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15042,12 +15042,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15058,10 +15058,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126890324</v>
+        <v>126890593</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15069,34 +15069,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685394</v>
+        <v>685219</v>
       </c>
       <c r="R140" t="n">
-        <v>7107061</v>
+        <v>7107117</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15131,11 +15131,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15148,12 +15143,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15164,10 +15159,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126889620</v>
+        <v>126890174</v>
       </c>
       <c r="B141" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15175,34 +15170,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685391</v>
+        <v>685415</v>
       </c>
       <c r="R141" t="n">
-        <v>7107082</v>
+        <v>7107015</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15249,12 +15244,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15265,10 +15260,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126890593</v>
+        <v>126890324</v>
       </c>
       <c r="B142" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15276,34 +15271,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685219</v>
+        <v>685394</v>
       </c>
       <c r="R142" t="n">
-        <v>7107117</v>
+        <v>7107061</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15338,6 +15333,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15366,10 +15366,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126890622</v>
+        <v>126890162</v>
       </c>
       <c r="B143" t="n">
-        <v>78772</v>
+        <v>91326</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15377,34 +15377,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685368</v>
+        <v>685401</v>
       </c>
       <c r="R143" t="n">
-        <v>7107109</v>
+        <v>7107105</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15467,7 +15467,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126890621</v>
+        <v>126890622</v>
       </c>
       <c r="B144" t="n">
         <v>78772</v>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685370</v>
+        <v>685368</v>
       </c>
       <c r="R144" t="n">
-        <v>7107120</v>
+        <v>7107109</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15568,10 +15568,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126891638</v>
+        <v>126890621</v>
       </c>
       <c r="B145" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15579,34 +15579,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685363</v>
+        <v>685370</v>
       </c>
       <c r="R145" t="n">
-        <v>7107112</v>
+        <v>7107120</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15653,12 +15653,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Carl Jansson, Gunilla R Burke, Alexandra Astafourova, Eleonor Johansson, Jennica Andersson, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, Torbjörn Söderquist, Elin Kannerby, kristina stenmarck, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15871,10 +15871,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126890162</v>
+        <v>126891638</v>
       </c>
       <c r="B148" t="n">
-        <v>91326</v>
+        <v>78773</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15882,34 +15882,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685401</v>
+        <v>685363</v>
       </c>
       <c r="R148" t="n">
-        <v>7107105</v>
+        <v>7107112</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15956,12 +15956,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126890591</v>
+        <v>126891648</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685370</v>
+        <v>685260</v>
       </c>
       <c r="R2" t="n">
-        <v>7107120</v>
+        <v>7107165</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +748,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På späd gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890629</v>
+        <v>126890591</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685283</v>
+        <v>685370</v>
       </c>
       <c r="R3" t="n">
-        <v>7107035</v>
+        <v>7107120</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893464</v>
+        <v>126890606</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685240</v>
+        <v>685377</v>
       </c>
       <c r="R4" t="n">
-        <v>7107184</v>
+        <v>7107099</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +955,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -967,12 +967,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1089,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126891648</v>
+        <v>126890629</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1120,14 +1120,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685260</v>
+        <v>685283</v>
       </c>
       <c r="R6" t="n">
-        <v>7107165</v>
+        <v>7107035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1162,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På späd gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1179,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890606</v>
+        <v>126893464</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685377</v>
+        <v>685240</v>
       </c>
       <c r="R7" t="n">
-        <v>7107099</v>
+        <v>7107184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1263,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,12 +1280,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2471,45 +2471,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126890200</v>
+        <v>126890082</v>
       </c>
       <c r="B19" t="n">
-        <v>77992</v>
+        <v>92616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685218</v>
+        <v>685213</v>
       </c>
       <c r="R19" t="n">
-        <v>7107060</v>
+        <v>7107071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2556,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2572,45 +2572,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890082</v>
+        <v>126890316</v>
       </c>
       <c r="B20" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685213</v>
+        <v>685410</v>
       </c>
       <c r="R20" t="n">
-        <v>7107071</v>
+        <v>7106991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,6 +2645,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2657,12 +2662,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890316</v>
+        <v>126891185</v>
       </c>
       <c r="B21" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2684,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685410</v>
+        <v>685417</v>
       </c>
       <c r="R21" t="n">
-        <v>7106991</v>
+        <v>7106968</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,29 +2751,25 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2779,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891185</v>
+        <v>126890200</v>
       </c>
       <c r="B22" t="n">
-        <v>78420</v>
+        <v>77992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,34 +2791,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685417</v>
+        <v>685218</v>
       </c>
       <c r="R22" t="n">
-        <v>7106968</v>
+        <v>7107060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2858,19 +2859,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890098</v>
+        <v>126890075</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685407</v>
+        <v>685334</v>
       </c>
       <c r="R24" t="n">
-        <v>7107134</v>
+        <v>7107003</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,21 +3063,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3098,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890075</v>
+        <v>126890098</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3109,21 +3094,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685334</v>
+        <v>685407</v>
       </c>
       <c r="R25" t="n">
-        <v>7107003</v>
+        <v>7107134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,6 +3164,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -4318,45 +4318,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890615</v>
+        <v>126890196</v>
       </c>
       <c r="B37" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685399</v>
+        <v>685270</v>
       </c>
       <c r="R37" t="n">
-        <v>7107027</v>
+        <v>7107166</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4403,12 +4403,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4419,7 +4419,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890196</v>
+        <v>126891178</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4450,14 +4450,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685270</v>
+        <v>685220</v>
       </c>
       <c r="R38" t="n">
-        <v>7107166</v>
+        <v>7107060</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4504,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891178</v>
+        <v>126891170</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4531,21 +4531,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685220</v>
+        <v>685426</v>
       </c>
       <c r="R39" t="n">
-        <v>7107060</v>
+        <v>7106971</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4621,45 +4621,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891170</v>
+        <v>126890615</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>80153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685426</v>
+        <v>685399</v>
       </c>
       <c r="R40" t="n">
-        <v>7106971</v>
+        <v>7107027</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4706,12 +4706,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4722,53 +4722,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126891640</v>
+        <v>126891173</v>
       </c>
       <c r="B41" t="n">
-        <v>58027</v>
+        <v>78773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685539</v>
+        <v>685248</v>
       </c>
       <c r="R41" t="n">
-        <v>7107065</v>
+        <v>7107014</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,11 +4795,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4807,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4836,45 +4823,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891173</v>
+        <v>126891640</v>
       </c>
       <c r="B42" t="n">
-        <v>78773</v>
+        <v>58027</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685248</v>
+        <v>685539</v>
       </c>
       <c r="R42" t="n">
-        <v>7107014</v>
+        <v>7107065</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,6 +4904,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4921,12 +4921,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4937,45 +4937,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126891169</v>
+        <v>126890631</v>
       </c>
       <c r="B43" t="n">
-        <v>91291</v>
+        <v>78681</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685394</v>
+        <v>685215</v>
       </c>
       <c r="R43" t="n">
-        <v>7107163</v>
+        <v>7107084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,12 +5022,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890325</v>
+        <v>126889641</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685363</v>
+        <v>685348</v>
       </c>
       <c r="R44" t="n">
-        <v>7107208</v>
+        <v>7106970</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,11 +5111,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5128,12 +5123,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5144,45 +5139,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890169</v>
+        <v>126891169</v>
       </c>
       <c r="B45" t="n">
-        <v>78772</v>
+        <v>91291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685422</v>
+        <v>685394</v>
       </c>
       <c r="R45" t="n">
-        <v>7107111</v>
+        <v>7107163</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5229,12 +5224,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5245,10 +5240,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890087</v>
+        <v>126890325</v>
       </c>
       <c r="B46" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5256,34 +5251,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685222</v>
+        <v>685363</v>
       </c>
       <c r="R46" t="n">
-        <v>7107114</v>
+        <v>7107208</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,6 +5313,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5326,31 +5326,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5361,10 +5346,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126893463</v>
+        <v>126890169</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5372,21 +5357,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5396,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685387</v>
+        <v>685422</v>
       </c>
       <c r="R47" t="n">
-        <v>7107051</v>
+        <v>7107111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5434,11 +5419,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5456,7 +5436,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5467,10 +5447,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890147</v>
+        <v>126890087</v>
       </c>
       <c r="B48" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5478,34 +5458,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685392</v>
+        <v>685222</v>
       </c>
       <c r="R48" t="n">
-        <v>7107087</v>
+        <v>7107114</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5549,15 +5529,30 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5568,10 +5563,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890631</v>
+        <v>126893463</v>
       </c>
       <c r="B49" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,34 +5574,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685215</v>
+        <v>685387</v>
       </c>
       <c r="R49" t="n">
-        <v>7107084</v>
+        <v>7107051</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5641,6 +5636,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5653,12 +5653,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126889641</v>
+        <v>126890147</v>
       </c>
       <c r="B50" t="n">
-        <v>78681</v>
+        <v>78772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5680,34 +5680,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685348</v>
+        <v>685392</v>
       </c>
       <c r="R50" t="n">
-        <v>7106970</v>
+        <v>7107087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893490</v>
+        <v>126889632</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5781,34 +5781,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685403</v>
+        <v>685270</v>
       </c>
       <c r="R51" t="n">
-        <v>7107099</v>
+        <v>7107186</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,19 +5849,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5872,10 +5871,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126889632</v>
+        <v>126890590</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,34 +5882,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685270</v>
+        <v>685371</v>
       </c>
       <c r="R52" t="n">
-        <v>7107186</v>
+        <v>7107135</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5957,12 +5956,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5973,10 +5972,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890590</v>
+        <v>126890329</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5984,34 +5983,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685371</v>
+        <v>685287</v>
       </c>
       <c r="R53" t="n">
-        <v>7107135</v>
+        <v>7107034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6046,6 +6045,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6058,12 +6062,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6074,10 +6078,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890329</v>
+        <v>126890083</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6085,34 +6089,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685287</v>
+        <v>685222</v>
       </c>
       <c r="R54" t="n">
-        <v>7107034</v>
+        <v>7107061</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6147,11 +6151,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6160,16 +6159,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6180,10 +6194,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126890083</v>
+        <v>126891181</v>
       </c>
       <c r="B55" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6191,34 +6205,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685222</v>
+        <v>685396</v>
       </c>
       <c r="R55" t="n">
-        <v>7107061</v>
+        <v>7106961</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6262,30 +6276,15 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,45 +6295,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891181</v>
+        <v>126893459</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>105463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685396</v>
+        <v>685327</v>
       </c>
       <c r="R56" t="n">
-        <v>7106961</v>
+        <v>7107177</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6369,24 +6368,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6397,48 +6402,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893459</v>
+        <v>126877810</v>
       </c>
       <c r="B57" t="n">
-        <v>105463</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Fäbodtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685327</v>
+        <v>685341</v>
       </c>
       <c r="R57" t="n">
-        <v>7107177</v>
+        <v>7107003</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6465,14 +6470,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6481,30 +6491,25 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Eleonor Johansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126877810</v>
+        <v>126893490</v>
       </c>
       <c r="B58" t="n">
         <v>78773</v>
@@ -6535,17 +6540,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fäbodtjärnen, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685341</v>
+        <v>685403</v>
       </c>
       <c r="R58" t="n">
-        <v>7107003</v>
+        <v>7107099</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6572,49 +6577,44 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eleonor Johansson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Torbjörn Söderquist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890597</v>
+        <v>126890189</v>
       </c>
       <c r="B59" t="n">
-        <v>57817</v>
+        <v>80989</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,42 +6622,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685576</v>
+        <v>685256</v>
       </c>
       <c r="R59" t="n">
-        <v>7107009</v>
+        <v>7107175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6704,12 +6696,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7240,10 +7232,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890185</v>
+        <v>126890597</v>
       </c>
       <c r="B65" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7251,34 +7243,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685259</v>
+        <v>685576</v>
       </c>
       <c r="R65" t="n">
-        <v>7107105</v>
+        <v>7107009</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7325,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7341,7 +7341,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126891174</v>
+        <v>126890185</v>
       </c>
       <c r="B66" t="n">
         <v>78773</v>
@@ -7372,14 +7372,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685430</v>
+        <v>685259</v>
       </c>
       <c r="R66" t="n">
-        <v>7106963</v>
+        <v>7107105</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126890189</v>
+        <v>126891174</v>
       </c>
       <c r="B67" t="n">
-        <v>80989</v>
+        <v>78773</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685256</v>
+        <v>685430</v>
       </c>
       <c r="R67" t="n">
-        <v>7107175</v>
+        <v>7106963</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8492,45 +8492,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126891642</v>
+        <v>126890088</v>
       </c>
       <c r="B77" t="n">
-        <v>78772</v>
+        <v>91291</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685361</v>
+        <v>685251</v>
       </c>
       <c r="R77" t="n">
-        <v>7107114</v>
+        <v>7107154</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8565,11 +8565,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8578,16 +8573,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8598,7 +8608,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126893466</v>
+        <v>126891642</v>
       </c>
       <c r="B78" t="n">
         <v>78772</v>
@@ -8629,14 +8639,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685256</v>
+        <v>685361</v>
       </c>
       <c r="R78" t="n">
-        <v>7107043</v>
+        <v>7107114</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8673,7 +8683,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På kolad silverhögstubbe</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8682,19 +8692,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8705,10 +8714,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126890588</v>
+        <v>126893466</v>
       </c>
       <c r="B79" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8716,34 +8725,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685418</v>
+        <v>685256</v>
       </c>
       <c r="R79" t="n">
-        <v>7106975</v>
+        <v>7107043</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8778,24 +8787,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8806,10 +8821,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890102</v>
+        <v>126890588</v>
       </c>
       <c r="B80" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8817,39 +8832,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685393</v>
+        <v>685418</v>
       </c>
       <c r="R80" t="n">
-        <v>7107081</v>
+        <v>7106975</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8896,12 +8906,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8912,7 +8922,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890080</v>
+        <v>126890102</v>
       </c>
       <c r="B81" t="n">
         <v>57657</v>
@@ -8943,7 +8953,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8952,10 +8962,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685217</v>
+        <v>685393</v>
       </c>
       <c r="R81" t="n">
-        <v>7107067</v>
+        <v>7107081</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9018,10 +9028,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890594</v>
+        <v>126890080</v>
       </c>
       <c r="B82" t="n">
-        <v>79603</v>
+        <v>57657</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9029,34 +9039,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685372</v>
+        <v>685217</v>
       </c>
       <c r="R82" t="n">
-        <v>7106953</v>
+        <v>7107067</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,12 +9118,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9119,45 +9134,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890088</v>
+        <v>126890094</v>
       </c>
       <c r="B83" t="n">
-        <v>91291</v>
+        <v>57479</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>102976</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685251</v>
+        <v>685274</v>
       </c>
       <c r="R83" t="n">
-        <v>7107154</v>
+        <v>7107182</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9200,21 +9220,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9235,50 +9240,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890094</v>
+        <v>126890594</v>
       </c>
       <c r="B84" t="n">
-        <v>57479</v>
+        <v>79603</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102976</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685274</v>
+        <v>685372</v>
       </c>
       <c r="R84" t="n">
-        <v>7107182</v>
+        <v>7106953</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,12 +9325,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9341,32 +9341,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890612</v>
+        <v>126890598</v>
       </c>
       <c r="B85" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685371</v>
+        <v>685154</v>
       </c>
       <c r="R85" t="n">
-        <v>7107135</v>
+        <v>7107066</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126890611</v>
+        <v>126890084</v>
       </c>
       <c r="B86" t="n">
-        <v>78773</v>
+        <v>77992</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9453,34 +9453,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685418</v>
+        <v>685223</v>
       </c>
       <c r="R86" t="n">
-        <v>7106975</v>
+        <v>7107061</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9524,15 +9524,30 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9543,45 +9558,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126890598</v>
+        <v>126890078</v>
       </c>
       <c r="B87" t="n">
-        <v>80146</v>
+        <v>79632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685154</v>
+        <v>685255</v>
       </c>
       <c r="R87" t="n">
-        <v>7107066</v>
+        <v>7107048</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9625,15 +9640,30 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9644,10 +9674,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126890084</v>
+        <v>126890612</v>
       </c>
       <c r="B88" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9655,34 +9685,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685223</v>
+        <v>685371</v>
       </c>
       <c r="R88" t="n">
-        <v>7107061</v>
+        <v>7107135</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9726,30 +9756,15 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9760,10 +9775,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126890078</v>
+        <v>126890611</v>
       </c>
       <c r="B89" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9771,34 +9786,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685255</v>
+        <v>685418</v>
       </c>
       <c r="R89" t="n">
-        <v>7107048</v>
+        <v>7106975</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9842,30 +9857,15 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9876,10 +9876,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126890628</v>
+        <v>126893458</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9887,34 +9887,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685371</v>
+        <v>685383</v>
       </c>
       <c r="R90" t="n">
-        <v>7107135</v>
+        <v>7107114</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9949,6 +9949,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9961,12 +9966,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9977,45 +9982,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126893493</v>
+        <v>126890178</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685266</v>
+        <v>685495</v>
       </c>
       <c r="R91" t="n">
-        <v>7107184</v>
+        <v>7107045</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10062,12 +10067,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10078,10 +10083,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893458</v>
+        <v>126890190</v>
       </c>
       <c r="B92" t="n">
-        <v>57817</v>
+        <v>80989</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10089,21 +10094,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10113,10 +10118,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685383</v>
+        <v>685223</v>
       </c>
       <c r="R92" t="n">
-        <v>7107114</v>
+        <v>7107071</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10151,11 +10156,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10184,10 +10184,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890190</v>
+        <v>126890625</v>
       </c>
       <c r="B93" t="n">
-        <v>80989</v>
+        <v>91344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10195,34 +10195,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685223</v>
+        <v>685539</v>
       </c>
       <c r="R93" t="n">
-        <v>7107071</v>
+        <v>7107056</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10269,12 +10269,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10285,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890625</v>
+        <v>126890628</v>
       </c>
       <c r="B94" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10296,21 +10296,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685539</v>
+        <v>685371</v>
       </c>
       <c r="R94" t="n">
-        <v>7107056</v>
+        <v>7107135</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10487,10 +10487,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890099</v>
+        <v>126893493</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10498,34 +10498,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685420</v>
+        <v>685266</v>
       </c>
       <c r="R96" t="n">
-        <v>7107121</v>
+        <v>7107184</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10569,30 +10569,15 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10713,45 +10698,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126890178</v>
+        <v>126890099</v>
       </c>
       <c r="B98" t="n">
-        <v>98360</v>
+        <v>80117</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685495</v>
+        <v>685420</v>
       </c>
       <c r="R98" t="n">
-        <v>7107045</v>
+        <v>7107121</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10795,15 +10780,30 @@
       <c r="AG98" t="b">
         <v>0</v>
       </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890614</v>
+        <v>126890155</v>
       </c>
       <c r="B99" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,34 +10825,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685368</v>
+        <v>685312</v>
       </c>
       <c r="R99" t="n">
-        <v>7107109</v>
+        <v>7107169</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10899,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890184</v>
+        <v>126889630</v>
       </c>
       <c r="B100" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685257</v>
+        <v>685385</v>
       </c>
       <c r="R100" t="n">
-        <v>7107113</v>
+        <v>7106995</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11000,12 +11000,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11122,10 +11122,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126890149</v>
+        <v>126893494</v>
       </c>
       <c r="B102" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11133,34 +11133,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685396</v>
+        <v>685374</v>
       </c>
       <c r="R102" t="n">
-        <v>7107168</v>
+        <v>7106951</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126890155</v>
+        <v>126890149</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11258,10 +11258,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685312</v>
+        <v>685396</v>
       </c>
       <c r="R103" t="n">
-        <v>7107169</v>
+        <v>7107168</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126889630</v>
+        <v>126890614</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,34 +11335,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685385</v>
+        <v>685368</v>
       </c>
       <c r="R104" t="n">
-        <v>7106995</v>
+        <v>7107109</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11409,12 +11409,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126893494</v>
+        <v>126890184</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11436,34 +11436,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685374</v>
+        <v>685257</v>
       </c>
       <c r="R105" t="n">
-        <v>7106951</v>
+        <v>7107113</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11510,12 +11510,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891648</v>
+        <v>126890591</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685260</v>
+        <v>685370</v>
       </c>
       <c r="R2" t="n">
-        <v>7107165</v>
+        <v>7107120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +748,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På späd gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890591</v>
+        <v>126890629</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685370</v>
+        <v>685283</v>
       </c>
       <c r="R3" t="n">
-        <v>7107120</v>
+        <v>7107035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126890606</v>
+        <v>126893464</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685377</v>
+        <v>685240</v>
       </c>
       <c r="R4" t="n">
-        <v>7107099</v>
+        <v>7107184</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +950,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -967,12 +967,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1089,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890629</v>
+        <v>126891648</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1120,14 +1120,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685283</v>
+        <v>685260</v>
       </c>
       <c r="R6" t="n">
-        <v>7107035</v>
+        <v>7107165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1162,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På späd gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893464</v>
+        <v>126890606</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685240</v>
+        <v>685377</v>
       </c>
       <c r="R7" t="n">
-        <v>7107184</v>
+        <v>7107099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,11 +1268,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,12 +1280,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890075</v>
+        <v>126890098</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685334</v>
+        <v>685407</v>
       </c>
       <c r="R24" t="n">
-        <v>7107003</v>
+        <v>7107134</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,6 +3063,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3083,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890098</v>
+        <v>126890075</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,21 +3109,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3118,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685407</v>
+        <v>685334</v>
       </c>
       <c r="R25" t="n">
-        <v>7107134</v>
+        <v>7107003</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,21 +3179,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3704,45 +3704,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126890146</v>
+        <v>126890616</v>
       </c>
       <c r="B31" t="n">
-        <v>91799</v>
+        <v>58027</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5467</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685217</v>
+        <v>685576</v>
       </c>
       <c r="R31" t="n">
-        <v>7107070</v>
+        <v>7107009</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3789,12 +3797,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3805,10 +3813,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126890627</v>
+        <v>126890146</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>91799</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3816,34 +3824,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685410</v>
+        <v>685217</v>
       </c>
       <c r="R32" t="n">
-        <v>7106989</v>
+        <v>7107070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3890,12 +3898,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3906,10 +3914,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891394</v>
+        <v>126890627</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3917,34 +3925,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685267</v>
+        <v>685410</v>
       </c>
       <c r="R33" t="n">
-        <v>7107032</v>
+        <v>7106989</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3991,12 +3999,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4007,10 +4015,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126890081</v>
+        <v>126891394</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,34 +4026,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685215</v>
+        <v>685267</v>
       </c>
       <c r="R34" t="n">
-        <v>7107071</v>
+        <v>7107032</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4092,12 +4100,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4108,7 +4116,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890103</v>
+        <v>126890081</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -4143,10 +4151,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685370</v>
+        <v>685215</v>
       </c>
       <c r="R35" t="n">
-        <v>7107029</v>
+        <v>7107071</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,53 +4217,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126890616</v>
+        <v>126890103</v>
       </c>
       <c r="B36" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685576</v>
+        <v>685370</v>
       </c>
       <c r="R36" t="n">
-        <v>7107009</v>
+        <v>7107029</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4302,12 +4302,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4318,45 +4318,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890196</v>
+        <v>126890615</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685270</v>
+        <v>685399</v>
       </c>
       <c r="R37" t="n">
-        <v>7107166</v>
+        <v>7107027</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4403,12 +4403,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4419,7 +4419,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891178</v>
+        <v>126890196</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4450,14 +4450,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685220</v>
+        <v>685270</v>
       </c>
       <c r="R38" t="n">
-        <v>7107060</v>
+        <v>7107166</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4504,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891170</v>
+        <v>126891178</v>
       </c>
       <c r="B39" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4531,21 +4531,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685426</v>
+        <v>685220</v>
       </c>
       <c r="R39" t="n">
-        <v>7106971</v>
+        <v>7107060</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4621,45 +4621,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890615</v>
+        <v>126891170</v>
       </c>
       <c r="B40" t="n">
-        <v>80153</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685399</v>
+        <v>685426</v>
       </c>
       <c r="R40" t="n">
-        <v>7107027</v>
+        <v>7106971</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4706,12 +4706,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4722,45 +4722,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126891173</v>
+        <v>126891640</v>
       </c>
       <c r="B41" t="n">
-        <v>78773</v>
+        <v>58027</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685248</v>
+        <v>685539</v>
       </c>
       <c r="R41" t="n">
-        <v>7107014</v>
+        <v>7107065</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,6 +4803,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4807,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4823,53 +4836,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891640</v>
+        <v>126891173</v>
       </c>
       <c r="B42" t="n">
-        <v>58027</v>
+        <v>78773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685539</v>
+        <v>685248</v>
       </c>
       <c r="R42" t="n">
-        <v>7107065</v>
+        <v>7107014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4904,11 +4909,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4921,12 +4921,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4937,45 +4937,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126890631</v>
+        <v>126891169</v>
       </c>
       <c r="B43" t="n">
-        <v>78681</v>
+        <v>91291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685215</v>
+        <v>685394</v>
       </c>
       <c r="R43" t="n">
-        <v>7107084</v>
+        <v>7107163</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,12 +5022,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126889641</v>
+        <v>126890325</v>
       </c>
       <c r="B44" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685348</v>
+        <v>685363</v>
       </c>
       <c r="R44" t="n">
-        <v>7106970</v>
+        <v>7107208</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,6 +5111,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5123,12 +5128,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5139,45 +5144,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126891169</v>
+        <v>126890169</v>
       </c>
       <c r="B45" t="n">
-        <v>91291</v>
+        <v>78772</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685394</v>
+        <v>685422</v>
       </c>
       <c r="R45" t="n">
-        <v>7107163</v>
+        <v>7107111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,12 +5229,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5240,10 +5245,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890325</v>
+        <v>126890087</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5251,34 +5256,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685363</v>
+        <v>685222</v>
       </c>
       <c r="R46" t="n">
-        <v>7107208</v>
+        <v>7107114</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5313,11 +5318,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5326,16 +5326,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5346,10 +5361,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890169</v>
+        <v>126893463</v>
       </c>
       <c r="B47" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5357,21 +5372,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5381,10 +5396,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685422</v>
+        <v>685387</v>
       </c>
       <c r="R47" t="n">
-        <v>7107111</v>
+        <v>7107051</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,6 +5434,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5436,7 +5456,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5447,10 +5467,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890087</v>
+        <v>126890147</v>
       </c>
       <c r="B48" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5458,34 +5478,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685222</v>
+        <v>685392</v>
       </c>
       <c r="R48" t="n">
-        <v>7107114</v>
+        <v>7107087</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,30 +5549,15 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5563,10 +5568,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893463</v>
+        <v>126890631</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5574,34 +5579,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685387</v>
+        <v>685215</v>
       </c>
       <c r="R49" t="n">
-        <v>7107051</v>
+        <v>7107084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,11 +5641,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5653,12 +5653,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126890147</v>
+        <v>126889641</v>
       </c>
       <c r="B50" t="n">
-        <v>78772</v>
+        <v>78681</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5680,34 +5680,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685392</v>
+        <v>685348</v>
       </c>
       <c r="R50" t="n">
-        <v>7107087</v>
+        <v>7106970</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890189</v>
+        <v>126890597</v>
       </c>
       <c r="B59" t="n">
-        <v>80989</v>
+        <v>57817</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,34 +6622,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685256</v>
+        <v>685576</v>
       </c>
       <c r="R59" t="n">
-        <v>7107175</v>
+        <v>7107009</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6696,12 +6704,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7232,10 +7240,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890597</v>
+        <v>126890185</v>
       </c>
       <c r="B65" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7243,42 +7251,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685576</v>
+        <v>685259</v>
       </c>
       <c r="R65" t="n">
-        <v>7107009</v>
+        <v>7107105</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7325,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7341,7 +7341,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126890185</v>
+        <v>126891174</v>
       </c>
       <c r="B66" t="n">
         <v>78773</v>
@@ -7372,14 +7372,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685259</v>
+        <v>685430</v>
       </c>
       <c r="R66" t="n">
-        <v>7107105</v>
+        <v>7106963</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126891174</v>
+        <v>126890189</v>
       </c>
       <c r="B67" t="n">
-        <v>78773</v>
+        <v>80989</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685430</v>
+        <v>685256</v>
       </c>
       <c r="R67" t="n">
-        <v>7106963</v>
+        <v>7107175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7644,53 +7644,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890617</v>
+        <v>126890595</v>
       </c>
       <c r="B69" t="n">
-        <v>58027</v>
+        <v>91326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685406</v>
+        <v>685417</v>
       </c>
       <c r="R69" t="n">
-        <v>7107034</v>
+        <v>7107135</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7753,57 +7745,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890188</v>
+        <v>126890173</v>
       </c>
       <c r="B70" t="n">
-        <v>57761</v>
+        <v>91487</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685274</v>
+        <v>685398</v>
       </c>
       <c r="R70" t="n">
-        <v>7107181</v>
+        <v>7106958</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7866,10 +7846,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890595</v>
+        <v>126890620</v>
       </c>
       <c r="B71" t="n">
-        <v>91326</v>
+        <v>78772</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7877,21 +7857,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7901,10 +7881,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685417</v>
+        <v>685161</v>
       </c>
       <c r="R71" t="n">
-        <v>7107135</v>
+        <v>7107091</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7967,45 +7947,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126890173</v>
+        <v>126890091</v>
       </c>
       <c r="B72" t="n">
-        <v>91487</v>
+        <v>78772</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685398</v>
+        <v>685268</v>
       </c>
       <c r="R72" t="n">
-        <v>7106958</v>
+        <v>7107185</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8049,15 +8029,30 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8068,45 +8063,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126890157</v>
+        <v>126890188</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>57761</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685265</v>
+        <v>685274</v>
       </c>
       <c r="R73" t="n">
-        <v>7107114</v>
+        <v>7107181</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8169,45 +8176,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890197</v>
+        <v>126890617</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685263</v>
+        <v>685406</v>
       </c>
       <c r="R74" t="n">
-        <v>7107013</v>
+        <v>7107034</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8242,11 +8257,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8259,12 +8269,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8275,10 +8285,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890620</v>
+        <v>126890157</v>
       </c>
       <c r="B75" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8286,34 +8296,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685161</v>
+        <v>685265</v>
       </c>
       <c r="R75" t="n">
-        <v>7107091</v>
+        <v>7107114</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8360,12 +8370,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8376,10 +8386,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890091</v>
+        <v>126890197</v>
       </c>
       <c r="B76" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8387,34 +8397,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685268</v>
+        <v>685263</v>
       </c>
       <c r="R76" t="n">
-        <v>7107185</v>
+        <v>7107013</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8449,6 +8459,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8457,31 +8472,16 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8492,45 +8492,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890088</v>
+        <v>126891642</v>
       </c>
       <c r="B77" t="n">
-        <v>91291</v>
+        <v>78772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685251</v>
+        <v>685361</v>
       </c>
       <c r="R77" t="n">
-        <v>7107154</v>
+        <v>7107114</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8565,6 +8565,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8573,31 +8578,16 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8608,7 +8598,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126891642</v>
+        <v>126893466</v>
       </c>
       <c r="B78" t="n">
         <v>78772</v>
@@ -8639,14 +8629,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685361</v>
+        <v>685256</v>
       </c>
       <c r="R78" t="n">
-        <v>7107114</v>
+        <v>7107043</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8683,7 +8673,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På kolad silverhögstubbe</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8692,18 +8682,19 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8714,10 +8705,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126893466</v>
+        <v>126890588</v>
       </c>
       <c r="B79" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8725,34 +8716,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685256</v>
+        <v>685418</v>
       </c>
       <c r="R79" t="n">
-        <v>7107043</v>
+        <v>7106975</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8787,30 +8778,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8821,10 +8806,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890588</v>
+        <v>126890102</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8832,34 +8817,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685418</v>
+        <v>685393</v>
       </c>
       <c r="R80" t="n">
-        <v>7106975</v>
+        <v>7107081</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8906,12 +8896,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8922,7 +8912,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890102</v>
+        <v>126890080</v>
       </c>
       <c r="B81" t="n">
         <v>57657</v>
@@ -8953,7 +8943,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8962,10 +8952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685393</v>
+        <v>685217</v>
       </c>
       <c r="R81" t="n">
-        <v>7107081</v>
+        <v>7107067</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9028,10 +9018,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890080</v>
+        <v>126890594</v>
       </c>
       <c r="B82" t="n">
-        <v>57657</v>
+        <v>79603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,39 +9029,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685217</v>
+        <v>685372</v>
       </c>
       <c r="R82" t="n">
-        <v>7107067</v>
+        <v>7106953</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9118,12 +9103,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9134,50 +9119,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890094</v>
+        <v>126890088</v>
       </c>
       <c r="B83" t="n">
-        <v>57479</v>
+        <v>91291</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102976</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685274</v>
+        <v>685251</v>
       </c>
       <c r="R83" t="n">
-        <v>7107182</v>
+        <v>7107154</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9220,6 +9200,21 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9240,45 +9235,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890594</v>
+        <v>126890094</v>
       </c>
       <c r="B84" t="n">
-        <v>79603</v>
+        <v>57479</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>102976</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685372</v>
+        <v>685274</v>
       </c>
       <c r="R84" t="n">
-        <v>7106953</v>
+        <v>7107182</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,12 +9325,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9876,32 +9876,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126893458</v>
+        <v>126890178</v>
       </c>
       <c r="B90" t="n">
-        <v>57817</v>
+        <v>98360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9911,10 +9911,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685383</v>
+        <v>685495</v>
       </c>
       <c r="R90" t="n">
-        <v>7107114</v>
+        <v>7107045</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9949,11 +9949,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9971,7 +9966,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9982,45 +9977,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126890178</v>
+        <v>126890628</v>
       </c>
       <c r="B91" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685495</v>
+        <v>685371</v>
       </c>
       <c r="R91" t="n">
-        <v>7107045</v>
+        <v>7107135</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10067,12 +10062,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10083,10 +10078,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126890190</v>
+        <v>126893493</v>
       </c>
       <c r="B92" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10094,34 +10089,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685223</v>
+        <v>685266</v>
       </c>
       <c r="R92" t="n">
-        <v>7107071</v>
+        <v>7107184</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10168,12 +10163,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10184,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126890625</v>
+        <v>126893458</v>
       </c>
       <c r="B93" t="n">
-        <v>91344</v>
+        <v>57817</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10195,34 +10190,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685539</v>
+        <v>685383</v>
       </c>
       <c r="R93" t="n">
-        <v>7107056</v>
+        <v>7107114</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10257,6 +10252,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10269,12 +10269,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10285,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890628</v>
+        <v>126890190</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10296,34 +10296,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685371</v>
+        <v>685223</v>
       </c>
       <c r="R94" t="n">
-        <v>7107135</v>
+        <v>7107071</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10370,12 +10370,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10386,10 +10386,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890619</v>
+        <v>126890625</v>
       </c>
       <c r="B95" t="n">
-        <v>78772</v>
+        <v>91344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10397,21 +10397,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685146</v>
+        <v>685539</v>
       </c>
       <c r="R95" t="n">
-        <v>7107092</v>
+        <v>7107056</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10487,10 +10487,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893493</v>
+        <v>126890619</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10498,34 +10498,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685266</v>
+        <v>685146</v>
       </c>
       <c r="R96" t="n">
-        <v>7107184</v>
+        <v>7107092</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10572,12 +10572,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10588,10 +10588,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126891632</v>
+        <v>126890099</v>
       </c>
       <c r="B97" t="n">
-        <v>57654</v>
+        <v>80117</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10599,38 +10599,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685370</v>
+        <v>685420</v>
       </c>
       <c r="R97" t="n">
-        <v>7107190</v>
+        <v>7107121</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10665,11 +10661,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Bohål i gran. Långt ner.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10678,16 +10669,31 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10698,10 +10704,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126890099</v>
+        <v>126891632</v>
       </c>
       <c r="B98" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10709,34 +10715,38 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685420</v>
+        <v>685370</v>
       </c>
       <c r="R98" t="n">
-        <v>7107121</v>
+        <v>7107190</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10771,6 +10781,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10779,31 +10794,16 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890155</v>
+        <v>126890614</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,34 +10825,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685312</v>
+        <v>685368</v>
       </c>
       <c r="R99" t="n">
-        <v>7107169</v>
+        <v>7107109</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10899,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126889630</v>
+        <v>126890184</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10926,34 +10926,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685385</v>
+        <v>685257</v>
       </c>
       <c r="R100" t="n">
-        <v>7106995</v>
+        <v>7107113</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11000,12 +11000,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11122,10 +11122,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126893494</v>
+        <v>126890149</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11133,34 +11133,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685374</v>
+        <v>685396</v>
       </c>
       <c r="R102" t="n">
-        <v>7106951</v>
+        <v>7107168</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126890149</v>
+        <v>126890155</v>
       </c>
       <c r="B103" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11258,10 +11258,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685396</v>
+        <v>685312</v>
       </c>
       <c r="R103" t="n">
-        <v>7107168</v>
+        <v>7107169</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126890614</v>
+        <v>126889630</v>
       </c>
       <c r="B104" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,34 +11335,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685368</v>
+        <v>685385</v>
       </c>
       <c r="R104" t="n">
-        <v>7107109</v>
+        <v>7106995</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11409,12 +11409,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126890184</v>
+        <v>126893494</v>
       </c>
       <c r="B105" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11436,34 +11436,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685257</v>
+        <v>685374</v>
       </c>
       <c r="R105" t="n">
-        <v>7107113</v>
+        <v>7106951</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11510,12 +11510,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -13085,7 +13085,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126890154</v>
+        <v>126890158</v>
       </c>
       <c r="B121" t="n">
         <v>79014</v>
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685361</v>
+        <v>685225</v>
       </c>
       <c r="R121" t="n">
-        <v>7107207</v>
+        <v>7107113</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13287,7 +13287,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126890158</v>
+        <v>126890154</v>
       </c>
       <c r="B123" t="n">
         <v>79014</v>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685225</v>
+        <v>685361</v>
       </c>
       <c r="R123" t="n">
-        <v>7107113</v>
+        <v>7107207</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13388,10 +13388,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126890086</v>
+        <v>126893491</v>
       </c>
       <c r="B124" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13399,34 +13399,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685221</v>
+        <v>685369</v>
       </c>
       <c r="R124" t="n">
-        <v>7107115</v>
+        <v>7107086</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13470,30 +13470,15 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13504,10 +13489,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893491</v>
+        <v>126890086</v>
       </c>
       <c r="B125" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13515,34 +13500,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685369</v>
+        <v>685221</v>
       </c>
       <c r="R125" t="n">
-        <v>7107086</v>
+        <v>7107115</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13586,15 +13571,30 @@
       <c r="AG125" t="b">
         <v>0</v>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13605,10 +13605,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893461</v>
+        <v>126890085</v>
       </c>
       <c r="B126" t="n">
-        <v>78681</v>
+        <v>80989</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13616,34 +13616,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685338</v>
+        <v>685222</v>
       </c>
       <c r="R126" t="n">
-        <v>7107092</v>
+        <v>7107058</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13678,30 +13678,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13712,10 +13721,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126890085</v>
+        <v>126893461</v>
       </c>
       <c r="B127" t="n">
-        <v>80989</v>
+        <v>78681</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13723,34 +13732,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685222</v>
+        <v>685338</v>
       </c>
       <c r="R127" t="n">
-        <v>7107058</v>
+        <v>7107092</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13785,39 +13794,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13828,7 +13828,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126889626</v>
+        <v>126890159</v>
       </c>
       <c r="B128" t="n">
         <v>79014</v>
@@ -13857,23 +13857,16 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685337</v>
+        <v>685238</v>
       </c>
       <c r="R128" t="n">
-        <v>7107187</v>
+        <v>7107094</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13914,19 +13907,18 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13937,45 +13929,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126890176</v>
+        <v>126890599</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685413</v>
+        <v>685411</v>
       </c>
       <c r="R129" t="n">
-        <v>7107035</v>
+        <v>7107223</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14022,12 +14014,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14038,45 +14030,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126890159</v>
+        <v>126889639</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685238</v>
+        <v>685328</v>
       </c>
       <c r="R130" t="n">
-        <v>7107094</v>
+        <v>7107189</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14123,12 +14115,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14139,32 +14131,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126889631</v>
+        <v>126889638</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14174,10 +14166,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685348</v>
+        <v>685366</v>
       </c>
       <c r="R131" t="n">
-        <v>7107202</v>
+        <v>7107208</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14240,7 +14232,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126890326</v>
+        <v>126889626</v>
       </c>
       <c r="B132" t="n">
         <v>79014</v>
@@ -14269,16 +14261,23 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685271</v>
+        <v>685337</v>
       </c>
       <c r="R132" t="n">
-        <v>7107170</v>
+        <v>7107187</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14313,29 +14312,25 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14346,45 +14341,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126890599</v>
+        <v>126890176</v>
       </c>
       <c r="B133" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685411</v>
+        <v>685413</v>
       </c>
       <c r="R133" t="n">
-        <v>7107223</v>
+        <v>7107035</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14431,12 +14426,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14447,32 +14442,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126889639</v>
+        <v>126889631</v>
       </c>
       <c r="B134" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14482,10 +14477,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685328</v>
+        <v>685348</v>
       </c>
       <c r="R134" t="n">
-        <v>7107189</v>
+        <v>7107202</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14537,7 +14532,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14548,45 +14543,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126889638</v>
+        <v>126890326</v>
       </c>
       <c r="B135" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685366</v>
+        <v>685271</v>
       </c>
       <c r="R135" t="n">
-        <v>7107208</v>
+        <v>7107170</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14621,6 +14616,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14633,12 +14633,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14957,10 +14957,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126889620</v>
+        <v>126890174</v>
       </c>
       <c r="B139" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14968,34 +14968,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685391</v>
+        <v>685415</v>
       </c>
       <c r="R139" t="n">
-        <v>7107082</v>
+        <v>7107015</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15042,12 +15042,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15058,10 +15058,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126890593</v>
+        <v>126890324</v>
       </c>
       <c r="B140" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15069,34 +15069,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685219</v>
+        <v>685394</v>
       </c>
       <c r="R140" t="n">
-        <v>7107117</v>
+        <v>7107061</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15131,6 +15131,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15143,12 +15148,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15159,10 +15164,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126890174</v>
+        <v>126889620</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15170,34 +15175,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685415</v>
+        <v>685391</v>
       </c>
       <c r="R141" t="n">
-        <v>7107015</v>
+        <v>7107082</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15244,12 +15249,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15260,10 +15265,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126890324</v>
+        <v>126890593</v>
       </c>
       <c r="B142" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15271,34 +15276,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685394</v>
+        <v>685219</v>
       </c>
       <c r="R142" t="n">
-        <v>7107061</v>
+        <v>7107117</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15333,11 +15338,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15350,12 +15350,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126891180</v>
+        <v>126891638</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15680,21 +15680,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15704,10 +15704,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685372</v>
+        <v>685363</v>
       </c>
       <c r="R146" t="n">
-        <v>7106948</v>
+        <v>7107112</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15770,7 +15770,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126890074</v>
+        <v>126891180</v>
       </c>
       <c r="B147" t="n">
         <v>79014</v>
@@ -15801,14 +15801,14 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685303</v>
+        <v>685372</v>
       </c>
       <c r="R147" t="n">
-        <v>7107030</v>
+        <v>7106948</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15855,12 +15855,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15871,10 +15871,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126891638</v>
+        <v>126890074</v>
       </c>
       <c r="B148" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15882,34 +15882,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685363</v>
+        <v>685303</v>
       </c>
       <c r="R148" t="n">
-        <v>7107112</v>
+        <v>7107030</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15956,12 +15956,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126890591</v>
+        <v>126890629</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685370</v>
+        <v>685283</v>
       </c>
       <c r="R2" t="n">
-        <v>7107120</v>
+        <v>7107035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126890629</v>
+        <v>126893460</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685283</v>
+        <v>685477</v>
       </c>
       <c r="R3" t="n">
-        <v>7107035</v>
+        <v>7107122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,6 +849,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -861,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +885,7 @@
         <v>126893464</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893460</v>
+        <v>126891648</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,14 +1019,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685477</v>
+        <v>685260</v>
       </c>
       <c r="R5" t="n">
-        <v>7107122</v>
+        <v>7107165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,7 +1063,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På späd gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126891648</v>
+        <v>126890606</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685260</v>
+        <v>685377</v>
       </c>
       <c r="R6" t="n">
-        <v>7107165</v>
+        <v>7107099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1167,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På späd gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1195,45 +1195,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126890606</v>
+        <v>126891182</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685377</v>
+        <v>685327</v>
       </c>
       <c r="R7" t="n">
-        <v>7107099</v>
+        <v>7107186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,18 +1282,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1296,53 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126891182</v>
+        <v>126893467</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685327</v>
+        <v>685256</v>
       </c>
       <c r="R8" t="n">
-        <v>7107186</v>
+        <v>7107058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,25 +1378,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1406,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893467</v>
+        <v>126890591</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,34 +1422,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685256</v>
+        <v>685370</v>
       </c>
       <c r="R9" t="n">
-        <v>7107058</v>
+        <v>7107120</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,11 +1484,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1496,12 +1496,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1515,7 +1515,7 @@
         <v>126890071</v>
       </c>
       <c r="B10" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126890148</v>
+        <v>126889633</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,34 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685419</v>
+        <v>685223</v>
       </c>
       <c r="R11" t="n">
-        <v>7107117</v>
+        <v>7107049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1713,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126889633</v>
+        <v>126890100</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>75142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,34 +1740,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685223</v>
+        <v>685405</v>
       </c>
       <c r="R12" t="n">
-        <v>7107049</v>
+        <v>7107108</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,15 +1811,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1830,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126890180</v>
+        <v>126890191</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>78776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,7 +1880,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685259</v>
+        <v>685257</v>
       </c>
       <c r="R13" t="n">
         <v>7107109</v>
@@ -1901,11 +1916,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890191</v>
+        <v>126890148</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>91348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,21 +1957,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685257</v>
+        <v>685419</v>
       </c>
       <c r="R14" t="n">
-        <v>7107109</v>
+        <v>7107117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890587</v>
+        <v>126890180</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,14 +2078,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685398</v>
+        <v>685259</v>
       </c>
       <c r="R15" t="n">
-        <v>7106998</v>
+        <v>7107109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,6 +2120,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2122,12 +2137,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2138,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890100</v>
+        <v>126890587</v>
       </c>
       <c r="B16" t="n">
-        <v>75138</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685405</v>
+        <v>685398</v>
       </c>
       <c r="R16" t="n">
-        <v>7107108</v>
+        <v>7106998</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,30 +2235,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2257,7 +2257,7 @@
         <v>126890092</v>
       </c>
       <c r="B17" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>126890166</v>
       </c>
       <c r="B18" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126890082</v>
       </c>
       <c r="B19" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890316</v>
+        <v>126890200</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>77996</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2583,34 +2583,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685410</v>
+        <v>685218</v>
       </c>
       <c r="R20" t="n">
-        <v>7106991</v>
+        <v>7107060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,11 +2645,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2662,12 +2657,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2678,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891185</v>
+        <v>126890316</v>
       </c>
       <c r="B21" t="n">
-        <v>78420</v>
+        <v>79636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,21 +2684,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685417</v>
+        <v>685410</v>
       </c>
       <c r="R21" t="n">
-        <v>7106968</v>
+        <v>7106991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,25 +2746,29 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2780,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126890200</v>
+        <v>126891185</v>
       </c>
       <c r="B22" t="n">
-        <v>77992</v>
+        <v>78424</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2791,34 +2790,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685218</v>
+        <v>685417</v>
       </c>
       <c r="R22" t="n">
-        <v>7107060</v>
+        <v>7106968</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,18 +2858,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2884,7 +2884,7 @@
         <v>126890630</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126890098</v>
+        <v>126891637</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,34 +2993,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685407</v>
+        <v>685419</v>
       </c>
       <c r="R24" t="n">
-        <v>7107134</v>
+        <v>7107106</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,30 +3064,15 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3098,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890075</v>
+        <v>126890098</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3109,21 +3094,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685334</v>
+        <v>685407</v>
       </c>
       <c r="R25" t="n">
-        <v>7107003</v>
+        <v>7107134</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,6 +3164,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3202,7 +3202,7 @@
         <v>126890101</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>126890156</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890328</v>
+        <v>126890075</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,14 +3432,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685268</v>
+        <v>685334</v>
       </c>
       <c r="R28" t="n">
-        <v>7107110</v>
+        <v>7107003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,12 +3486,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890201</v>
+        <v>126890328</v>
       </c>
       <c r="B29" t="n">
-        <v>78420</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,34 +3513,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685214</v>
+        <v>685268</v>
       </c>
       <c r="R29" t="n">
-        <v>7107061</v>
+        <v>7107110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3587,12 +3587,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126891637</v>
+        <v>126890201</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>78424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,34 +3614,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685419</v>
+        <v>685214</v>
       </c>
       <c r="R30" t="n">
-        <v>7107106</v>
+        <v>7107061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,12 +3688,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3707,7 +3707,7 @@
         <v>126890616</v>
       </c>
       <c r="B31" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>126890146</v>
       </c>
       <c r="B32" t="n">
-        <v>91799</v>
+        <v>91803</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>126890627</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126891394</v>
+        <v>126890081</v>
       </c>
       <c r="B34" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4026,34 +4026,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685267</v>
+        <v>685215</v>
       </c>
       <c r="R34" t="n">
-        <v>7107032</v>
+        <v>7107071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,12 +4100,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4116,10 +4116,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126890081</v>
+        <v>126890103</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685215</v>
+        <v>685370</v>
       </c>
       <c r="R35" t="n">
-        <v>7107071</v>
+        <v>7107029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126890103</v>
+        <v>126891394</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4228,34 +4228,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685370</v>
+        <v>685267</v>
       </c>
       <c r="R36" t="n">
-        <v>7107029</v>
+        <v>7107032</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4302,12 +4302,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4318,10 +4318,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890615</v>
+        <v>126891640</v>
       </c>
       <c r="B37" t="n">
-        <v>80153</v>
+        <v>58031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,34 +4329,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685399</v>
+        <v>685539</v>
       </c>
       <c r="R37" t="n">
-        <v>7107027</v>
+        <v>7107065</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,6 +4399,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4403,12 +4416,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4419,10 +4432,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890196</v>
+        <v>126891173</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4430,34 +4443,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685270</v>
+        <v>685248</v>
       </c>
       <c r="R38" t="n">
-        <v>7107166</v>
+        <v>7107014</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,12 +4517,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4520,10 +4533,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891178</v>
+        <v>126891170</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4531,21 +4544,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4555,10 +4568,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685220</v>
+        <v>685426</v>
       </c>
       <c r="R39" t="n">
-        <v>7107060</v>
+        <v>7106971</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4621,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891170</v>
+        <v>126891178</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4632,21 +4645,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4656,10 +4669,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685426</v>
+        <v>685220</v>
       </c>
       <c r="R40" t="n">
-        <v>7106971</v>
+        <v>7107060</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,10 +4735,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126891640</v>
+        <v>126890615</v>
       </c>
       <c r="B41" t="n">
-        <v>58027</v>
+        <v>80157</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4733,42 +4746,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685539</v>
+        <v>685399</v>
       </c>
       <c r="R41" t="n">
-        <v>7107065</v>
+        <v>7107027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,11 +4808,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4820,12 +4820,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891173</v>
+        <v>126890196</v>
       </c>
       <c r="B42" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4847,34 +4847,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685248</v>
+        <v>685270</v>
       </c>
       <c r="R42" t="n">
-        <v>7107014</v>
+        <v>7107166</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4921,12 +4921,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4937,45 +4937,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126891169</v>
+        <v>126890631</v>
       </c>
       <c r="B43" t="n">
-        <v>91291</v>
+        <v>78685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685394</v>
+        <v>685215</v>
       </c>
       <c r="R43" t="n">
-        <v>7107163</v>
+        <v>7107084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,12 +5022,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126890325</v>
+        <v>126889641</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685363</v>
+        <v>685348</v>
       </c>
       <c r="R44" t="n">
-        <v>7107208</v>
+        <v>7106970</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,11 +5111,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5128,12 +5123,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5144,10 +5139,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126890169</v>
+        <v>126890325</v>
       </c>
       <c r="B45" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5155,34 +5150,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685422</v>
+        <v>685363</v>
       </c>
       <c r="R45" t="n">
-        <v>7107111</v>
+        <v>7107208</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5217,6 +5212,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Jätte mycket i hela det fuktigare område på de senvuxna granarna</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5229,12 +5229,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5245,45 +5245,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126890087</v>
+        <v>126891169</v>
       </c>
       <c r="B46" t="n">
-        <v>79632</v>
+        <v>91295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685222</v>
+        <v>685394</v>
       </c>
       <c r="R46" t="n">
-        <v>7107114</v>
+        <v>7107163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5327,30 +5327,15 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5364,7 +5349,7 @@
         <v>126893463</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5467,10 +5452,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890147</v>
+        <v>126890169</v>
       </c>
       <c r="B48" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5502,10 +5487,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685392</v>
+        <v>685422</v>
       </c>
       <c r="R48" t="n">
-        <v>7107087</v>
+        <v>7107111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5568,10 +5553,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890631</v>
+        <v>126890087</v>
       </c>
       <c r="B49" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,34 +5564,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685215</v>
+        <v>685222</v>
       </c>
       <c r="R49" t="n">
-        <v>7107084</v>
+        <v>7107114</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5650,15 +5635,30 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126889641</v>
+        <v>126890147</v>
       </c>
       <c r="B50" t="n">
-        <v>78681</v>
+        <v>78776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5680,34 +5680,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685348</v>
+        <v>685392</v>
       </c>
       <c r="R50" t="n">
-        <v>7106970</v>
+        <v>7107087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5754,12 +5754,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889632</v>
+        <v>126890590</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5781,34 +5781,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685270</v>
+        <v>685371</v>
       </c>
       <c r="R51" t="n">
-        <v>7107186</v>
+        <v>7107135</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5855,12 +5855,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5871,10 +5871,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126890590</v>
+        <v>126891181</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5882,34 +5882,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685371</v>
+        <v>685396</v>
       </c>
       <c r="R52" t="n">
-        <v>7107135</v>
+        <v>7106961</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5956,12 +5956,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5972,10 +5972,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126890329</v>
+        <v>126889632</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6003,14 +6003,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685287</v>
+        <v>685270</v>
       </c>
       <c r="R53" t="n">
-        <v>7107034</v>
+        <v>7107186</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6045,11 +6045,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6062,12 +6057,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6078,10 +6073,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126890083</v>
+        <v>126890329</v>
       </c>
       <c r="B54" t="n">
-        <v>78420</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,34 +6084,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685222</v>
+        <v>685287</v>
       </c>
       <c r="R54" t="n">
-        <v>7107061</v>
+        <v>7107034</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6151,6 +6146,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6159,31 +6159,16 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6194,10 +6179,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891181</v>
+        <v>126890083</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>78424</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6205,34 +6190,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685396</v>
+        <v>685222</v>
       </c>
       <c r="R55" t="n">
-        <v>7106961</v>
+        <v>7107061</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6276,15 +6261,30 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6298,7 +6298,7 @@
         <v>126893459</v>
       </c>
       <c r="B56" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>126877810</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>126893490</v>
       </c>
       <c r="B58" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126890597</v>
+        <v>126890189</v>
       </c>
       <c r="B59" t="n">
-        <v>57817</v>
+        <v>80993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6622,42 +6622,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685576</v>
+        <v>685256</v>
       </c>
       <c r="R59" t="n">
-        <v>7107009</v>
+        <v>7107175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6704,12 +6696,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6720,10 +6712,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890097</v>
+        <v>126891393</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,34 +6723,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685305</v>
+        <v>685263</v>
       </c>
       <c r="R60" t="n">
-        <v>7107176</v>
+        <v>7107150</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6802,30 +6794,15 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6836,10 +6813,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126891393</v>
+        <v>126890586</v>
       </c>
       <c r="B61" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,14 +6844,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685263</v>
+        <v>685419</v>
       </c>
       <c r="R61" t="n">
-        <v>7107150</v>
+        <v>7107080</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6921,12 +6898,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6937,10 +6914,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890586</v>
+        <v>126890592</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6972,10 +6949,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685419</v>
+        <v>685368</v>
       </c>
       <c r="R62" t="n">
-        <v>7107080</v>
+        <v>7107109</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7038,10 +7015,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890618</v>
+        <v>126890597</v>
       </c>
       <c r="B63" t="n">
-        <v>78772</v>
+        <v>57821</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7049,34 +7026,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685398</v>
+        <v>685576</v>
       </c>
       <c r="R63" t="n">
-        <v>7106998</v>
+        <v>7107009</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7139,10 +7124,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126890592</v>
+        <v>126890185</v>
       </c>
       <c r="B64" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,34 +7135,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685368</v>
+        <v>685259</v>
       </c>
       <c r="R64" t="n">
-        <v>7107109</v>
+        <v>7107105</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7209,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,10 +7225,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126890185</v>
+        <v>126891174</v>
       </c>
       <c r="B65" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7271,14 +7256,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685259</v>
+        <v>685430</v>
       </c>
       <c r="R65" t="n">
-        <v>7107105</v>
+        <v>7106963</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7310,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7341,10 +7326,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126891174</v>
+        <v>126890097</v>
       </c>
       <c r="B66" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7337,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685430</v>
+        <v>685305</v>
       </c>
       <c r="R66" t="n">
-        <v>7106963</v>
+        <v>7107176</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7423,15 +7408,30 @@
       <c r="AG66" t="b">
         <v>0</v>
       </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126890189</v>
+        <v>126890618</v>
       </c>
       <c r="B67" t="n">
-        <v>80989</v>
+        <v>78776</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,34 +7453,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685256</v>
+        <v>685398</v>
       </c>
       <c r="R67" t="n">
-        <v>7107175</v>
+        <v>7106998</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,12 +7527,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7543,45 +7543,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889640</v>
+        <v>126890188</v>
       </c>
       <c r="B68" t="n">
-        <v>78681</v>
+        <v>57765</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685311</v>
+        <v>685274</v>
       </c>
       <c r="R68" t="n">
-        <v>7107020</v>
+        <v>7107181</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,12 +7640,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7644,45 +7656,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890595</v>
+        <v>126890617</v>
       </c>
       <c r="B69" t="n">
-        <v>91326</v>
+        <v>58031</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685417</v>
+        <v>685406</v>
       </c>
       <c r="R69" t="n">
-        <v>7107135</v>
+        <v>7107034</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7745,45 +7765,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890173</v>
+        <v>126890620</v>
       </c>
       <c r="B70" t="n">
-        <v>91487</v>
+        <v>78776</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685398</v>
+        <v>685161</v>
       </c>
       <c r="R70" t="n">
-        <v>7106958</v>
+        <v>7107091</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7830,12 +7850,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7846,10 +7866,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890620</v>
+        <v>126890091</v>
       </c>
       <c r="B71" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7877,14 +7897,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685161</v>
+        <v>685268</v>
       </c>
       <c r="R71" t="n">
-        <v>7107091</v>
+        <v>7107185</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7928,15 +7948,30 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7947,10 +7982,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126890091</v>
+        <v>126889640</v>
       </c>
       <c r="B72" t="n">
-        <v>78772</v>
+        <v>78685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7958,34 +7993,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685268</v>
+        <v>685311</v>
       </c>
       <c r="R72" t="n">
-        <v>7107185</v>
+        <v>7107020</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8029,30 +8064,15 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8063,57 +8083,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126890188</v>
+        <v>126890173</v>
       </c>
       <c r="B73" t="n">
-        <v>57761</v>
+        <v>91491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685274</v>
+        <v>685398</v>
       </c>
       <c r="R73" t="n">
-        <v>7107181</v>
+        <v>7106958</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8176,53 +8184,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890617</v>
+        <v>126890595</v>
       </c>
       <c r="B74" t="n">
-        <v>58027</v>
+        <v>91330</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685406</v>
+        <v>685417</v>
       </c>
       <c r="R74" t="n">
-        <v>7107034</v>
+        <v>7107135</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8288,7 +8288,7 @@
         <v>126890157</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>126890197</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8492,45 +8492,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126891642</v>
+        <v>126890094</v>
       </c>
       <c r="B77" t="n">
-        <v>78772</v>
+        <v>57483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>102976</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685361</v>
+        <v>685274</v>
       </c>
       <c r="R77" t="n">
-        <v>7107114</v>
+        <v>7107182</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8565,11 +8570,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På kolad silverhögstubbe</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8582,12 +8582,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8598,45 +8598,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126893466</v>
+        <v>126890088</v>
       </c>
       <c r="B78" t="n">
-        <v>78772</v>
+        <v>91295</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685256</v>
+        <v>685251</v>
       </c>
       <c r="R78" t="n">
-        <v>7107043</v>
+        <v>7107154</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8671,30 +8671,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8708,7 +8717,7 @@
         <v>126890588</v>
       </c>
       <c r="B79" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8806,10 +8815,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890102</v>
+        <v>126891642</v>
       </c>
       <c r="B80" t="n">
-        <v>57657</v>
+        <v>78776</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8817,39 +8826,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685393</v>
+        <v>685361</v>
       </c>
       <c r="R80" t="n">
-        <v>7107081</v>
+        <v>7107114</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8884,6 +8888,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På kolad silverhögstubbe</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8896,12 +8905,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8912,10 +8921,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890080</v>
+        <v>126893466</v>
       </c>
       <c r="B81" t="n">
-        <v>57657</v>
+        <v>78776</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8923,39 +8932,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685217</v>
+        <v>685256</v>
       </c>
       <c r="R81" t="n">
-        <v>7107067</v>
+        <v>7107043</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8990,24 +8994,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9018,10 +9028,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126890594</v>
+        <v>126890102</v>
       </c>
       <c r="B82" t="n">
-        <v>79603</v>
+        <v>57661</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9029,34 +9039,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685372</v>
+        <v>685393</v>
       </c>
       <c r="R82" t="n">
-        <v>7106953</v>
+        <v>7107081</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,12 +9118,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9119,45 +9134,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126890088</v>
+        <v>126890080</v>
       </c>
       <c r="B83" t="n">
-        <v>91291</v>
+        <v>57661</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685251</v>
+        <v>685217</v>
       </c>
       <c r="R83" t="n">
-        <v>7107154</v>
+        <v>7107067</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9200,21 +9220,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9235,50 +9240,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890094</v>
+        <v>126890594</v>
       </c>
       <c r="B84" t="n">
-        <v>57479</v>
+        <v>79607</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102976</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685274</v>
+        <v>685372</v>
       </c>
       <c r="R84" t="n">
-        <v>7107182</v>
+        <v>7106953</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,12 +9325,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9341,45 +9341,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890598</v>
+        <v>126890084</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>77996</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685154</v>
+        <v>685223</v>
       </c>
       <c r="R85" t="n">
-        <v>7107066</v>
+        <v>7107061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9423,15 +9423,30 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9442,45 +9457,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126890084</v>
+        <v>126890598</v>
       </c>
       <c r="B86" t="n">
-        <v>77992</v>
+        <v>80150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685223</v>
+        <v>685154</v>
       </c>
       <c r="R86" t="n">
-        <v>7107061</v>
+        <v>7107066</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9524,30 +9539,15 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9561,7 +9561,7 @@
         <v>126890078</v>
       </c>
       <c r="B87" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>126890612</v>
       </c>
       <c r="B88" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>126890611</v>
       </c>
       <c r="B89" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>126890178</v>
       </c>
       <c r="B90" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126890628</v>
+        <v>126890625</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>91348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9988,21 +9988,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685371</v>
+        <v>685539</v>
       </c>
       <c r="R91" t="n">
-        <v>7107135</v>
+        <v>7107056</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,7 +10081,7 @@
         <v>126893493</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893458</v>
+        <v>126890628</v>
       </c>
       <c r="B93" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10190,34 +10190,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685383</v>
+        <v>685371</v>
       </c>
       <c r="R93" t="n">
-        <v>7107114</v>
+        <v>7107135</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10252,11 +10252,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10269,12 +10264,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10285,10 +10280,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126890190</v>
+        <v>126890099</v>
       </c>
       <c r="B94" t="n">
-        <v>80989</v>
+        <v>80121</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10296,34 +10291,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685223</v>
+        <v>685420</v>
       </c>
       <c r="R94" t="n">
-        <v>7107071</v>
+        <v>7107121</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10367,15 +10362,30 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10386,10 +10396,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126890625</v>
+        <v>126891632</v>
       </c>
       <c r="B95" t="n">
-        <v>91344</v>
+        <v>57658</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10397,34 +10407,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685539</v>
+        <v>685370</v>
       </c>
       <c r="R95" t="n">
-        <v>7107056</v>
+        <v>7107190</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10459,6 +10473,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Bohål i gran. Långt ner.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10471,12 +10490,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10487,10 +10506,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126890619</v>
+        <v>126890190</v>
       </c>
       <c r="B96" t="n">
-        <v>78772</v>
+        <v>80993</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10498,34 +10517,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685146</v>
+        <v>685223</v>
       </c>
       <c r="R96" t="n">
-        <v>7107092</v>
+        <v>7107071</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10572,12 +10591,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10588,10 +10607,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126890099</v>
+        <v>126890619</v>
       </c>
       <c r="B97" t="n">
-        <v>80117</v>
+        <v>78776</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10599,34 +10618,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685420</v>
+        <v>685146</v>
       </c>
       <c r="R97" t="n">
-        <v>7107121</v>
+        <v>7107092</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10670,30 +10689,15 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10704,10 +10708,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126891632</v>
+        <v>126893458</v>
       </c>
       <c r="B98" t="n">
-        <v>57654</v>
+        <v>57821</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10715,38 +10719,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685370</v>
+        <v>685383</v>
       </c>
       <c r="R98" t="n">
-        <v>7107190</v>
+        <v>7107114</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Bohål i gran. Långt ner.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10798,12 +10798,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126890614</v>
+        <v>126890149</v>
       </c>
       <c r="B99" t="n">
-        <v>78773</v>
+        <v>91348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10825,34 +10825,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685368</v>
+        <v>685396</v>
       </c>
       <c r="R99" t="n">
-        <v>7107109</v>
+        <v>7107168</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10899,12 +10899,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126890184</v>
+        <v>126890155</v>
       </c>
       <c r="B100" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10926,21 +10926,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685257</v>
+        <v>685312</v>
       </c>
       <c r="R100" t="n">
-        <v>7107113</v>
+        <v>7107169</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11019,7 +11019,7 @@
         <v>126890323</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11122,10 +11122,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126890149</v>
+        <v>126893494</v>
       </c>
       <c r="B102" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11133,34 +11133,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685396</v>
+        <v>685374</v>
       </c>
       <c r="R102" t="n">
-        <v>7107168</v>
+        <v>7106951</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11207,12 +11207,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11223,10 +11223,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126890155</v>
+        <v>126889630</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11254,14 +11254,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685312</v>
+        <v>685385</v>
       </c>
       <c r="R103" t="n">
-        <v>7107169</v>
+        <v>7106995</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,12 +11308,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126889630</v>
+        <v>126890614</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11335,34 +11335,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685385</v>
+        <v>685368</v>
       </c>
       <c r="R104" t="n">
-        <v>7106995</v>
+        <v>7107109</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11409,12 +11409,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Eleonor Johansson, Anne Siivola, Alexandra Astafourova, Anne Siivola, Beke Regelin, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Carl Jansson, Jennica Andersson, kristina stenmarck, Elin Kannerby</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126893494</v>
+        <v>126890184</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11436,34 +11436,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685374</v>
+        <v>685257</v>
       </c>
       <c r="R105" t="n">
-        <v>7106951</v>
+        <v>7107113</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11510,12 +11510,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11526,45 +11526,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126890161</v>
+        <v>126890633</v>
       </c>
       <c r="B106" t="n">
-        <v>91291</v>
+        <v>75134</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685360</v>
+        <v>685311</v>
       </c>
       <c r="R106" t="n">
-        <v>7107179</v>
+        <v>7107013</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11599,11 +11599,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11616,12 +11611,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11632,10 +11627,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126891176</v>
+        <v>126890093</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>80993</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11643,34 +11638,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685352</v>
+        <v>685268</v>
       </c>
       <c r="R107" t="n">
-        <v>7107016</v>
+        <v>7107183</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11714,15 +11709,30 @@
       <c r="AG107" t="b">
         <v>0</v>
       </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11733,45 +11743,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126890089</v>
+        <v>126890161</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685254</v>
+        <v>685360</v>
       </c>
       <c r="R108" t="n">
-        <v>7107171</v>
+        <v>7107179</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11806,6 +11816,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11818,12 +11833,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11834,10 +11849,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126891177</v>
+        <v>126891176</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11869,10 +11884,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685232</v>
+        <v>685352</v>
       </c>
       <c r="R109" t="n">
-        <v>7107114</v>
+        <v>7107016</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11935,10 +11950,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126890327</v>
+        <v>126890089</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11966,14 +11981,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685267</v>
+        <v>685254</v>
       </c>
       <c r="R110" t="n">
-        <v>7107149</v>
+        <v>7107171</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12008,11 +12023,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12025,12 +12035,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12041,10 +12051,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893465</v>
+        <v>126891177</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12072,14 +12082,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>685211</v>
+        <v>685232</v>
       </c>
       <c r="R111" t="n">
-        <v>7107147</v>
+        <v>7107114</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12114,11 +12124,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12131,12 +12136,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12147,10 +12152,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126889621</v>
+        <v>126890327</v>
       </c>
       <c r="B112" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12158,34 +12163,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685397</v>
+        <v>685267</v>
       </c>
       <c r="R112" t="n">
-        <v>7107085</v>
+        <v>7107149</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12220,6 +12225,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12232,12 +12242,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12248,10 +12258,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126890633</v>
+        <v>126893465</v>
       </c>
       <c r="B113" t="n">
-        <v>75130</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12259,34 +12269,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685311</v>
+        <v>685211</v>
       </c>
       <c r="R113" t="n">
-        <v>7107013</v>
+        <v>7107147</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12321,6 +12331,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12333,12 +12348,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12349,10 +12364,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126890093</v>
+        <v>126890589</v>
       </c>
       <c r="B114" t="n">
-        <v>80989</v>
+        <v>79636</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12360,34 +12375,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685268</v>
+        <v>685289</v>
       </c>
       <c r="R114" t="n">
-        <v>7107183</v>
+        <v>7107194</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12431,30 +12446,15 @@
       <c r="AG114" t="b">
         <v>0</v>
       </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12465,10 +12465,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126890589</v>
+        <v>126890317</v>
       </c>
       <c r="B115" t="n">
-        <v>79632</v>
+        <v>57661</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12476,34 +12476,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685289</v>
+        <v>685420</v>
       </c>
       <c r="R115" t="n">
-        <v>7107194</v>
+        <v>7107002</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12538,6 +12538,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färsk ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -12550,12 +12555,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12566,10 +12571,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126890317</v>
+        <v>126889621</v>
       </c>
       <c r="B116" t="n">
-        <v>57657</v>
+        <v>78777</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,34 +12582,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685420</v>
+        <v>685397</v>
       </c>
       <c r="R116" t="n">
-        <v>7107002</v>
+        <v>7107085</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12639,11 +12644,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Färsk ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -12656,12 +12656,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12672,45 +12672,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126890608</v>
+        <v>126890073</v>
       </c>
       <c r="B117" t="n">
-        <v>79038</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685410</v>
+        <v>685306</v>
       </c>
       <c r="R117" t="n">
-        <v>7106989</v>
+        <v>7107003</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12757,12 +12757,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12773,45 +12773,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126890073</v>
+        <v>126890608</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79042</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685306</v>
+        <v>685410</v>
       </c>
       <c r="R118" t="n">
-        <v>7107003</v>
+        <v>7106989</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12858,12 +12858,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12877,7 +12877,7 @@
         <v>126891179</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>126891631</v>
       </c>
       <c r="B120" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13085,10 +13085,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126890158</v>
+        <v>126889634</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13116,14 +13116,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685225</v>
+        <v>685358</v>
       </c>
       <c r="R121" t="n">
-        <v>7107113</v>
+        <v>7106974</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13170,12 +13170,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13186,10 +13186,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126889634</v>
+        <v>126890158</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13217,14 +13217,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685358</v>
+        <v>685225</v>
       </c>
       <c r="R122" t="n">
-        <v>7106974</v>
+        <v>7107113</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13271,12 +13271,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13290,7 +13290,7 @@
         <v>126890154</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>126893491</v>
       </c>
       <c r="B124" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>126890086</v>
       </c>
       <c r="B125" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13605,10 +13605,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126890085</v>
+        <v>126890159</v>
       </c>
       <c r="B126" t="n">
-        <v>80989</v>
+        <v>79018</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13616,34 +13616,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685222</v>
+        <v>685238</v>
       </c>
       <c r="R126" t="n">
-        <v>7107058</v>
+        <v>7107094</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13687,30 +13687,15 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13721,10 +13706,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126893461</v>
+        <v>126889626</v>
       </c>
       <c r="B127" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13732,34 +13717,41 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685338</v>
+        <v>685337</v>
       </c>
       <c r="R127" t="n">
-        <v>7107092</v>
+        <v>7107187</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13794,11 +13786,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13812,12 +13799,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13828,10 +13815,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126890159</v>
+        <v>126889631</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13859,14 +13846,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685238</v>
+        <v>685348</v>
       </c>
       <c r="R128" t="n">
-        <v>7107094</v>
+        <v>7107202</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13913,12 +13900,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13929,45 +13916,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126890599</v>
+        <v>126890176</v>
       </c>
       <c r="B129" t="n">
-        <v>98464</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685411</v>
+        <v>685413</v>
       </c>
       <c r="R129" t="n">
-        <v>7107223</v>
+        <v>7107035</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14014,12 +14001,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14030,45 +14017,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126889639</v>
+        <v>126890326</v>
       </c>
       <c r="B130" t="n">
-        <v>98360</v>
+        <v>79018</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685328</v>
+        <v>685271</v>
       </c>
       <c r="R130" t="n">
-        <v>7107189</v>
+        <v>7107170</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14103,6 +14090,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -14115,12 +14107,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14131,45 +14123,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126889638</v>
+        <v>126893461</v>
       </c>
       <c r="B131" t="n">
-        <v>98360</v>
+        <v>78685</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685366</v>
+        <v>685338</v>
       </c>
       <c r="R131" t="n">
-        <v>7107208</v>
+        <v>7107092</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14204,24 +14196,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14232,10 +14230,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126889626</v>
+        <v>126890085</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>80993</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14243,41 +14241,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685337</v>
+        <v>685222</v>
       </c>
       <c r="R132" t="n">
-        <v>7107187</v>
+        <v>7107058</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14318,19 +14309,33 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14341,45 +14346,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126890176</v>
+        <v>126889638</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685413</v>
+        <v>685366</v>
       </c>
       <c r="R133" t="n">
-        <v>7107035</v>
+        <v>7107208</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14426,12 +14431,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14442,32 +14447,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126889631</v>
+        <v>126889639</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14477,10 +14482,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685348</v>
+        <v>685328</v>
       </c>
       <c r="R134" t="n">
-        <v>7107202</v>
+        <v>7107189</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14532,7 +14537,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Hedda Bring, Eleonor Johansson, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Elin Kannerby, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14543,45 +14548,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126890326</v>
+        <v>126890599</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>98468</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685271</v>
+        <v>685411</v>
       </c>
       <c r="R135" t="n">
-        <v>7107170</v>
+        <v>7107223</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14616,11 +14621,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14633,12 +14633,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14652,7 +14652,7 @@
         <v>126889622</v>
       </c>
       <c r="B136" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>126890613</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>126893468</v>
       </c>
       <c r="B138" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>126890174</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>126890324</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>126889620</v>
       </c>
       <c r="B141" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>126890593</v>
       </c>
       <c r="B142" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15366,10 +15366,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126890162</v>
+        <v>126891638</v>
       </c>
       <c r="B143" t="n">
-        <v>91326</v>
+        <v>78777</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15377,34 +15377,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685401</v>
+        <v>685363</v>
       </c>
       <c r="R143" t="n">
-        <v>7107105</v>
+        <v>7107112</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15467,10 +15467,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126890622</v>
+        <v>126890162</v>
       </c>
       <c r="B144" t="n">
-        <v>78772</v>
+        <v>91330</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15478,34 +15478,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685368</v>
+        <v>685401</v>
       </c>
       <c r="R144" t="n">
-        <v>7107109</v>
+        <v>7107105</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15552,12 +15552,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15568,10 +15568,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126890621</v>
+        <v>126890622</v>
       </c>
       <c r="B145" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15603,10 +15603,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685370</v>
+        <v>685368</v>
       </c>
       <c r="R145" t="n">
-        <v>7107120</v>
+        <v>7107109</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15669,10 +15669,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126891638</v>
+        <v>126890621</v>
       </c>
       <c r="B146" t="n">
-        <v>78773</v>
+        <v>78776</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15680,34 +15680,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685363</v>
+        <v>685370</v>
       </c>
       <c r="R146" t="n">
-        <v>7107112</v>
+        <v>7107120</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15754,12 +15754,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15773,7 +15773,7 @@
         <v>126891180</v>
       </c>
       <c r="B147" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>126890074</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 19688-2021 artfynd.xlsx
+++ b/artfynd/A 19688-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126890629</v>
+        <v>126890591</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685283</v>
+        <v>685370</v>
       </c>
       <c r="R2" t="n">
-        <v>7107035</v>
+        <v>7107120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126893460</v>
+        <v>126891648</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -807,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685477</v>
+        <v>685260</v>
       </c>
       <c r="R3" t="n">
-        <v>7107122</v>
+        <v>7107165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>På späd gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,12 +866,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Gunilla R Burke</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -882,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893464</v>
+        <v>126890629</v>
       </c>
       <c r="B4" t="n">
         <v>79018</v>
@@ -913,14 +913,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685240</v>
+        <v>685283</v>
       </c>
       <c r="R4" t="n">
-        <v>7107184</v>
+        <v>7107035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -972,12 +967,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126891648</v>
+        <v>126893460</v>
       </c>
       <c r="B5" t="n">
         <v>79018</v>
@@ -1019,14 +1014,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685260</v>
+        <v>685477</v>
       </c>
       <c r="R5" t="n">
-        <v>7107165</v>
+        <v>7107122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1058,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På späd gran</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,12 +1073,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1094,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126890606</v>
+        <v>126893464</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685377</v>
+        <v>685240</v>
       </c>
       <c r="R6" t="n">
-        <v>7107099</v>
+        <v>7107184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1162,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1179,12 +1179,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1195,53 +1195,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126891182</v>
+        <v>126890606</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685327</v>
+        <v>685377</v>
       </c>
       <c r="R7" t="n">
-        <v>7107186</v>
+        <v>7107099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,19 +1274,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1305,45 +1296,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893467</v>
+        <v>126891182</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685256</v>
+        <v>685327</v>
       </c>
       <c r="R8" t="n">
-        <v>7107058</v>
+        <v>7107186</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,29 +1377,25 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1411,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126890591</v>
+        <v>126893467</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,34 +1417,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685370</v>
+        <v>685256</v>
       </c>
       <c r="R9" t="n">
-        <v>7107120</v>
+        <v>7107058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,6 +1479,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1496,12 +1496,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Eleonor Johansson, Beke Regelin, Elin Kannerby, Hedda Bring, Gunilla R Burke, Lars-Erik Nilsson, Anne Siivola, Jennica Andersson, kristina stenmarck, Torbjörn Söderquist, Lotta Ihse, Carl Jansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126889633</v>
+        <v>126890148</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,34 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Rödåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685223</v>
+        <v>685419</v>
       </c>
       <c r="R11" t="n">
-        <v>7107049</v>
+        <v>7107117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1713,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hedda Bring</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126890100</v>
+        <v>126890180</v>
       </c>
       <c r="B12" t="n">
-        <v>75142</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,34 +1740,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685405</v>
+        <v>685259</v>
       </c>
       <c r="R12" t="n">
-        <v>7107108</v>
+        <v>7107109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,6 +1802,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Artnamn</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,31 +1815,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1946,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126890148</v>
+        <v>126890587</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,34 +1947,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685419</v>
+        <v>685398</v>
       </c>
       <c r="R14" t="n">
-        <v>7107117</v>
+        <v>7106998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2021,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2047,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126890180</v>
+        <v>126890100</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>75142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,34 +2048,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685259</v>
+        <v>685405</v>
       </c>
       <c r="R15" t="n">
-        <v>7107109</v>
+        <v>7107108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,11 +2110,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Artnamn</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2133,16 +2118,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126890587</v>
+        <v>126890092</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685398</v>
+        <v>685268</v>
       </c>
       <c r="R16" t="n">
-        <v>7106998</v>
+        <v>7107182</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,15 +2235,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2254,7 +2269,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126890092</v>
+        <v>126890166</v>
       </c>
       <c r="B17" t="n">
         <v>78777</v>
@@ -2285,14 +2300,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685268</v>
+        <v>685415</v>
       </c>
       <c r="R17" t="n">
-        <v>7107182</v>
+        <v>7107111</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,30 +2351,15 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126890166</v>
+        <v>126889633</v>
       </c>
       <c r="B18" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,34 +2381,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Rödåberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685415</v>
+        <v>685223</v>
       </c>
       <c r="R18" t="n">
-        <v>7107111</v>
+        <v>7107049</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,12 +2455,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Hedda Bring</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Hedda Bring, Jennica Andersson, Torbjörn Söderquist, Alexandra Astafourova, Anne Siivola, Beke Regelin, Carl Jansson, Eleonor Johansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Lotta Ihse</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126890200</v>
+        <v>126890316</v>
       </c>
       <c r="B20" t="n">
-        <v>77996</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2583,34 +2583,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Lill-Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685218</v>
+        <v>685410</v>
       </c>
       <c r="R20" t="n">
-        <v>7107060</v>
+        <v>7106991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,6 +2645,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På stor torraka med brännspår</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2657,12 +2662,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Beke Regelin, Torbjörn Söderquist, Lotta Ihse, Hedda Bring, Anne Siivola, Lars-Erik Nilsson, kristina stenmarck, Gunilla R Burke, Elin Kannerby, Carl Jansson, Eleonor Johansson, Jennica Andersson</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126890316</v>
+        <v>126891185</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>78424</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2684,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685410</v>
+        <v>685417</v>
       </c>
       <c r="R21" t="n">
-        <v>7106991</v>
+        <v>7106968</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,29 +2751,25 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På stor torraka med brännspår</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lotta Ihse</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
+          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2779,45 +2780,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891185</v>
+        <v>126890630</v>
       </c>
       <c r="B22" t="n">
-        <v>78424</v>
+        <v>98364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Lögdåberget, Ång</t>
+          <t>Lill Lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685417</v>
+        <v>685421</v>
       </c>
       <c r="R22" t="n">
-        <v>7106968</v>
+        <v>7107205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2858,19 +2859,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lotta Ihse</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lotta Ihse, Carl Jansson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Anne Siivola, Beke Regelin, Lars-Erik Nilsson, Torbjörn Söderquist</t>
+          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2881,45 +2881,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126890630</v>
+        <v>126890200</v>
       </c>
       <c r="B23" t="n">
-        <v>98364</v>
+        <v>77996</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill Lögdåberget, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685421</v>
+        <v>685218</v>
       </c>
       <c r="R23" t="n">
-        <v>7107205</v>
+        <v>7107060</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,12 +2966,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2982,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891637</v>
+        <v>126890328</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685419</v>
+        <v>685268</v>
       </c>
       <c r="R24" t="n">
-        <v>7107106</v>
+        <v>7107110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3067,12 +3067,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunilla R Burke, Carl Jansson, Alexandra Astafourova, kristina stenmarck, Eleonor Johansson, Jennica Andersson, Anne Siivola, Beke Regelin, Elin Kannerby, Hedda Bring, Lotta Ihse, Torbjörn Söderquist</t>
+          <t>Beke Regelin, Carl Jansson, Lars-Erik Nilsson, Elin Kannerby, Alexandra Astafourova, kristina stenmarck, Gunilla R Burke, Eleonor Johansson, Hedda Bring, Jennica Andersson, Lotta Ihse, Anne Siivola, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3083,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126890098</v>
+        <v>126890101</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,21 +3094,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685407</v>
+        <v>685405</v>
       </c>
       <c r="R25" t="n">
-        <v>7107134</v>
+        <v>7107108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,21 +3164,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3199,7 +3184,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126890101</v>
+        <v>126890156</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3230,14 +3215,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685405</v>
+        <v>685267</v>
       </c>
       <c r="R26" t="n">
-        <v>7107108</v>
+        <v>7107114</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,12 +3269,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3300,7 +3285,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126890156</v>
+        <v>126890075</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3331,14 +3316,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-lögdåberget, Ång</t>
+          <t>Norrholmsjö, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685267</v>
+        <v>685334</v>
       </c>
       <c r="R27" t="n">
-        <v>7107114</v>
+        <v>7107003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3385,12 +3370,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
+          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3401,10 +3386,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126890075</v>
+        <v>126890201</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,34 +3397,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrholmsjö, Ång</t>
+          <t>Lill-lögdåberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685334</v>
+        <v>685214</v>
       </c>
       <c r="R28" t="n">
-        <v>7107003</v>
+        <v>7107061</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,12 +3471,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Beke Regelin, kristina stenmarck, Elin Kannerby, Torbjörn Söderquist, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Jennica Andersson, Eleonor Johansson, Alexandra Astafourova, Gunilla R Burke</t>
+          <t>Alexandra Astafourova, Jennica Andersson, Eleonor Johansson, Carl Jansson, Elin Kannerby, Gunilla R Burke, kristina stenmarck, Lars-Erik Nilsson, Anne Siivola, Hedda Bring, Lotta Ihse, Torbjörn Söderquist, Beke Regelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3502,10 +3487,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126890328</v>
+        <v>126891637</v>
       </c>
